--- a/cluster_analysis/latest.xlsx
+++ b/cluster_analysis/latest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://creativeartistsagencygbr.sharepoint.com/sites/NFSIMPLEMENTATIONSAFF/Shared Documents/04 Deliverables WIP/SAFF 2025 Plan/Competitions restructure/Analysis/Clubs Gap Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="189" documentId="13_ncr:1_{973241F7-B0A8-4B0E-9B8D-D4C79E1A4082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1729CBD-BEC8-4DAA-ADBD-FE5D98CF8C9D}"/>
+  <xr:revisionPtr revIDLastSave="312" documentId="13_ncr:1_{973241F7-B0A8-4B0E-9B8D-D4C79E1A4082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B015C482-CA87-4520-9DB4-9750795B1568}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="3" xr2:uid="{696254E1-FDC9-4707-85DD-EE834AB8F841}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{696254E1-FDC9-4707-85DD-EE834AB8F841}"/>
   </bookViews>
   <sheets>
     <sheet name="ملخص المجموعات" sheetId="4" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3601" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3826" uniqueCount="707">
   <si>
     <t>المجموعة</t>
   </si>
@@ -2403,160 +2403,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3258,6 +3104,160 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3276,21 +3276,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D5714613-7CB3-4778-9CFB-5F2E956CE80E}" name="ملخص_المجموعات" displayName="ملخص_المجموعات" ref="B2:G271" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D5714613-7CB3-4778-9CFB-5F2E956CE80E}" name="ملخص_المجموعات" displayName="ملخص_المجموعات" ref="B2:G271" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
   <autoFilter ref="B2:G271" xr:uid="{D5714613-7CB3-4778-9CFB-5F2E956CE80E}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{21357364-A1AC-40A0-A103-719BBF35D23E}" name="الفئة" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{FED87C10-4531-4310-A0AB-63BF8FB11944}" name="المجموعة" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{AE4FCF05-32B9-4C29-8A35-872FE1B3A005}" name="عدد المدن" dataDxfId="21">
+    <tableColumn id="1" xr3:uid="{21357364-A1AC-40A0-A103-719BBF35D23E}" name="الفئة" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{FED87C10-4531-4310-A0AB-63BF8FB11944}" name="المجموعة" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{AE4FCF05-32B9-4C29-8A35-872FE1B3A005}" name="عدد المدن" dataDxfId="30">
       <calculatedColumnFormula>COUNTIFS(تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{FD58C7EE-75CB-499E-85CF-7282CB19CA62}" name="المدن" dataDxfId="20">
+    <tableColumn id="6" xr3:uid="{FD58C7EE-75CB-499E-85CF-7282CB19CA62}" name="المدن" dataDxfId="29">
       <calculatedColumnFormula array="1">_xlfn.TEXTJOIN("، ",TRUE,IF((تفاصيل_الفرق[الفئة العمرية]=ملخص_المجموعات[[#This Row],[الفئة]])*(تفاصيل_الفرق[المجموعة]=ملخص_المجموعات[[#This Row],[المجموعة]]),تفاصيل_الفرق[المدينة/المحافظة],""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EB7BF368-B482-4173-985E-A61BA4F4C980}" name="مجموع الفرق" dataDxfId="19">
+    <tableColumn id="4" xr3:uid="{EB7BF368-B482-4173-985E-A61BA4F4C980}" name="مجموع الفرق" dataDxfId="28">
       <calculatedColumnFormula>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B4DAD3B8-5E7E-481E-B3FC-6B7F1675A2AC}" name="المتبقي" dataDxfId="18">
+    <tableColumn id="5" xr3:uid="{B4DAD3B8-5E7E-481E-B3FC-6B7F1675A2AC}" name="المتبقي" dataDxfId="27">
       <calculatedColumnFormula>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3299,15 +3299,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C701D678-71F0-44FF-ADB2-214FC277166A}" name="تفاصيل_الفرق" displayName="تفاصيل_الفرق" ref="B2:E580" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C701D678-71F0-44FF-ADB2-214FC277166A}" name="تفاصيل_الفرق" displayName="تفاصيل_الفرق" ref="B2:E580" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="B2:E580" xr:uid="{C701D678-71F0-44FF-ADB2-214FC277166A}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BA3E5021-A230-4D22-874F-F4F2E40E742F}" name="الفئة العمرية" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{125018BC-E7FF-461A-A50D-47C8428F3CCC}" name="المدينة/المحافظة" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{CB78D930-6811-46BE-9E54-828AD86943E6}" name="المجموعة" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{BA3E5021-A230-4D22-874F-F4F2E40E742F}" name="الفئة العمرية" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{125018BC-E7FF-461A-A50D-47C8428F3CCC}" name="المدينة/المحافظة" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{CB78D930-6811-46BE-9E54-828AD86943E6}" name="المجموعة" dataDxfId="22">
       <calculatedColumnFormula array="1">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EF5C574A-EDBE-4210-9614-DB0BF5439C78}" name="عدد الفرق" dataDxfId="12">
+    <tableColumn id="4" xr3:uid="{EF5C574A-EDBE-4210-9614-DB0BF5439C78}" name="عدد الفرق" dataDxfId="21">
       <calculatedColumnFormula array="1">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3316,57 +3316,51 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C98C69F7-A5A5-41A9-9F9D-AF91B174B3C2}" name="التسجيل" displayName="التسجيل" ref="B2:Q227" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" tableBorderDxfId="42" dataCellStyle="Normal 2">
-  <autoFilter ref="B2:Q227" xr:uid="{C98C69F7-A5A5-41A9-9F9D-AF91B174B3C2}">
-    <filterColumn colId="7">
-      <filters>
-        <filter val="عيون الجواء"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:Q203">
-    <sortCondition ref="I2:I203"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C98C69F7-A5A5-41A9-9F9D-AF91B174B3C2}" name="التسجيل" displayName="التسجيل" ref="B2:Q227" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18" dataCellStyle="Normal 2">
+  <autoFilter ref="B2:Q227" xr:uid="{C98C69F7-A5A5-41A9-9F9D-AF91B174B3C2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:Q227">
+    <sortCondition ref="B2:B227"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{090AD518-161E-48A1-BB46-837D6EA74252}" name="Entry Id" dataDxfId="41" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{AC3FCE35-ED74-4BDA-B2C1-71DE81164517}" name="اسم الفريق" dataDxfId="40" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{BAB92966-1EB1-4C4A-A003-A8F57A08F900}" name="الاسم " dataDxfId="39" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{41B901FC-6026-4BE2-A9C0-4BA71B6BC5DE}" name="رقم الجوال" dataDxfId="38" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{9F68BE70-1FDC-4425-9940-DF2CEFD9B032}" name="اسم الملعب" dataDxfId="37" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{0BB31EF5-FF5E-497E-95C0-AC1316951F24}" name="الصفة" dataDxfId="36" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{50DE72A8-1E19-4962-9931-E2D97E6E6125}" name="المنطقة" dataDxfId="35" dataCellStyle="Normal 2"/>
-    <tableColumn id="8" xr3:uid="{0A336E9A-961E-4220-ADF7-AB5BC3EFC496}" name="المدينة" dataDxfId="34" dataCellStyle="Normal 2"/>
-    <tableColumn id="17" xr3:uid="{9A1E561B-D0E7-4011-9527-4DE3A58FAD08}" name="مكتب الوزارة" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{313DDC39-AC82-48CC-BCED-A8D8B0B50F10}" name="المشاركة تحت 14" dataDxfId="32" dataCellStyle="Normal 2"/>
-    <tableColumn id="10" xr3:uid="{056EB01F-9295-4034-859B-42056695639E}" name="المشاركة تحت 13" dataDxfId="31" dataCellStyle="Normal 2"/>
-    <tableColumn id="11" xr3:uid="{0A942E27-C19C-4583-B65B-63FA254B3871}" name="المشاركة تحت 12" dataDxfId="30" dataCellStyle="Normal 2"/>
-    <tableColumn id="12" xr3:uid="{4FD6226C-F925-47F1-A13D-AA249B8D9FD0}" name="المشاركة تحت 11" dataDxfId="29" dataCellStyle="Normal 2"/>
-    <tableColumn id="13" xr3:uid="{7C0BB045-F917-4504-A7B2-0720DBB4DE2F}" name="المشاركة تحت 9" dataDxfId="28" dataCellStyle="Normal 2"/>
-    <tableColumn id="14" xr3:uid="{FD475FF4-5023-4EA1-B10C-9DE555315DBC}" name="المشاركة تحت 7 " dataDxfId="27" dataCellStyle="Normal 2"/>
-    <tableColumn id="15" xr3:uid="{43B89F76-F8D8-491F-B6E6-05BED7569326}" name="المشاركة تحت 5" dataDxfId="26" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{090AD518-161E-48A1-BB46-837D6EA74252}" name="Entry Id" dataDxfId="17" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{AC3FCE35-ED74-4BDA-B2C1-71DE81164517}" name="اسم الفريق" dataDxfId="16" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{BAB92966-1EB1-4C4A-A003-A8F57A08F900}" name="الاسم " dataDxfId="15" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{41B901FC-6026-4BE2-A9C0-4BA71B6BC5DE}" name="رقم الجوال" dataDxfId="14" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{9F68BE70-1FDC-4425-9940-DF2CEFD9B032}" name="اسم الملعب" dataDxfId="13" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{0BB31EF5-FF5E-497E-95C0-AC1316951F24}" name="الصفة" dataDxfId="12" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{50DE72A8-1E19-4962-9931-E2D97E6E6125}" name="المنطقة" dataDxfId="11" dataCellStyle="Normal 2"/>
+    <tableColumn id="8" xr3:uid="{0A336E9A-961E-4220-ADF7-AB5BC3EFC496}" name="المدينة" dataDxfId="10" dataCellStyle="Normal 2"/>
+    <tableColumn id="17" xr3:uid="{9A1E561B-D0E7-4011-9527-4DE3A58FAD08}" name="مكتب الوزارة" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{313DDC39-AC82-48CC-BCED-A8D8B0B50F10}" name="المشاركة تحت 14" dataDxfId="8" dataCellStyle="Normal 2"/>
+    <tableColumn id="10" xr3:uid="{056EB01F-9295-4034-859B-42056695639E}" name="المشاركة تحت 13" dataDxfId="7" dataCellStyle="Normal 2"/>
+    <tableColumn id="11" xr3:uid="{0A942E27-C19C-4583-B65B-63FA254B3871}" name="المشاركة تحت 12" dataDxfId="6" dataCellStyle="Normal 2"/>
+    <tableColumn id="12" xr3:uid="{4FD6226C-F925-47F1-A13D-AA249B8D9FD0}" name="المشاركة تحت 11" dataDxfId="5" dataCellStyle="Normal 2"/>
+    <tableColumn id="13" xr3:uid="{7C0BB045-F917-4504-A7B2-0720DBB4DE2F}" name="المشاركة تحت 9" dataDxfId="4" dataCellStyle="Normal 2"/>
+    <tableColumn id="14" xr3:uid="{FD475FF4-5023-4EA1-B10C-9DE555315DBC}" name="المشاركة تحت 7 " dataDxfId="3" dataCellStyle="Normal 2"/>
+    <tableColumn id="15" xr3:uid="{43B89F76-F8D8-491F-B6E6-05BED7569326}" name="المشاركة تحت 5" dataDxfId="2" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CB8954BF-907E-4B78-AA0B-B695FCB5D5AC}" name="ربط_الفئات" displayName="ربط_الفئات" ref="F2:G9" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CB8954BF-907E-4B78-AA0B-B695FCB5D5AC}" name="ربط_الفئات" displayName="ربط_الفئات" ref="F2:G9" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" tableBorderDxfId="42">
   <autoFilter ref="F2:G9" xr:uid="{CB8954BF-907E-4B78-AA0B-B695FCB5D5AC}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{30FFDE77-56F6-44C2-B6A6-155DCF4CF8DB}" name="الفئة" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{86DFE088-41CB-49A5-A5FE-6AC945BFCDB8}" name="مجموعة الفئات" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{30FFDE77-56F6-44C2-B6A6-155DCF4CF8DB}" name="الفئة" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{86DFE088-41CB-49A5-A5FE-6AC945BFCDB8}" name="مجموعة الفئات" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C0D9CA94-7B1D-4BB6-9D8F-BBAF4BDFA449}" name="المدن_المصدر" displayName="المدن_المصدر" ref="B2:D166" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C0D9CA94-7B1D-4BB6-9D8F-BBAF4BDFA449}" name="المدن_المصدر" displayName="المدن_المصدر" ref="B2:D166" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <autoFilter ref="B2:D166" xr:uid="{C0D9CA94-7B1D-4BB6-9D8F-BBAF4BDFA449}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{230C2C42-A057-407F-B36C-357E7EDD9E62}" name="الفئة العمرية" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{DA75C6C1-EEE2-478C-AB61-D44245FEF7F3}" name="المجموعة" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{6A5033B9-28EA-44F9-A1C0-ACDB72370A69}" name="المدينة/المحافظة" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{230C2C42-A057-407F-B36C-357E7EDD9E62}" name="الفئة العمرية" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{DA75C6C1-EEE2-478C-AB61-D44245FEF7F3}" name="المجموعة" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{6A5033B9-28EA-44F9-A1C0-ACDB72370A69}" name="المدينة/المحافظة" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3689,7 +3683,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="525" row="1">
+  <wetp:taskpane dockstate="right" visibility="0" width="924" row="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -19604,7 +19598,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="3" spans="2:221" s="13" customFormat="1" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:221" s="13" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="12">
         <v>1</v>
       </c>
@@ -19629,7 +19623,9 @@
       <c r="I3" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="J3" s="12"/>
+      <c r="J3" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="K3" s="12">
         <v>0</v>
       </c>
@@ -19856,7 +19852,7 @@
       <c r="HL3"/>
       <c r="HM3"/>
     </row>
-    <row r="4" spans="2:221" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:221" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="12">
         <v>2</v>
       </c>
@@ -19881,7 +19877,9 @@
       <c r="I4" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="12"/>
+      <c r="J4" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K4" s="12">
         <v>1</v>
       </c>
@@ -19904,7 +19902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:221" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:221" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="12">
         <v>3</v>
       </c>
@@ -19929,7 +19927,9 @@
       <c r="I5" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="J5" s="12"/>
+      <c r="J5" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="K5" s="12">
         <v>1</v>
       </c>
@@ -19952,7 +19952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:221" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:221" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="12">
         <v>4</v>
       </c>
@@ -19977,7 +19977,9 @@
       <c r="I6" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="J6" s="12"/>
+      <c r="J6" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="K6" s="12">
         <v>0</v>
       </c>
@@ -20025,7 +20027,9 @@
       <c r="I7" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J7" s="12"/>
+      <c r="J7" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="K7" s="12">
         <v>1</v>
       </c>
@@ -20048,7 +20052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:221" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:221" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="12">
         <v>6</v>
       </c>
@@ -20073,7 +20077,9 @@
       <c r="I8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="12"/>
+      <c r="J8" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K8" s="12">
         <v>1</v>
       </c>
@@ -20096,7 +20102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:221" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:221" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="12">
         <v>7</v>
       </c>
@@ -20121,7 +20127,9 @@
       <c r="I9" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="J9" s="12"/>
+      <c r="J9" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="K9" s="12">
         <v>0</v>
       </c>
@@ -20144,7 +20152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:221" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:221" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="12">
         <v>8</v>
       </c>
@@ -20169,7 +20177,9 @@
       <c r="I10" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J10" s="12"/>
+      <c r="J10" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K10" s="12">
         <v>1</v>
       </c>
@@ -20192,7 +20202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:221" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:221" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="12">
         <v>9</v>
       </c>
@@ -20217,7 +20227,9 @@
       <c r="I11" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="12"/>
+      <c r="J11" s="12" t="s">
+        <v>144</v>
+      </c>
       <c r="K11" s="12">
         <v>1</v>
       </c>
@@ -20240,7 +20252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:221" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:221" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="12">
         <v>10</v>
       </c>
@@ -20265,7 +20277,9 @@
       <c r="I12" s="12" t="s">
         <v>701</v>
       </c>
-      <c r="J12" s="12"/>
+      <c r="J12" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="K12" s="12">
         <v>1</v>
       </c>
@@ -20288,7 +20302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:221" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:221" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="12">
         <v>11</v>
       </c>
@@ -20313,7 +20327,9 @@
       <c r="I13" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="J13" s="12"/>
+      <c r="J13" s="12" t="s">
+        <v>94</v>
+      </c>
       <c r="K13" s="12">
         <v>1</v>
       </c>
@@ -20336,7 +20352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:221" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:221" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="12">
         <v>12</v>
       </c>
@@ -20361,7 +20377,9 @@
       <c r="I14" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="J14" s="12"/>
+      <c r="J14" s="12" t="s">
+        <v>87</v>
+      </c>
       <c r="K14" s="12">
         <v>1</v>
       </c>
@@ -20384,7 +20402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:221" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:221" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="12">
         <v>13</v>
       </c>
@@ -20409,7 +20427,9 @@
       <c r="I15" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J15" s="12"/>
+      <c r="J15" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K15" s="12">
         <v>0</v>
       </c>
@@ -20432,7 +20452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:221" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:221" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="12">
         <v>14</v>
       </c>
@@ -20457,7 +20477,9 @@
       <c r="I16" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="J16" s="12"/>
+      <c r="J16" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="K16" s="12">
         <v>1</v>
       </c>
@@ -20480,7 +20502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:17" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="12">
         <v>15</v>
       </c>
@@ -20505,7 +20527,9 @@
       <c r="I17" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="12"/>
+      <c r="J17" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="K17" s="12">
         <v>1</v>
       </c>
@@ -20528,7 +20552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:17" ht="14" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="12">
         <v>16</v>
       </c>
@@ -20553,7 +20577,9 @@
       <c r="I18" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J18" s="12"/>
+      <c r="J18" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="K18" s="12">
         <v>1</v>
       </c>
@@ -20576,7 +20602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B19" s="12">
         <v>17</v>
       </c>
@@ -20601,7 +20627,9 @@
       <c r="I19" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J19" s="12"/>
+      <c r="J19" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K19" s="12">
         <v>1</v>
       </c>
@@ -20624,7 +20652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B20" s="12">
         <v>18</v>
       </c>
@@ -20649,7 +20677,9 @@
       <c r="I20" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J20" s="12"/>
+      <c r="J20" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K20" s="12">
         <v>0</v>
       </c>
@@ -20672,7 +20702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B21" s="12">
         <v>19</v>
       </c>
@@ -20697,7 +20727,9 @@
       <c r="I21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="J21" s="12"/>
+      <c r="J21" s="12" t="s">
+        <v>227</v>
+      </c>
       <c r="K21" s="12">
         <v>1</v>
       </c>
@@ -20720,7 +20752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B22" s="12">
         <v>20</v>
       </c>
@@ -20745,7 +20777,9 @@
       <c r="I22" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="J22" s="12"/>
+      <c r="J22" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="K22" s="12">
         <v>0</v>
       </c>
@@ -20768,7 +20802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B23" s="12">
         <v>21</v>
       </c>
@@ -20793,7 +20827,9 @@
       <c r="I23" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="J23" s="12"/>
+      <c r="J23" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="K23" s="12">
         <v>0</v>
       </c>
@@ -20816,7 +20852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B24" s="12">
         <v>22</v>
       </c>
@@ -20841,7 +20877,9 @@
       <c r="I24" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J24" s="12"/>
+      <c r="J24" s="12" t="s">
+        <v>94</v>
+      </c>
       <c r="K24" s="12">
         <v>1</v>
       </c>
@@ -20864,7 +20902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B25" s="12">
         <v>23</v>
       </c>
@@ -20889,7 +20927,9 @@
       <c r="I25" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J25" s="12"/>
+      <c r="J25" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K25" s="12">
         <v>1</v>
       </c>
@@ -20912,7 +20952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B26" s="12">
         <v>24</v>
       </c>
@@ -20937,7 +20977,9 @@
       <c r="I26" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="J26" s="12"/>
+      <c r="J26" s="12" t="s">
+        <v>100</v>
+      </c>
       <c r="K26" s="12">
         <v>1</v>
       </c>
@@ -20960,7 +21002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B27" s="12">
         <v>25</v>
       </c>
@@ -20985,7 +21027,9 @@
       <c r="I27" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="J27" s="12"/>
+      <c r="J27" s="12" t="s">
+        <v>227</v>
+      </c>
       <c r="K27" s="12">
         <v>1</v>
       </c>
@@ -21008,7 +21052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B28" s="12">
         <v>26</v>
       </c>
@@ -21033,7 +21077,9 @@
       <c r="I28" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J28" s="12"/>
+      <c r="J28" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="K28" s="12">
         <v>1</v>
       </c>
@@ -21056,7 +21102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B29" s="12">
         <v>27</v>
       </c>
@@ -21081,7 +21127,9 @@
       <c r="I29" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J29" s="12"/>
+      <c r="J29" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K29" s="12">
         <v>0</v>
       </c>
@@ -21104,7 +21152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B30" s="12">
         <v>28</v>
       </c>
@@ -21129,7 +21177,9 @@
       <c r="I30" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J30" s="12"/>
+      <c r="J30" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K30" s="12">
         <v>1</v>
       </c>
@@ -21152,7 +21202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B31" s="12">
         <v>29</v>
       </c>
@@ -21177,7 +21227,9 @@
       <c r="I31" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J31" s="12"/>
+      <c r="J31" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K31" s="12">
         <v>1</v>
       </c>
@@ -21200,7 +21252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B32" s="12">
         <v>30</v>
       </c>
@@ -21225,7 +21277,9 @@
       <c r="I32" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J32" s="12"/>
+      <c r="J32" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K32" s="12">
         <v>0</v>
       </c>
@@ -21248,7 +21302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B33" s="12">
         <v>31</v>
       </c>
@@ -21273,7 +21327,9 @@
       <c r="I33" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="J33" s="12"/>
+      <c r="J33" s="12" t="s">
+        <v>227</v>
+      </c>
       <c r="K33" s="12">
         <v>1</v>
       </c>
@@ -21296,7 +21352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B34" s="12">
         <v>32</v>
       </c>
@@ -21321,7 +21377,9 @@
       <c r="I34" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J34" s="12"/>
+      <c r="J34" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K34" s="12">
         <v>1</v>
       </c>
@@ -21344,7 +21402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B35" s="12">
         <v>33</v>
       </c>
@@ -21369,7 +21427,9 @@
       <c r="I35" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="J35" s="12"/>
+      <c r="J35" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K35" s="12">
         <v>1</v>
       </c>
@@ -21392,7 +21452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B36" s="12">
         <v>34</v>
       </c>
@@ -21417,7 +21477,9 @@
       <c r="I36" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J36" s="12"/>
+      <c r="J36" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K36" s="12">
         <v>1</v>
       </c>
@@ -21440,7 +21502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B37" s="12">
         <v>35</v>
       </c>
@@ -21465,7 +21527,9 @@
       <c r="I37" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="J37" s="12"/>
+      <c r="J37" s="12" t="s">
+        <v>100</v>
+      </c>
       <c r="K37" s="12">
         <v>0</v>
       </c>
@@ -21488,7 +21552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B38" s="12">
         <v>36</v>
       </c>
@@ -21513,7 +21577,9 @@
       <c r="I38" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J38" s="12"/>
+      <c r="J38" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K38" s="12">
         <v>1</v>
       </c>
@@ -21536,7 +21602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B39" s="12">
         <v>37</v>
       </c>
@@ -21561,7 +21627,9 @@
       <c r="I39" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J39" s="12"/>
+      <c r="J39" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K39" s="12">
         <v>0</v>
       </c>
@@ -21584,7 +21652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B40" s="12">
         <v>38</v>
       </c>
@@ -21609,7 +21677,9 @@
       <c r="I40" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="J40" s="12"/>
+      <c r="J40" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="K40" s="12">
         <v>0</v>
       </c>
@@ -21632,7 +21702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B41" s="12">
         <v>39</v>
       </c>
@@ -21657,7 +21727,9 @@
       <c r="I41" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="J41" s="12"/>
+      <c r="J41" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="K41" s="12">
         <v>0</v>
       </c>
@@ -21680,7 +21752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B42" s="12">
         <v>40</v>
       </c>
@@ -21705,7 +21777,9 @@
       <c r="I42" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="J42" s="12"/>
+      <c r="J42" s="12" t="s">
+        <v>100</v>
+      </c>
       <c r="K42" s="12">
         <v>1</v>
       </c>
@@ -21728,7 +21802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B43" s="12">
         <v>41</v>
       </c>
@@ -21753,7 +21827,9 @@
       <c r="I43" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="J43" s="12"/>
+      <c r="J43" s="12" t="s">
+        <v>94</v>
+      </c>
       <c r="K43" s="12">
         <v>1</v>
       </c>
@@ -21776,7 +21852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B44" s="12">
         <v>42</v>
       </c>
@@ -21801,7 +21877,9 @@
       <c r="I44" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J44" s="12"/>
+      <c r="J44" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="K44" s="12">
         <v>1</v>
       </c>
@@ -21824,7 +21902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B45" s="12">
         <v>43</v>
       </c>
@@ -21849,7 +21927,9 @@
       <c r="I45" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="J45" s="12"/>
+      <c r="J45" s="12" t="s">
+        <v>138</v>
+      </c>
       <c r="K45" s="12">
         <v>1</v>
       </c>
@@ -21872,7 +21952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B46" s="12">
         <v>44</v>
       </c>
@@ -21897,7 +21977,9 @@
       <c r="I46" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="J46" s="12"/>
+      <c r="J46" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="K46" s="12">
         <v>1</v>
       </c>
@@ -21920,7 +22002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B47" s="12">
         <v>45</v>
       </c>
@@ -21945,7 +22027,9 @@
       <c r="I47" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="J47" s="12"/>
+      <c r="J47" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="K47" s="12">
         <v>1</v>
       </c>
@@ -21968,7 +22052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B48" s="12">
         <v>46</v>
       </c>
@@ -21993,7 +22077,9 @@
       <c r="I48" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J48" s="12"/>
+      <c r="J48" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K48" s="12">
         <v>1</v>
       </c>
@@ -22017,7 +22103,7 @@
       </c>
       <c r="R48" s="3"/>
     </row>
-    <row r="49" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B49" s="12">
         <v>47</v>
       </c>
@@ -22042,7 +22128,9 @@
       <c r="I49" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J49" s="12"/>
+      <c r="J49" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K49" s="12">
         <v>1</v>
       </c>
@@ -22066,7 +22154,7 @@
       </c>
       <c r="R49" s="3"/>
     </row>
-    <row r="50" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B50" s="12">
         <v>48</v>
       </c>
@@ -22091,7 +22179,9 @@
       <c r="I50" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="J50" s="12"/>
+      <c r="J50" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="K50" s="12">
         <v>0</v>
       </c>
@@ -22114,7 +22204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B51" s="12">
         <v>49</v>
       </c>
@@ -22139,7 +22229,9 @@
       <c r="I51" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J51" s="12"/>
+      <c r="J51" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K51" s="12">
         <v>1</v>
       </c>
@@ -22162,7 +22254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B52" s="12">
         <v>50</v>
       </c>
@@ -22187,7 +22279,9 @@
       <c r="I52" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J52" s="12"/>
+      <c r="J52" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K52" s="12">
         <v>0</v>
       </c>
@@ -22210,7 +22304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B53" s="12">
         <v>51</v>
       </c>
@@ -22235,7 +22329,9 @@
       <c r="I53" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="J53" s="12"/>
+      <c r="J53" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="K53" s="12">
         <v>1</v>
       </c>
@@ -22259,7 +22355,7 @@
       </c>
       <c r="R53" s="3"/>
     </row>
-    <row r="54" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B54" s="12">
         <v>52</v>
       </c>
@@ -22284,7 +22380,9 @@
       <c r="I54" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J54" s="12"/>
+      <c r="J54" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K54" s="12">
         <v>1</v>
       </c>
@@ -22307,7 +22405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B55" s="12">
         <v>53</v>
       </c>
@@ -22332,7 +22430,9 @@
       <c r="I55" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="J55" s="12"/>
+      <c r="J55" s="12" t="s">
+        <v>144</v>
+      </c>
       <c r="K55" s="12">
         <v>1</v>
       </c>
@@ -22356,7 +22456,7 @@
       </c>
       <c r="R55" s="3"/>
     </row>
-    <row r="56" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B56" s="12">
         <v>54</v>
       </c>
@@ -22381,7 +22481,9 @@
       <c r="I56" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J56" s="12"/>
+      <c r="J56" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K56" s="12">
         <v>1</v>
       </c>
@@ -22405,7 +22507,7 @@
       </c>
       <c r="R56" s="3"/>
     </row>
-    <row r="57" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B57" s="12">
         <v>55</v>
       </c>
@@ -22430,7 +22532,9 @@
       <c r="I57" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J57" s="12"/>
+      <c r="J57" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K57" s="12">
         <v>1</v>
       </c>
@@ -22453,7 +22557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B58" s="12">
         <v>56</v>
       </c>
@@ -22478,7 +22582,9 @@
       <c r="I58" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J58" s="12"/>
+      <c r="J58" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K58" s="12">
         <v>1</v>
       </c>
@@ -22501,7 +22607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B59" s="12">
         <v>57</v>
       </c>
@@ -22526,7 +22632,9 @@
       <c r="I59" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J59" s="12"/>
+      <c r="J59" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K59" s="12">
         <v>0</v>
       </c>
@@ -22549,7 +22657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B60" s="12">
         <v>58</v>
       </c>
@@ -22574,7 +22682,9 @@
       <c r="I60" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J60" s="12"/>
+      <c r="J60" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K60" s="12">
         <v>1</v>
       </c>
@@ -22598,7 +22708,7 @@
       </c>
       <c r="R60" s="3"/>
     </row>
-    <row r="61" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B61" s="12">
         <v>59</v>
       </c>
@@ -22623,7 +22733,9 @@
       <c r="I61" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="J61" s="12"/>
+      <c r="J61" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="K61" s="12">
         <v>1</v>
       </c>
@@ -22646,7 +22758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B62" s="12">
         <v>60</v>
       </c>
@@ -22671,7 +22783,9 @@
       <c r="I62" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J62" s="12"/>
+      <c r="J62" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K62" s="12">
         <v>1</v>
       </c>
@@ -22694,7 +22808,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B63" s="12">
         <v>61</v>
       </c>
@@ -22719,7 +22833,9 @@
       <c r="I63" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="J63" s="12"/>
+      <c r="J63" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="K63" s="12">
         <v>0</v>
       </c>
@@ -22742,7 +22858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="2:18" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:18" ht="17" x14ac:dyDescent="0.35">
       <c r="B64" s="12">
         <v>62</v>
       </c>
@@ -22767,7 +22883,9 @@
       <c r="I64" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="J64" s="12"/>
+      <c r="J64" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="K64" s="12">
         <v>0</v>
       </c>
@@ -22790,7 +22908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B65" s="12">
         <v>63</v>
       </c>
@@ -22815,7 +22933,9 @@
       <c r="I65" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="J65" s="12"/>
+      <c r="J65" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="K65" s="12">
         <v>0</v>
       </c>
@@ -22838,7 +22958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B66" s="12">
         <v>64</v>
       </c>
@@ -22863,7 +22983,9 @@
       <c r="I66" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J66" s="12"/>
+      <c r="J66" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K66" s="12">
         <v>0</v>
       </c>
@@ -22886,7 +23008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B67" s="12">
         <v>65</v>
       </c>
@@ -22911,7 +23033,9 @@
       <c r="I67" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="J67" s="12"/>
+      <c r="J67" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="K67" s="12">
         <v>1</v>
       </c>
@@ -22934,7 +23058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B68" s="12">
         <v>66</v>
       </c>
@@ -22959,7 +23083,9 @@
       <c r="I68" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="J68" s="12"/>
+      <c r="J68" s="12" t="s">
+        <v>138</v>
+      </c>
       <c r="K68" s="12">
         <v>1</v>
       </c>
@@ -22982,7 +23108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B69" s="12">
         <v>67</v>
       </c>
@@ -23007,7 +23133,9 @@
       <c r="I69" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J69" s="12"/>
+      <c r="J69" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K69" s="12">
         <v>1</v>
       </c>
@@ -23030,7 +23158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B70" s="12">
         <v>68</v>
       </c>
@@ -23055,7 +23183,9 @@
       <c r="I70" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J70" s="12"/>
+      <c r="J70" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K70" s="12">
         <v>1</v>
       </c>
@@ -23078,7 +23208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B71" s="12">
         <v>69</v>
       </c>
@@ -23103,7 +23233,9 @@
       <c r="I71" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J71" s="12"/>
+      <c r="J71" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K71" s="12">
         <v>1</v>
       </c>
@@ -23126,7 +23258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B72" s="12">
         <v>70</v>
       </c>
@@ -23151,7 +23283,9 @@
       <c r="I72" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J72" s="12"/>
+      <c r="J72" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K72" s="12">
         <v>1</v>
       </c>
@@ -23174,7 +23308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B73" s="12">
         <v>71</v>
       </c>
@@ -23199,7 +23333,9 @@
       <c r="I73" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="J73" s="12"/>
+      <c r="J73" s="12" t="s">
+        <v>144</v>
+      </c>
       <c r="K73" s="12">
         <v>1</v>
       </c>
@@ -23222,7 +23358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B74" s="12">
         <v>72</v>
       </c>
@@ -23247,7 +23383,9 @@
       <c r="I74" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J74" s="12"/>
+      <c r="J74" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K74" s="12">
         <v>1</v>
       </c>
@@ -23270,7 +23408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B75" s="12">
         <v>73</v>
       </c>
@@ -23295,7 +23433,9 @@
       <c r="I75" s="12" t="s">
         <v>362</v>
       </c>
-      <c r="J75" s="12"/>
+      <c r="J75" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="K75" s="12">
         <v>1</v>
       </c>
@@ -23318,7 +23458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B76" s="12">
         <v>74</v>
       </c>
@@ -23343,7 +23483,9 @@
       <c r="I76" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="J76" s="12"/>
+      <c r="J76" s="12" t="s">
+        <v>144</v>
+      </c>
       <c r="K76" s="12">
         <v>1</v>
       </c>
@@ -23366,7 +23508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B77" s="12">
         <v>75</v>
       </c>
@@ -23391,7 +23533,9 @@
       <c r="I77" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J77" s="12"/>
+      <c r="J77" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="K77" s="12">
         <v>1</v>
       </c>
@@ -23414,7 +23558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B78" s="12">
         <v>76</v>
       </c>
@@ -23439,7 +23583,9 @@
       <c r="I78" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J78" s="12"/>
+      <c r="J78" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K78" s="12">
         <v>1</v>
       </c>
@@ -23462,7 +23608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B79" s="12">
         <v>77</v>
       </c>
@@ -23487,7 +23633,9 @@
       <c r="I79" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J79" s="12"/>
+      <c r="J79" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K79" s="12">
         <v>1</v>
       </c>
@@ -23510,7 +23658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B80" s="12">
         <v>78</v>
       </c>
@@ -23535,7 +23683,9 @@
       <c r="I80" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J80" s="12"/>
+      <c r="J80" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K80" s="12">
         <v>0</v>
       </c>
@@ -23558,7 +23708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B81" s="12">
         <v>79</v>
       </c>
@@ -23583,7 +23733,9 @@
       <c r="I81" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J81" s="12"/>
+      <c r="J81" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K81" s="12">
         <v>0</v>
       </c>
@@ -23606,7 +23758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B82" s="12">
         <v>80</v>
       </c>
@@ -23631,7 +23783,9 @@
       <c r="I82" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J82" s="12"/>
+      <c r="J82" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K82" s="12">
         <v>0</v>
       </c>
@@ -23654,7 +23808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B83" s="12">
         <v>81</v>
       </c>
@@ -23679,7 +23833,9 @@
       <c r="I83" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J83" s="12"/>
+      <c r="J83" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K83" s="12">
         <v>0</v>
       </c>
@@ -23702,7 +23858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B84" s="12">
         <v>82</v>
       </c>
@@ -23727,7 +23883,9 @@
       <c r="I84" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="J84" s="12"/>
+      <c r="J84" s="12" t="s">
+        <v>144</v>
+      </c>
       <c r="K84" s="12">
         <v>1</v>
       </c>
@@ -23750,7 +23908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B85" s="12">
         <v>83</v>
       </c>
@@ -23775,7 +23933,9 @@
       <c r="I85" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J85" s="12"/>
+      <c r="J85" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K85" s="12">
         <v>1</v>
       </c>
@@ -23798,7 +23958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B86" s="12">
         <v>84</v>
       </c>
@@ -23823,7 +23983,9 @@
       <c r="I86" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="J86" s="12"/>
+      <c r="J86" s="12" t="s">
+        <v>100</v>
+      </c>
       <c r="K86" s="12">
         <v>1</v>
       </c>
@@ -23846,7 +24008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B87" s="12">
         <v>85</v>
       </c>
@@ -23871,7 +24033,9 @@
       <c r="I87" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J87" s="12"/>
+      <c r="J87" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K87" s="12">
         <v>0</v>
       </c>
@@ -23894,7 +24058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B88" s="12">
         <v>86</v>
       </c>
@@ -23919,7 +24083,9 @@
       <c r="I88" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J88" s="12"/>
+      <c r="J88" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K88" s="12">
         <v>1</v>
       </c>
@@ -23942,7 +24108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B89" s="12">
         <v>87</v>
       </c>
@@ -23967,7 +24133,9 @@
       <c r="I89" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J89" s="12"/>
+      <c r="J89" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K89" s="12">
         <v>1</v>
       </c>
@@ -23990,7 +24158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B90" s="12">
         <v>88</v>
       </c>
@@ -24015,7 +24183,9 @@
       <c r="I90" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="J90" s="12"/>
+      <c r="J90" s="12" t="s">
+        <v>87</v>
+      </c>
       <c r="K90" s="12">
         <v>1</v>
       </c>
@@ -24038,7 +24208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B91" s="12">
         <v>89</v>
       </c>
@@ -24063,7 +24233,9 @@
       <c r="I91" s="12" t="s">
         <v>606</v>
       </c>
-      <c r="J91" s="12"/>
+      <c r="J91" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="K91" s="12">
         <v>0</v>
       </c>
@@ -24086,7 +24258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B92" s="12">
         <v>90</v>
       </c>
@@ -24111,7 +24283,9 @@
       <c r="I92" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="J92" s="12"/>
+      <c r="J92" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K92" s="12">
         <v>1</v>
       </c>
@@ -24134,7 +24308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B93" s="12">
         <v>91</v>
       </c>
@@ -24159,7 +24333,9 @@
       <c r="I93" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J93" s="12"/>
+      <c r="J93" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K93" s="12">
         <v>1</v>
       </c>
@@ -24182,7 +24358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B94" s="12">
         <v>92</v>
       </c>
@@ -24207,7 +24383,9 @@
       <c r="I94" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J94" s="12"/>
+      <c r="J94" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K94" s="12">
         <v>1</v>
       </c>
@@ -24230,7 +24408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B95" s="12">
         <v>93</v>
       </c>
@@ -24255,7 +24433,9 @@
       <c r="I95" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J95" s="12"/>
+      <c r="J95" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K95" s="12">
         <v>1</v>
       </c>
@@ -24278,7 +24458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B96" s="12">
         <v>94</v>
       </c>
@@ -24303,7 +24483,9 @@
       <c r="I96" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J96" s="12"/>
+      <c r="J96" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K96" s="12">
         <v>1</v>
       </c>
@@ -24326,7 +24508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B97" s="12">
         <v>95</v>
       </c>
@@ -24351,7 +24533,9 @@
       <c r="I97" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J97" s="12"/>
+      <c r="J97" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K97" s="12">
         <v>1</v>
       </c>
@@ -24374,7 +24558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B98" s="12">
         <v>96</v>
       </c>
@@ -24399,7 +24583,9 @@
       <c r="I98" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J98" s="12"/>
+      <c r="J98" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K98" s="12">
         <v>1</v>
       </c>
@@ -24422,7 +24608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B99" s="12">
         <v>97</v>
       </c>
@@ -24447,7 +24633,9 @@
       <c r="I99" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J99" s="12"/>
+      <c r="J99" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K99" s="12">
         <v>1</v>
       </c>
@@ -24470,7 +24658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B100" s="12">
         <v>98</v>
       </c>
@@ -24495,7 +24683,9 @@
       <c r="I100" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="J100" s="12"/>
+      <c r="J100" s="12" t="s">
+        <v>144</v>
+      </c>
       <c r="K100" s="12">
         <v>1</v>
       </c>
@@ -24518,7 +24708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B101" s="12">
         <v>99</v>
       </c>
@@ -24543,7 +24733,9 @@
       <c r="I101" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J101" s="12"/>
+      <c r="J101" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K101" s="12">
         <v>1</v>
       </c>
@@ -24566,7 +24758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B102" s="12">
         <v>100</v>
       </c>
@@ -24591,7 +24783,9 @@
       <c r="I102" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J102" s="12"/>
+      <c r="J102" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K102" s="12">
         <v>1</v>
       </c>
@@ -24614,7 +24808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B103" s="12">
         <v>101</v>
       </c>
@@ -24639,7 +24833,9 @@
       <c r="I103" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J103" s="12"/>
+      <c r="J103" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K103" s="12">
         <v>1</v>
       </c>
@@ -24662,7 +24858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B104" s="12">
         <v>102</v>
       </c>
@@ -24687,7 +24883,9 @@
       <c r="I104" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J104" s="12"/>
+      <c r="J104" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K104" s="12">
         <v>0</v>
       </c>
@@ -24710,7 +24908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B105" s="12">
         <v>103</v>
       </c>
@@ -24735,7 +24933,9 @@
       <c r="I105" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J105" s="12"/>
+      <c r="J105" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K105" s="12">
         <v>1</v>
       </c>
@@ -24758,7 +24958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B106" s="12">
         <v>104</v>
       </c>
@@ -24779,7 +24979,9 @@
       <c r="I106" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="J106" s="12"/>
+      <c r="J106" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K106" s="12">
         <v>1</v>
       </c>
@@ -24802,7 +25004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B107" s="12">
         <v>105</v>
       </c>
@@ -24825,7 +25027,9 @@
       <c r="I107" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="J107" s="12"/>
+      <c r="J107" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K107" s="12">
         <v>1</v>
       </c>
@@ -24848,7 +25052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B108" s="12">
         <v>106</v>
       </c>
@@ -24873,7 +25077,9 @@
       <c r="I108" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J108" s="12"/>
+      <c r="J108" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K108" s="12">
         <v>1</v>
       </c>
@@ -24896,7 +25102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B109" s="12">
         <v>107</v>
       </c>
@@ -24921,7 +25127,9 @@
       <c r="I109" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J109" s="12"/>
+      <c r="J109" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K109" s="12">
         <v>1</v>
       </c>
@@ -24944,7 +25152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B110" s="12">
         <v>108</v>
       </c>
@@ -24967,7 +25175,9 @@
       <c r="I110" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J110" s="12"/>
+      <c r="J110" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K110" s="12">
         <v>1</v>
       </c>
@@ -24990,7 +25200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B111" s="12">
         <v>109</v>
       </c>
@@ -25015,7 +25225,9 @@
       <c r="I111" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="J111" s="12"/>
+      <c r="J111" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K111" s="12">
         <v>1</v>
       </c>
@@ -25038,7 +25250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B112" s="12">
         <v>110</v>
       </c>
@@ -25063,7 +25275,9 @@
       <c r="I112" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="J112" s="12"/>
+      <c r="J112" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K112" s="12">
         <v>1</v>
       </c>
@@ -25086,7 +25300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B113" s="12">
         <v>111</v>
       </c>
@@ -25111,7 +25325,9 @@
       <c r="I113" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J113" s="12"/>
+      <c r="J113" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K113" s="12">
         <v>1</v>
       </c>
@@ -25134,7 +25350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B114" s="12">
         <v>112</v>
       </c>
@@ -25159,7 +25375,9 @@
       <c r="I114" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="J114" s="12"/>
+      <c r="J114" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K114" s="12">
         <v>1</v>
       </c>
@@ -25182,7 +25400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B115" s="12">
         <v>113</v>
       </c>
@@ -25205,7 +25423,9 @@
       <c r="I115" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J115" s="12"/>
+      <c r="J115" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K115" s="12">
         <v>0</v>
       </c>
@@ -25228,7 +25448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B116" s="12">
         <v>114</v>
       </c>
@@ -25251,7 +25471,9 @@
       <c r="I116" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J116" s="12"/>
+      <c r="J116" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K116" s="12">
         <v>1</v>
       </c>
@@ -25274,7 +25496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B117" s="12">
         <v>115</v>
       </c>
@@ -25297,7 +25519,9 @@
       <c r="I117" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J117" s="12"/>
+      <c r="J117" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K117" s="12">
         <v>1</v>
       </c>
@@ -25320,7 +25544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B118" s="12">
         <v>116</v>
       </c>
@@ -25345,7 +25569,9 @@
       <c r="I118" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J118" s="12"/>
+      <c r="J118" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K118" s="12">
         <v>1</v>
       </c>
@@ -25368,7 +25594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B119" s="12">
         <v>117</v>
       </c>
@@ -25393,7 +25619,9 @@
       <c r="I119" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="J119" s="12"/>
+      <c r="J119" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K119" s="12">
         <v>1</v>
       </c>
@@ -25416,7 +25644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B120" s="12">
         <v>118</v>
       </c>
@@ -25441,7 +25669,9 @@
       <c r="I120" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="J120" s="12"/>
+      <c r="J120" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K120" s="12">
         <v>1</v>
       </c>
@@ -25464,7 +25694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B121" s="12">
         <v>119</v>
       </c>
@@ -25489,7 +25719,9 @@
       <c r="I121" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="J121" s="12"/>
+      <c r="J121" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K121" s="12">
         <v>1</v>
       </c>
@@ -25512,7 +25744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B122" s="12">
         <v>120</v>
       </c>
@@ -25533,7 +25765,9 @@
       <c r="I122" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J122" s="12"/>
+      <c r="J122" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K122" s="12">
         <v>1</v>
       </c>
@@ -25556,7 +25790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B123" s="12">
         <v>121</v>
       </c>
@@ -25581,7 +25815,9 @@
       <c r="I123" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="J123" s="12"/>
+      <c r="J123" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K123" s="12">
         <v>1</v>
       </c>
@@ -25604,7 +25840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B124" s="12">
         <v>122</v>
       </c>
@@ -25629,7 +25865,9 @@
       <c r="I124" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="J124" s="12"/>
+      <c r="J124" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K124" s="12">
         <v>1</v>
       </c>
@@ -25652,7 +25890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B125" s="12">
         <v>123</v>
       </c>
@@ -25673,7 +25911,9 @@
       <c r="I125" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J125" s="12"/>
+      <c r="J125" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K125" s="12">
         <v>1</v>
       </c>
@@ -25696,7 +25936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B126" s="12">
         <v>124</v>
       </c>
@@ -25721,7 +25961,9 @@
       <c r="I126" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="J126" s="12"/>
+      <c r="J126" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K126" s="12">
         <v>1</v>
       </c>
@@ -25744,7 +25986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B127" s="12">
         <v>125</v>
       </c>
@@ -25769,7 +26011,9 @@
       <c r="I127" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="J127" s="12"/>
+      <c r="J127" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K127" s="12">
         <v>1</v>
       </c>
@@ -25792,7 +26036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B128" s="12">
         <v>126</v>
       </c>
@@ -25817,7 +26061,9 @@
       <c r="I128" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J128" s="12"/>
+      <c r="J128" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K128" s="12">
         <v>1</v>
       </c>
@@ -25840,7 +26086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B129" s="12">
         <v>127</v>
       </c>
@@ -25865,7 +26111,9 @@
       <c r="I129" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="J129" s="12"/>
+      <c r="J129" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K129" s="12">
         <v>1</v>
       </c>
@@ -25888,7 +26136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B130" s="12">
         <v>128</v>
       </c>
@@ -25913,7 +26161,9 @@
       <c r="I130" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J130" s="12"/>
+      <c r="J130" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K130" s="12">
         <v>1</v>
       </c>
@@ -25936,7 +26186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B131" s="12">
         <v>129</v>
       </c>
@@ -25961,7 +26211,9 @@
       <c r="I131" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J131" s="12"/>
+      <c r="J131" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K131" s="12">
         <v>0</v>
       </c>
@@ -25984,7 +26236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B132" s="12">
         <v>130</v>
       </c>
@@ -26009,7 +26261,9 @@
       <c r="I132" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="J132" s="12"/>
+      <c r="J132" s="12" t="s">
+        <v>144</v>
+      </c>
       <c r="K132" s="12">
         <v>1</v>
       </c>
@@ -26032,7 +26286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B133" s="12">
         <v>131</v>
       </c>
@@ -26057,7 +26311,9 @@
       <c r="I133" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J133" s="12"/>
+      <c r="J133" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="K133" s="12">
         <v>1</v>
       </c>
@@ -26080,7 +26336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B134" s="12">
         <v>132</v>
       </c>
@@ -26105,7 +26361,9 @@
       <c r="I134" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="J134" s="12"/>
+      <c r="J134" s="12" t="s">
+        <v>100</v>
+      </c>
       <c r="K134" s="12">
         <v>1</v>
       </c>
@@ -26128,7 +26386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B135" s="12">
         <v>133</v>
       </c>
@@ -26153,7 +26411,9 @@
       <c r="I135" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="J135" s="12"/>
+      <c r="J135" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K135" s="12">
         <v>1</v>
       </c>
@@ -26176,7 +26436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B136" s="12">
         <v>134</v>
       </c>
@@ -26201,7 +26461,9 @@
       <c r="I136" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="J136" s="12"/>
+      <c r="J136" s="12" t="s">
+        <v>87</v>
+      </c>
       <c r="K136" s="12">
         <v>1</v>
       </c>
@@ -26224,7 +26486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B137" s="12">
         <v>135</v>
       </c>
@@ -26249,7 +26511,9 @@
       <c r="I137" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J137" s="12"/>
+      <c r="J137" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K137" s="12">
         <v>1</v>
       </c>
@@ -26272,7 +26536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B138" s="12">
         <v>136</v>
       </c>
@@ -26297,7 +26561,9 @@
       <c r="I138" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J138" s="12"/>
+      <c r="J138" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K138" s="12">
         <v>1</v>
       </c>
@@ -26320,7 +26586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B139" s="12">
         <v>137</v>
       </c>
@@ -26345,7 +26611,9 @@
       <c r="I139" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="J139" s="12"/>
+      <c r="J139" s="12" t="s">
+        <v>87</v>
+      </c>
       <c r="K139" s="12">
         <v>1</v>
       </c>
@@ -26368,7 +26636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B140" s="12">
         <v>138</v>
       </c>
@@ -26393,7 +26661,9 @@
       <c r="I140" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="J140" s="12"/>
+      <c r="J140" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="K140" s="12">
         <v>1</v>
       </c>
@@ -26416,7 +26686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B141" s="12">
         <v>139</v>
       </c>
@@ -26441,7 +26711,9 @@
       <c r="I141" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="J141" s="12"/>
+      <c r="J141" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K141" s="12">
         <v>0</v>
       </c>
@@ -26464,7 +26736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B142" s="12">
         <v>140</v>
       </c>
@@ -26489,7 +26761,9 @@
       <c r="I142" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="J142" s="12"/>
+      <c r="J142" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="K142" s="12">
         <v>1</v>
       </c>
@@ -26512,7 +26786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B143" s="12">
         <v>141</v>
       </c>
@@ -26537,7 +26811,9 @@
       <c r="I143" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J143" s="12"/>
+      <c r="J143" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="K143" s="12">
         <v>0</v>
       </c>
@@ -26560,7 +26836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B144" s="12">
         <v>142</v>
       </c>
@@ -26585,7 +26861,9 @@
       <c r="I144" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="J144" s="12"/>
+      <c r="J144" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K144" s="12">
         <v>0</v>
       </c>
@@ -26608,7 +26886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B145" s="12">
         <v>143</v>
       </c>
@@ -26633,7 +26911,9 @@
       <c r="I145" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J145" s="12"/>
+      <c r="J145" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="K145" s="12">
         <v>1</v>
       </c>
@@ -26656,7 +26936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B146" s="12">
         <v>144</v>
       </c>
@@ -26681,7 +26961,9 @@
       <c r="I146" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="J146" s="12"/>
+      <c r="J146" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="K146" s="12">
         <v>0</v>
       </c>
@@ -26704,7 +26986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B147" s="12">
         <v>145</v>
       </c>
@@ -26729,7 +27011,9 @@
       <c r="I147" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J147" s="12"/>
+      <c r="J147" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K147" s="12">
         <v>1</v>
       </c>
@@ -26752,7 +27036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B148" s="12">
         <v>146</v>
       </c>
@@ -26777,7 +27061,9 @@
       <c r="I148" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J148" s="12"/>
+      <c r="J148" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K148" s="12">
         <v>1</v>
       </c>
@@ -26800,7 +27086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B149" s="12">
         <v>147</v>
       </c>
@@ -26825,7 +27111,9 @@
       <c r="I149" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J149" s="12"/>
+      <c r="J149" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K149" s="12">
         <v>1</v>
       </c>
@@ -26848,7 +27136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B150" s="12">
         <v>148</v>
       </c>
@@ -26873,7 +27161,9 @@
       <c r="I150" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J150" s="12"/>
+      <c r="J150" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K150" s="12">
         <v>1</v>
       </c>
@@ -26896,7 +27186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B151" s="12">
         <v>149</v>
       </c>
@@ -26921,7 +27211,9 @@
       <c r="I151" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J151" s="12"/>
+      <c r="J151" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K151" s="12">
         <v>1</v>
       </c>
@@ -26944,7 +27236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B152" s="12">
         <v>150</v>
       </c>
@@ -26969,7 +27261,9 @@
       <c r="I152" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J152" s="12"/>
+      <c r="J152" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K152" s="12">
         <v>1</v>
       </c>
@@ -26992,7 +27286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B153" s="12">
         <v>151</v>
       </c>
@@ -27017,7 +27311,9 @@
       <c r="I153" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J153" s="12"/>
+      <c r="J153" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K153" s="12">
         <v>1</v>
       </c>
@@ -27040,7 +27336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B154" s="12">
         <v>152</v>
       </c>
@@ -27065,7 +27361,9 @@
       <c r="I154" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="J154" s="12"/>
+      <c r="J154" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K154" s="12">
         <v>1</v>
       </c>
@@ -27088,7 +27386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B155" s="12">
         <v>153</v>
       </c>
@@ -27113,7 +27411,9 @@
       <c r="I155" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J155" s="12"/>
+      <c r="J155" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K155" s="12">
         <v>1</v>
       </c>
@@ -27136,7 +27436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B156" s="12">
         <v>154</v>
       </c>
@@ -27161,7 +27461,9 @@
       <c r="I156" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J156" s="12"/>
+      <c r="J156" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="K156" s="12">
         <v>1</v>
       </c>
@@ -27184,7 +27486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B157" s="12">
         <v>155</v>
       </c>
@@ -27209,7 +27511,9 @@
       <c r="I157" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J157" s="12"/>
+      <c r="J157" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K157" s="12">
         <v>1</v>
       </c>
@@ -27232,7 +27536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B158" s="12">
         <v>156</v>
       </c>
@@ -27257,7 +27561,9 @@
       <c r="I158" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J158" s="12"/>
+      <c r="J158" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K158" s="12">
         <v>1</v>
       </c>
@@ -27280,7 +27586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B159" s="12">
         <v>157</v>
       </c>
@@ -27305,7 +27611,9 @@
       <c r="I159" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J159" s="12"/>
+      <c r="J159" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K159" s="12">
         <v>1</v>
       </c>
@@ -27328,7 +27636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B160" s="12">
         <v>158</v>
       </c>
@@ -27353,7 +27661,9 @@
       <c r="I160" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J160" s="12"/>
+      <c r="J160" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K160" s="12">
         <v>1</v>
       </c>
@@ -27401,7 +27711,9 @@
       <c r="I161" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J161" s="12"/>
+      <c r="J161" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="K161" s="12">
         <v>1</v>
       </c>
@@ -27424,7 +27736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B162" s="12">
         <v>160</v>
       </c>
@@ -27449,7 +27761,9 @@
       <c r="I162" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J162" s="12"/>
+      <c r="J162" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K162" s="12">
         <v>0</v>
       </c>
@@ -27472,7 +27786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B163" s="12">
         <v>161</v>
       </c>
@@ -27497,7 +27811,9 @@
       <c r="I163" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J163" s="12"/>
+      <c r="J163" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K163" s="12">
         <v>1</v>
       </c>
@@ -27520,7 +27836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B164" s="12">
         <v>162</v>
       </c>
@@ -27545,7 +27861,9 @@
       <c r="I164" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J164" s="12"/>
+      <c r="J164" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K164" s="12">
         <v>1</v>
       </c>
@@ -27568,7 +27886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B165" s="12">
         <v>163</v>
       </c>
@@ -27593,7 +27911,9 @@
       <c r="I165" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J165" s="12"/>
+      <c r="J165" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K165" s="12">
         <v>0</v>
       </c>
@@ -27616,7 +27936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B166" s="12">
         <v>164</v>
       </c>
@@ -27641,7 +27961,9 @@
       <c r="I166" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J166" s="12"/>
+      <c r="J166" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K166" s="12">
         <v>1</v>
       </c>
@@ -27664,7 +27986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B167" s="12">
         <v>165</v>
       </c>
@@ -27689,7 +28011,9 @@
       <c r="I167" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="J167" s="12"/>
+      <c r="J167" s="12" t="s">
+        <v>92</v>
+      </c>
       <c r="K167" s="12">
         <v>1</v>
       </c>
@@ -27712,7 +28036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B168" s="12">
         <v>166</v>
       </c>
@@ -27737,7 +28061,9 @@
       <c r="I168" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="J168" s="12"/>
+      <c r="J168" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K168" s="12">
         <v>1</v>
       </c>
@@ -27760,7 +28086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B169" s="12">
         <v>167</v>
       </c>
@@ -27785,7 +28111,9 @@
       <c r="I169" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J169" s="12"/>
+      <c r="J169" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K169" s="12">
         <v>1</v>
       </c>
@@ -27808,7 +28136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B170" s="12">
         <v>168</v>
       </c>
@@ -27833,7 +28161,9 @@
       <c r="I170" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J170" s="12"/>
+      <c r="J170" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K170" s="12">
         <v>1</v>
       </c>
@@ -27856,7 +28186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B171" s="12">
         <v>169</v>
       </c>
@@ -27881,7 +28211,9 @@
       <c r="I171" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J171" s="12"/>
+      <c r="J171" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K171" s="12">
         <v>1</v>
       </c>
@@ -27904,7 +28236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B172" s="12">
         <v>170</v>
       </c>
@@ -27929,7 +28261,9 @@
       <c r="I172" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J172" s="12"/>
+      <c r="J172" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K172" s="12">
         <v>1</v>
       </c>
@@ -27952,7 +28286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B173" s="12">
         <v>171</v>
       </c>
@@ -27977,7 +28311,9 @@
       <c r="I173" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J173" s="12"/>
+      <c r="J173" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="K173" s="12">
         <v>1</v>
       </c>
@@ -28000,7 +28336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B174" s="12">
         <v>172</v>
       </c>
@@ -28025,7 +28361,9 @@
       <c r="I174" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="J174" s="12"/>
+      <c r="J174" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="K174" s="12">
         <v>1</v>
       </c>
@@ -28048,7 +28386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B175" s="12">
         <v>173</v>
       </c>
@@ -28073,7 +28411,9 @@
       <c r="I175" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="J175" s="12"/>
+      <c r="J175" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="K175" s="12">
         <v>1</v>
       </c>
@@ -28096,7 +28436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B176" s="12">
         <v>174</v>
       </c>
@@ -28121,7 +28461,9 @@
       <c r="I176" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="J176" s="12"/>
+      <c r="J176" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="K176" s="12">
         <v>1</v>
       </c>
@@ -28144,7 +28486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B177" s="12">
         <v>175</v>
       </c>
@@ -28169,7 +28511,9 @@
       <c r="I177" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="J177" s="12"/>
+      <c r="J177" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="K177" s="12">
         <v>0</v>
       </c>
@@ -28192,7 +28536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B178" s="12">
         <v>176</v>
       </c>
@@ -28217,7 +28561,9 @@
       <c r="I178" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J178" s="12"/>
+      <c r="J178" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K178" s="12">
         <v>0</v>
       </c>
@@ -28240,7 +28586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B179" s="12">
         <v>177</v>
       </c>
@@ -28265,7 +28611,9 @@
       <c r="I179" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J179" s="12"/>
+      <c r="J179" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K179" s="12">
         <v>0</v>
       </c>
@@ -28288,7 +28636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B180" s="12">
         <v>178</v>
       </c>
@@ -28313,7 +28661,9 @@
       <c r="I180" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="J180" s="12"/>
+      <c r="J180" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="K180" s="12">
         <v>0</v>
       </c>
@@ -28336,7 +28686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B181" s="12">
         <v>179</v>
       </c>
@@ -28361,7 +28711,9 @@
       <c r="I181" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J181" s="12"/>
+      <c r="J181" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K181" s="12">
         <v>1</v>
       </c>
@@ -28384,7 +28736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B182" s="12">
         <v>180</v>
       </c>
@@ -28409,7 +28761,9 @@
       <c r="I182" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J182" s="12"/>
+      <c r="J182" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K182" s="12">
         <v>0</v>
       </c>
@@ -28432,7 +28786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B183" s="12">
         <v>181</v>
       </c>
@@ -28457,7 +28811,9 @@
       <c r="I183" s="12" t="s">
         <v>606</v>
       </c>
-      <c r="J183" s="12"/>
+      <c r="J183" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="K183" s="12">
         <v>0</v>
       </c>
@@ -28480,7 +28836,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B184" s="12">
         <v>182</v>
       </c>
@@ -28505,7 +28861,9 @@
       <c r="I184" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="J184" s="12"/>
+      <c r="J184" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="K184" s="12">
         <v>1</v>
       </c>
@@ -28528,7 +28886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B185" s="12">
         <v>183</v>
       </c>
@@ -28553,7 +28911,9 @@
       <c r="I185" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="J185" s="12"/>
+      <c r="J185" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K185" s="12">
         <v>1</v>
       </c>
@@ -28576,7 +28936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B186" s="12">
         <v>184</v>
       </c>
@@ -28601,7 +28961,9 @@
       <c r="I186" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J186" s="12"/>
+      <c r="J186" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K186" s="12">
         <v>0</v>
       </c>
@@ -28624,7 +28986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B187" s="12">
         <v>185</v>
       </c>
@@ -28649,7 +29011,9 @@
       <c r="I187" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J187" s="12"/>
+      <c r="J187" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K187" s="12">
         <v>1</v>
       </c>
@@ -28670,7 +29034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B188" s="12">
         <v>186</v>
       </c>
@@ -28695,7 +29059,9 @@
       <c r="I188" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J188" s="12"/>
+      <c r="J188" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K188" s="12">
         <v>0</v>
       </c>
@@ -28718,7 +29084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B189" s="12">
         <v>187</v>
       </c>
@@ -28743,7 +29109,9 @@
       <c r="I189" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J189" s="12"/>
+      <c r="J189" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K189" s="12">
         <v>0</v>
       </c>
@@ -28766,7 +29134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B190" s="12">
         <v>188</v>
       </c>
@@ -28791,7 +29159,9 @@
       <c r="I190" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="J190" s="12"/>
+      <c r="J190" s="12" t="s">
+        <v>144</v>
+      </c>
       <c r="K190" s="12">
         <v>1</v>
       </c>
@@ -28814,7 +29184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B191" s="12">
         <v>189</v>
       </c>
@@ -28839,7 +29209,9 @@
       <c r="I191" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="J191" s="12"/>
+      <c r="J191" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K191" s="12">
         <v>1</v>
       </c>
@@ -28862,7 +29234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B192" s="12">
         <v>190</v>
       </c>
@@ -28887,7 +29259,9 @@
       <c r="I192" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="J192" s="12"/>
+      <c r="J192" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K192" s="12">
         <v>0</v>
       </c>
@@ -28910,7 +29284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B193" s="12">
         <v>191</v>
       </c>
@@ -28935,7 +29309,9 @@
       <c r="I193" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J193" s="12"/>
+      <c r="J193" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K193" s="12">
         <v>1</v>
       </c>
@@ -28958,7 +29334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B194" s="12">
         <v>192</v>
       </c>
@@ -28983,7 +29359,9 @@
       <c r="I194" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J194" s="12"/>
+      <c r="J194" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="K194" s="12">
         <v>1</v>
       </c>
@@ -29006,7 +29384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B195" s="12">
         <v>193</v>
       </c>
@@ -29031,7 +29409,9 @@
       <c r="I195" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J195" s="12"/>
+      <c r="J195" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K195" s="12">
         <v>1</v>
       </c>
@@ -29054,7 +29434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B196" s="12">
         <v>194</v>
       </c>
@@ -29079,7 +29459,9 @@
       <c r="I196" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J196" s="12"/>
+      <c r="J196" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K196" s="12">
         <v>0</v>
       </c>
@@ -29102,7 +29484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B197" s="12">
         <v>195</v>
       </c>
@@ -29127,7 +29509,9 @@
       <c r="I197" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J197" s="12"/>
+      <c r="J197" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K197" s="12">
         <v>1</v>
       </c>
@@ -29150,7 +29534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B198" s="12">
         <v>196</v>
       </c>
@@ -29175,7 +29559,9 @@
       <c r="I198" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="J198" s="12"/>
+      <c r="J198" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="K198" s="12">
         <v>1</v>
       </c>
@@ -29198,7 +29584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B199" s="12">
         <v>197</v>
       </c>
@@ -29223,7 +29609,9 @@
       <c r="I199" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="J199" s="12"/>
+      <c r="J199" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="K199" s="12">
         <v>0</v>
       </c>
@@ -29246,7 +29634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B200" s="12">
         <v>198</v>
       </c>
@@ -29271,7 +29659,9 @@
       <c r="I200" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="J200" s="12"/>
+      <c r="J200" s="12" t="s">
+        <v>144</v>
+      </c>
       <c r="K200" s="12">
         <v>1</v>
       </c>
@@ -29294,7 +29684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B201" s="12">
         <v>199</v>
       </c>
@@ -29319,7 +29709,9 @@
       <c r="I201" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J201" s="12"/>
+      <c r="J201" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K201" s="12">
         <v>1</v>
       </c>
@@ -29342,7 +29734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B202" s="12">
         <v>200</v>
       </c>
@@ -29367,7 +29759,9 @@
       <c r="I202" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J202" s="12"/>
+      <c r="J202" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K202" s="12">
         <v>1</v>
       </c>
@@ -29390,7 +29784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B203" s="12">
         <v>201</v>
       </c>
@@ -29415,7 +29809,9 @@
       <c r="I203" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="J203" s="12"/>
+      <c r="J203" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K203" s="12">
         <v>1</v>
       </c>
@@ -29438,7 +29834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B204" s="12">
         <v>202</v>
       </c>
@@ -29463,7 +29859,9 @@
       <c r="I204" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J204" s="12"/>
+      <c r="J204" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K204" s="12">
         <v>1</v>
       </c>
@@ -29486,7 +29884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B205" s="12">
         <v>203</v>
       </c>
@@ -29511,7 +29909,9 @@
       <c r="I205" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="J205" s="12"/>
+      <c r="J205" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="K205" s="12">
         <v>1</v>
       </c>
@@ -29534,7 +29934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B206" s="12">
         <v>204</v>
       </c>
@@ -29559,7 +29959,9 @@
       <c r="I206" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J206" s="12"/>
+      <c r="J206" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K206" s="12">
         <v>0</v>
       </c>
@@ -29582,7 +29984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B207" s="12">
         <v>205</v>
       </c>
@@ -29607,7 +30009,9 @@
       <c r="I207" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="J207" s="12"/>
+      <c r="J207" s="12" t="s">
+        <v>89</v>
+      </c>
       <c r="K207" s="12">
         <v>1</v>
       </c>
@@ -29630,7 +30034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B208" s="12">
         <v>206</v>
       </c>
@@ -29655,7 +30059,9 @@
       <c r="I208" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J208" s="12"/>
+      <c r="J208" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K208" s="12">
         <v>0</v>
       </c>
@@ -29678,7 +30084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B209" s="12">
         <v>207</v>
       </c>
@@ -29703,7 +30109,9 @@
       <c r="I209" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="J209" s="12"/>
+      <c r="J209" s="12" t="s">
+        <v>138</v>
+      </c>
       <c r="K209" s="12">
         <v>1</v>
       </c>
@@ -29726,7 +30134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B210" s="12">
         <v>208</v>
       </c>
@@ -29751,7 +30159,9 @@
       <c r="I210" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="J210" s="12"/>
+      <c r="J210" s="12" t="s">
+        <v>138</v>
+      </c>
       <c r="K210" s="12">
         <v>1</v>
       </c>
@@ -29774,7 +30184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B211" s="12">
         <v>209</v>
       </c>
@@ -29799,7 +30209,9 @@
       <c r="I211" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="J211" s="12"/>
+      <c r="J211" s="12" t="s">
+        <v>138</v>
+      </c>
       <c r="K211" s="12">
         <v>1</v>
       </c>
@@ -29822,7 +30234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B212" s="12">
         <v>210</v>
       </c>
@@ -29847,7 +30259,9 @@
       <c r="I212" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="J212" s="12"/>
+      <c r="J212" s="12" t="s">
+        <v>144</v>
+      </c>
       <c r="K212" s="12">
         <v>1</v>
       </c>
@@ -29870,7 +30284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B213" s="12">
         <v>211</v>
       </c>
@@ -29895,7 +30309,9 @@
       <c r="I213" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J213" s="12"/>
+      <c r="J213" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="K213" s="12">
         <v>0</v>
       </c>
@@ -29918,7 +30334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B214" s="12">
         <v>212</v>
       </c>
@@ -29943,7 +30359,9 @@
       <c r="I214" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="J214" s="12"/>
+      <c r="J214" s="12" t="s">
+        <v>144</v>
+      </c>
       <c r="K214" s="12">
         <v>0</v>
       </c>
@@ -29966,7 +30384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B215" s="12">
         <v>213</v>
       </c>
@@ -29991,7 +30409,9 @@
       <c r="I215" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="J215" s="12"/>
+      <c r="J215" s="12" t="s">
+        <v>144</v>
+      </c>
       <c r="K215" s="12">
         <v>1</v>
       </c>
@@ -30014,7 +30434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B216" s="12">
         <v>214</v>
       </c>
@@ -30039,7 +30459,9 @@
       <c r="I216" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J216" s="12"/>
+      <c r="J216" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="K216" s="12">
         <v>1</v>
       </c>
@@ -30062,7 +30484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B217" s="12">
         <v>215</v>
       </c>
@@ -30087,7 +30509,9 @@
       <c r="I217" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J217" s="12"/>
+      <c r="J217" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="K217" s="12">
         <v>1</v>
       </c>
@@ -30110,7 +30534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B218" s="12">
         <v>216</v>
       </c>
@@ -30135,7 +30559,9 @@
       <c r="I218" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J218" s="12"/>
+      <c r="J218" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K218" s="12">
         <v>1</v>
       </c>
@@ -30156,7 +30582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B219" s="12">
         <v>217</v>
       </c>
@@ -30181,7 +30607,9 @@
       <c r="I219" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J219" s="12"/>
+      <c r="J219" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="K219" s="12">
         <v>0</v>
       </c>
@@ -30204,7 +30632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B220" s="12">
         <v>218</v>
       </c>
@@ -30229,7 +30657,9 @@
       <c r="I220" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="J220" s="12"/>
+      <c r="J220" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K220" s="12">
         <v>1</v>
       </c>
@@ -30252,7 +30682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B221" s="12">
         <v>219</v>
       </c>
@@ -30277,7 +30707,9 @@
       <c r="I221" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="J221" s="12"/>
+      <c r="J221" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="K221" s="12">
         <v>0</v>
       </c>
@@ -30300,7 +30732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B222" s="12">
         <v>220</v>
       </c>
@@ -30325,7 +30757,9 @@
       <c r="I222" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="J222" s="12"/>
+      <c r="J222" s="12" t="s">
+        <v>94</v>
+      </c>
       <c r="K222" s="12">
         <v>0</v>
       </c>
@@ -30348,7 +30782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B223" s="12">
         <v>221</v>
       </c>
@@ -30373,7 +30807,9 @@
       <c r="I223" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J223" s="12"/>
+      <c r="J223" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K223" s="12">
         <v>1</v>
       </c>
@@ -30396,7 +30832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B224" s="12">
         <v>222</v>
       </c>
@@ -30421,7 +30857,9 @@
       <c r="I224" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="J224" s="12"/>
+      <c r="J224" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="K224" s="12">
         <v>0</v>
       </c>
@@ -30444,7 +30882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B225" s="12">
         <v>223</v>
       </c>
@@ -30469,7 +30907,9 @@
       <c r="I225" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J225" s="12"/>
+      <c r="J225" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="K225" s="12">
         <v>0</v>
       </c>
@@ -30492,7 +30932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B226" s="12">
         <v>224</v>
       </c>
@@ -30517,7 +30957,9 @@
       <c r="I226" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J226" s="12"/>
+      <c r="J226" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="K226" s="12">
         <v>1</v>
       </c>
@@ -30540,7 +30982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="2:17" ht="17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="2:17" ht="17" x14ac:dyDescent="0.35">
       <c r="B227" s="12">
         <v>225</v>
       </c>
@@ -30565,7 +31007,9 @@
       <c r="I227" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J227" s="12"/>
+      <c r="J227" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="K227" s="12">
         <v>0</v>
       </c>
@@ -30590,12 +31034,15 @@
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H227" xr:uid="{D6B9FDF5-5DF8-4124-BBB2-1189797DB0D6}">
       <formula1>"الشرقية,الحدود الشمالية,حائل,تبوك,الجوف,الرياض,القصيم,المدينة المنورة,مكة المكرمة,الباحة,عسير,جازان,نجران"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G227" xr:uid="{0D086DC4-C253-4F2C-BC46-4D98516339D1}">
       <formula1>"نادي,أكاديمية,هواة"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J1048576" xr:uid="{C70771D5-DC31-46B8-9D72-41134C1DE4DD}">
+      <formula1>"الرياض,الخرج,الدوادمي,وادي الدواسر,الزلفي,شقراء,مكة المكرمة,الأحساء,القطيف,عسير,جدة,القصيم,الرس,الطائف,حائل,تبوك,الباحة,المدينة المنورة,جازان,نجران,المجمعة,الجوف,الحدود الشمالية,الشرقية,حفر الباطن"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -32513,6 +32960,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="16be648b-369d-4545-b3ec-980ea45f5768" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="892e9dcf-b510-48d2-a32f-1ed59fe9f3eb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AFBC82852503AF4EAB2EF5018DE9DEC7" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="eab508c9951ee695015998ff06a21af9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="892e9dcf-b510-48d2-a32f-1ed59fe9f3eb" xmlns:ns3="16be648b-369d-4545-b3ec-980ea45f5768" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="73c3eb72b85b8edb3d3b90476ca60681" ns2:_="" ns3:_="">
     <xsd:import namespace="892e9dcf-b510-48d2-a32f-1ed59fe9f3eb"/>
@@ -32713,17 +33171,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="16be648b-369d-4545-b3ec-980ea45f5768" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="892e9dcf-b510-48d2-a32f-1ed59fe9f3eb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A115B9C8-233C-43CA-A247-273FF172EBFC}">
   <ds:schemaRefs>
@@ -32733,6 +33180,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FAA5E74-1211-482A-8855-78EF88D8B1E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="16be648b-369d-4545-b3ec-980ea45f5768"/>
+    <ds:schemaRef ds:uri="892e9dcf-b510-48d2-a32f-1ed59fe9f3eb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D063081C-01A5-4A80-B507-73DEE5C9C0AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32749,15 +33207,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FAA5E74-1211-482A-8855-78EF88D8B1E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="16be648b-369d-4545-b3ec-980ea45f5768"/>
-    <ds:schemaRef ds:uri="892e9dcf-b510-48d2-a32f-1ed59fe9f3eb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/cluster_analysis/latest.xlsx
+++ b/cluster_analysis/latest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://creativeartistsagencygbr.sharepoint.com/sites/NFSIMPLEMENTATIONSAFF/Shared Documents/04 Deliverables WIP/SAFF 2025 Plan/Competitions restructure/Analysis/Clubs Gap Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="312" documentId="13_ncr:1_{973241F7-B0A8-4B0E-9B8D-D4C79E1A4082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B015C482-CA87-4520-9DB4-9750795B1568}"/>
+  <xr:revisionPtr revIDLastSave="400" documentId="13_ncr:1_{973241F7-B0A8-4B0E-9B8D-D4C79E1A4082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A62AF2AB-40D2-4EC3-A171-FA0674699AD7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{696254E1-FDC9-4707-85DD-EE834AB8F841}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{696254E1-FDC9-4707-85DD-EE834AB8F841}"/>
   </bookViews>
   <sheets>
     <sheet name="ملخص المجموعات" sheetId="4" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="المدخلات" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'بيانات التسجيل'!$G$2:$Q$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'بيانات التسجيل'!$G$2:$Q$246</definedName>
     <definedName name="الحد_الأدنى">المدخلات!$I$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3826" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3968" uniqueCount="746">
   <si>
     <t>المجموعة</t>
   </si>
@@ -2189,6 +2189,123 @@
   </si>
   <si>
     <t>مكتب الوزارة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الصحراء الرياضية </t>
+  </si>
+  <si>
+    <t>نايف الغامدي</t>
+  </si>
+  <si>
+    <t>المدينة الرياضية بالباحة</t>
+  </si>
+  <si>
+    <t>تيم قول</t>
+  </si>
+  <si>
+    <t>محمد الغامدي</t>
+  </si>
+  <si>
+    <t>ليدرز هاوس</t>
+  </si>
+  <si>
+    <t>ابراهيم الحسيكا</t>
+  </si>
+  <si>
+    <t>الجوهرة المتحدة</t>
+  </si>
+  <si>
+    <t>عيسى المعلوي</t>
+  </si>
+  <si>
+    <t>الهدى</t>
+  </si>
+  <si>
+    <t>ابراهيم بوسرور</t>
+  </si>
+  <si>
+    <t>الجوهرية</t>
+  </si>
+  <si>
+    <t>عبدالعزيزالياسين</t>
+  </si>
+  <si>
+    <t>تضامن القنفذة بالقوز</t>
+  </si>
+  <si>
+    <t>خالد الفقيه</t>
+  </si>
+  <si>
+    <t>السوق بالقحمة</t>
+  </si>
+  <si>
+    <t>موسى الشقيقي</t>
+  </si>
+  <si>
+    <t>البرك</t>
+  </si>
+  <si>
+    <t>عبدالخالق الغبيشي</t>
+  </si>
+  <si>
+    <t>العقيد</t>
+  </si>
+  <si>
+    <t>رامي جحيلان</t>
+  </si>
+  <si>
+    <t>نادي الشعاع الرياضي</t>
+  </si>
+  <si>
+    <t>مديني الزيادي</t>
+  </si>
+  <si>
+    <t>الطموح</t>
+  </si>
+  <si>
+    <t>احمد المنتشري</t>
+  </si>
+  <si>
+    <t>التعاون الذهبي</t>
+  </si>
+  <si>
+    <t>هتان علي هتان</t>
+  </si>
+  <si>
+    <t>اكاديمية عز تن</t>
+  </si>
+  <si>
+    <t>احمد الرفيدي</t>
+  </si>
+  <si>
+    <t>اكاديمية بيتيس تبوك</t>
+  </si>
+  <si>
+    <t>عبدالرحمن العنزي</t>
+  </si>
+  <si>
+    <t>البداية الاولمبية</t>
+  </si>
+  <si>
+    <t>هاني الخزاعي</t>
+  </si>
+  <si>
+    <t>الاتحاد هواة</t>
+  </si>
+  <si>
+    <t>عبدالله حجي</t>
+  </si>
+  <si>
+    <t>الكوماندوز</t>
+  </si>
+  <si>
+    <t>عبدالرحمن الحارثي</t>
+  </si>
+  <si>
+    <t>اكاديمية موهبة نعجان</t>
+  </si>
+  <si>
+    <t>ابراهيم المنيف</t>
   </si>
 </sst>
 </file>
@@ -2258,7 +2375,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2277,8 +2394,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -2330,12 +2453,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2376,6 +2512,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2403,6 +2554,160 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3104,160 +3409,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3276,21 +3427,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D5714613-7CB3-4778-9CFB-5F2E956CE80E}" name="ملخص_المجموعات" displayName="ملخص_المجموعات" ref="B2:G271" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D5714613-7CB3-4778-9CFB-5F2E956CE80E}" name="ملخص_المجموعات" displayName="ملخص_المجموعات" ref="B2:G271" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
   <autoFilter ref="B2:G271" xr:uid="{D5714613-7CB3-4778-9CFB-5F2E956CE80E}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{21357364-A1AC-40A0-A103-719BBF35D23E}" name="الفئة" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{FED87C10-4531-4310-A0AB-63BF8FB11944}" name="المجموعة" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{AE4FCF05-32B9-4C29-8A35-872FE1B3A005}" name="عدد المدن" dataDxfId="30">
+    <tableColumn id="1" xr3:uid="{21357364-A1AC-40A0-A103-719BBF35D23E}" name="الفئة" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{FED87C10-4531-4310-A0AB-63BF8FB11944}" name="المجموعة" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{AE4FCF05-32B9-4C29-8A35-872FE1B3A005}" name="عدد المدن" dataDxfId="21">
       <calculatedColumnFormula>COUNTIFS(تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{FD58C7EE-75CB-499E-85CF-7282CB19CA62}" name="المدن" dataDxfId="29">
+    <tableColumn id="6" xr3:uid="{FD58C7EE-75CB-499E-85CF-7282CB19CA62}" name="المدن" dataDxfId="20">
       <calculatedColumnFormula array="1">_xlfn.TEXTJOIN("، ",TRUE,IF((تفاصيل_الفرق[الفئة العمرية]=ملخص_المجموعات[[#This Row],[الفئة]])*(تفاصيل_الفرق[المجموعة]=ملخص_المجموعات[[#This Row],[المجموعة]]),تفاصيل_الفرق[المدينة/المحافظة],""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EB7BF368-B482-4173-985E-A61BA4F4C980}" name="مجموع الفرق" dataDxfId="28">
+    <tableColumn id="4" xr3:uid="{EB7BF368-B482-4173-985E-A61BA4F4C980}" name="مجموع الفرق" dataDxfId="19">
       <calculatedColumnFormula>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B4DAD3B8-5E7E-481E-B3FC-6B7F1675A2AC}" name="المتبقي" dataDxfId="27">
+    <tableColumn id="5" xr3:uid="{B4DAD3B8-5E7E-481E-B3FC-6B7F1675A2AC}" name="المتبقي" dataDxfId="18">
       <calculatedColumnFormula>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3299,15 +3450,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C701D678-71F0-44FF-ADB2-214FC277166A}" name="تفاصيل_الفرق" displayName="تفاصيل_الفرق" ref="B2:E580" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
-  <autoFilter ref="B2:E580" xr:uid="{C701D678-71F0-44FF-ADB2-214FC277166A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C701D678-71F0-44FF-ADB2-214FC277166A}" name="تفاصيل_الفرق" displayName="تفاصيل_الفرق" ref="B2:E583" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="B2:E583" xr:uid="{C701D678-71F0-44FF-ADB2-214FC277166A}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BA3E5021-A230-4D22-874F-F4F2E40E742F}" name="الفئة العمرية" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{125018BC-E7FF-461A-A50D-47C8428F3CCC}" name="المدينة/المحافظة" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{CB78D930-6811-46BE-9E54-828AD86943E6}" name="المجموعة" dataDxfId="22">
+    <tableColumn id="1" xr3:uid="{BA3E5021-A230-4D22-874F-F4F2E40E742F}" name="الفئة العمرية" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{125018BC-E7FF-461A-A50D-47C8428F3CCC}" name="المدينة/المحافظة" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{CB78D930-6811-46BE-9E54-828AD86943E6}" name="المجموعة" dataDxfId="13">
       <calculatedColumnFormula array="1">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EF5C574A-EDBE-4210-9614-DB0BF5439C78}" name="عدد الفرق" dataDxfId="21">
+    <tableColumn id="4" xr3:uid="{EF5C574A-EDBE-4210-9614-DB0BF5439C78}" name="عدد الفرق" dataDxfId="12">
       <calculatedColumnFormula array="1">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3316,51 +3467,51 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C98C69F7-A5A5-41A9-9F9D-AF91B174B3C2}" name="التسجيل" displayName="التسجيل" ref="B2:Q227" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18" dataCellStyle="Normal 2">
-  <autoFilter ref="B2:Q227" xr:uid="{C98C69F7-A5A5-41A9-9F9D-AF91B174B3C2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C98C69F7-A5A5-41A9-9F9D-AF91B174B3C2}" name="التسجيل" displayName="التسجيل" ref="B2:Q246" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" tableBorderDxfId="42" dataCellStyle="Normal 2">
+  <autoFilter ref="B2:Q246" xr:uid="{C98C69F7-A5A5-41A9-9F9D-AF91B174B3C2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:Q227">
     <sortCondition ref="B2:B227"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{090AD518-161E-48A1-BB46-837D6EA74252}" name="Entry Id" dataDxfId="17" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{AC3FCE35-ED74-4BDA-B2C1-71DE81164517}" name="اسم الفريق" dataDxfId="16" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{BAB92966-1EB1-4C4A-A003-A8F57A08F900}" name="الاسم " dataDxfId="15" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{41B901FC-6026-4BE2-A9C0-4BA71B6BC5DE}" name="رقم الجوال" dataDxfId="14" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{9F68BE70-1FDC-4425-9940-DF2CEFD9B032}" name="اسم الملعب" dataDxfId="13" dataCellStyle="Normal 2"/>
-    <tableColumn id="6" xr3:uid="{0BB31EF5-FF5E-497E-95C0-AC1316951F24}" name="الصفة" dataDxfId="12" dataCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{50DE72A8-1E19-4962-9931-E2D97E6E6125}" name="المنطقة" dataDxfId="11" dataCellStyle="Normal 2"/>
-    <tableColumn id="8" xr3:uid="{0A336E9A-961E-4220-ADF7-AB5BC3EFC496}" name="المدينة" dataDxfId="10" dataCellStyle="Normal 2"/>
-    <tableColumn id="17" xr3:uid="{9A1E561B-D0E7-4011-9527-4DE3A58FAD08}" name="مكتب الوزارة" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{313DDC39-AC82-48CC-BCED-A8D8B0B50F10}" name="المشاركة تحت 14" dataDxfId="8" dataCellStyle="Normal 2"/>
-    <tableColumn id="10" xr3:uid="{056EB01F-9295-4034-859B-42056695639E}" name="المشاركة تحت 13" dataDxfId="7" dataCellStyle="Normal 2"/>
-    <tableColumn id="11" xr3:uid="{0A942E27-C19C-4583-B65B-63FA254B3871}" name="المشاركة تحت 12" dataDxfId="6" dataCellStyle="Normal 2"/>
-    <tableColumn id="12" xr3:uid="{4FD6226C-F925-47F1-A13D-AA249B8D9FD0}" name="المشاركة تحت 11" dataDxfId="5" dataCellStyle="Normal 2"/>
-    <tableColumn id="13" xr3:uid="{7C0BB045-F917-4504-A7B2-0720DBB4DE2F}" name="المشاركة تحت 9" dataDxfId="4" dataCellStyle="Normal 2"/>
-    <tableColumn id="14" xr3:uid="{FD475FF4-5023-4EA1-B10C-9DE555315DBC}" name="المشاركة تحت 7 " dataDxfId="3" dataCellStyle="Normal 2"/>
-    <tableColumn id="15" xr3:uid="{43B89F76-F8D8-491F-B6E6-05BED7569326}" name="المشاركة تحت 5" dataDxfId="2" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{090AD518-161E-48A1-BB46-837D6EA74252}" name="Entry Id" dataDxfId="41" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{AC3FCE35-ED74-4BDA-B2C1-71DE81164517}" name="اسم الفريق" dataDxfId="40" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{BAB92966-1EB1-4C4A-A003-A8F57A08F900}" name="الاسم " dataDxfId="39" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{41B901FC-6026-4BE2-A9C0-4BA71B6BC5DE}" name="رقم الجوال" dataDxfId="38" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{9F68BE70-1FDC-4425-9940-DF2CEFD9B032}" name="اسم الملعب" dataDxfId="37" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{0BB31EF5-FF5E-497E-95C0-AC1316951F24}" name="الصفة" dataDxfId="36" dataCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{50DE72A8-1E19-4962-9931-E2D97E6E6125}" name="المنطقة" dataDxfId="35" dataCellStyle="Normal 2"/>
+    <tableColumn id="8" xr3:uid="{0A336E9A-961E-4220-ADF7-AB5BC3EFC496}" name="المدينة" dataDxfId="34" dataCellStyle="Normal 2"/>
+    <tableColumn id="17" xr3:uid="{9A1E561B-D0E7-4011-9527-4DE3A58FAD08}" name="مكتب الوزارة" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{313DDC39-AC82-48CC-BCED-A8D8B0B50F10}" name="المشاركة تحت 14" dataDxfId="32" dataCellStyle="Normal 2"/>
+    <tableColumn id="10" xr3:uid="{056EB01F-9295-4034-859B-42056695639E}" name="المشاركة تحت 13" dataDxfId="31" dataCellStyle="Normal 2"/>
+    <tableColumn id="11" xr3:uid="{0A942E27-C19C-4583-B65B-63FA254B3871}" name="المشاركة تحت 12" dataDxfId="30" dataCellStyle="Normal 2"/>
+    <tableColumn id="12" xr3:uid="{4FD6226C-F925-47F1-A13D-AA249B8D9FD0}" name="المشاركة تحت 11" dataDxfId="29" dataCellStyle="Normal 2"/>
+    <tableColumn id="13" xr3:uid="{7C0BB045-F917-4504-A7B2-0720DBB4DE2F}" name="المشاركة تحت 9" dataDxfId="28" dataCellStyle="Normal 2"/>
+    <tableColumn id="14" xr3:uid="{FD475FF4-5023-4EA1-B10C-9DE555315DBC}" name="المشاركة تحت 7 " dataDxfId="27" dataCellStyle="Normal 2"/>
+    <tableColumn id="15" xr3:uid="{43B89F76-F8D8-491F-B6E6-05BED7569326}" name="المشاركة تحت 5" dataDxfId="26" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CB8954BF-907E-4B78-AA0B-B695FCB5D5AC}" name="ربط_الفئات" displayName="ربط_الفئات" ref="F2:G9" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" tableBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CB8954BF-907E-4B78-AA0B-B695FCB5D5AC}" name="ربط_الفئات" displayName="ربط_الفئات" ref="F2:G9" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" tableBorderDxfId="9">
   <autoFilter ref="F2:G9" xr:uid="{CB8954BF-907E-4B78-AA0B-B695FCB5D5AC}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{30FFDE77-56F6-44C2-B6A6-155DCF4CF8DB}" name="الفئة" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{86DFE088-41CB-49A5-A5FE-6AC945BFCDB8}" name="مجموعة الفئات" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{30FFDE77-56F6-44C2-B6A6-155DCF4CF8DB}" name="الفئة" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{86DFE088-41CB-49A5-A5FE-6AC945BFCDB8}" name="مجموعة الفئات" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C0D9CA94-7B1D-4BB6-9D8F-BBAF4BDFA449}" name="المدن_المصدر" displayName="المدن_المصدر" ref="B2:D166" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
-  <autoFilter ref="B2:D166" xr:uid="{C0D9CA94-7B1D-4BB6-9D8F-BBAF4BDFA449}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C0D9CA94-7B1D-4BB6-9D8F-BBAF4BDFA449}" name="المدن_المصدر" displayName="المدن_المصدر" ref="B2:D167" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="B2:D167" xr:uid="{C0D9CA94-7B1D-4BB6-9D8F-BBAF4BDFA449}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{230C2C42-A057-407F-B36C-357E7EDD9E62}" name="الفئة العمرية" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{DA75C6C1-EEE2-478C-AB61-D44245FEF7F3}" name="المجموعة" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{6A5033B9-28EA-44F9-A1C0-ACDB72370A69}" name="المدينة/المحافظة" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{230C2C42-A057-407F-B36C-357E7EDD9E62}" name="الفئة العمرية" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{DA75C6C1-EEE2-478C-AB61-D44245FEF7F3}" name="المجموعة" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{6A5033B9-28EA-44F9-A1C0-ACDB72370A69}" name="المدينة/المحافظة" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3683,7 +3834,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="924" row="1">
+  <wetp:taskpane dockstate="right" visibility="0" width="941" row="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -3845,11 +3996,11 @@
       </c>
       <c r="D7" s="1">
         <f>COUNTIFS(تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="5" t="str" cm="1">
         <f t="array" ref="E7">_xlfn.TEXTJOIN("، ",TRUE,IF((تفاصيل_الفرق[الفئة العمرية]=ملخص_المجموعات[[#This Row],[الفئة]])*(تفاصيل_الفرق[المجموعة]=ملخص_المجموعات[[#This Row],[المجموعة]]),تفاصيل_الفرق[المدينة/المحافظة],""))</f>
-        <v>الباحة، بلجرشي</v>
+        <v>الباحة، العقيق، بلجرشي</v>
       </c>
       <c r="F7" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
@@ -4213,11 +4364,11 @@
       </c>
       <c r="F22" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.35">
@@ -4501,7 +4652,7 @@
       </c>
       <c r="F34" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G34" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -5069,11 +5220,11 @@
       </c>
       <c r="D58" s="1">
         <f>COUNTIFS(تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" s="5" t="str" cm="1">
         <f t="array" ref="E58">_xlfn.TEXTJOIN("، ",TRUE,IF((تفاصيل_الفرق[الفئة العمرية]=ملخص_المجموعات[[#This Row],[الفئة]])*(تفاصيل_الفرق[المجموعة]=ملخص_المجموعات[[#This Row],[المجموعة]]),تفاصيل_الفرق[المدينة/المحافظة],""))</f>
-        <v>الباحة، بلجرشي</v>
+        <v>الباحة، العقيق، بلجرشي</v>
       </c>
       <c r="F58" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
@@ -5437,11 +5588,11 @@
       </c>
       <c r="F73" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G73" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.35">
@@ -5677,11 +5828,11 @@
       </c>
       <c r="F83" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.35">
@@ -5725,7 +5876,7 @@
       </c>
       <c r="F85" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G85" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -6293,19 +6444,19 @@
       </c>
       <c r="D109" s="1">
         <f>COUNTIFS(تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E109" s="5" t="str" cm="1">
         <f t="array" ref="E109">_xlfn.TEXTJOIN("، ",TRUE,IF((تفاصيل_الفرق[الفئة العمرية]=ملخص_المجموعات[[#This Row],[الفئة]])*(تفاصيل_الفرق[المجموعة]=ملخص_المجموعات[[#This Row],[المجموعة]]),تفاصيل_الفرق[المدينة/المحافظة],""))</f>
-        <v>الباحة، بلجرشي</v>
+        <v>الباحة، العقيق، بلجرشي</v>
       </c>
       <c r="F109" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G109" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.35">
@@ -6373,11 +6524,11 @@
       </c>
       <c r="F112" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G112" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.35">
@@ -6661,11 +6812,11 @@
       </c>
       <c r="F124" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G124" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="2:7" x14ac:dyDescent="0.35">
@@ -6901,11 +7052,11 @@
       </c>
       <c r="F134" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="2:7" x14ac:dyDescent="0.35">
@@ -6949,7 +7100,7 @@
       </c>
       <c r="F136" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G136" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -7477,7 +7628,7 @@
       </c>
       <c r="F158" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G158" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -7669,7 +7820,7 @@
       </c>
       <c r="F166" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G166" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -7693,7 +7844,7 @@
       </c>
       <c r="F167" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G167" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -7741,11 +7892,11 @@
       </c>
       <c r="F169" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G169" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="2:7" x14ac:dyDescent="0.35">
@@ -7837,11 +7988,11 @@
       </c>
       <c r="F173" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G173" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174" spans="2:7" x14ac:dyDescent="0.35">
@@ -7885,11 +8036,11 @@
       </c>
       <c r="F175" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G175" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="2:7" x14ac:dyDescent="0.35">
@@ -7933,7 +8084,7 @@
       </c>
       <c r="F177" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G177" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -8197,11 +8348,11 @@
       </c>
       <c r="F188" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G188" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="2:7" x14ac:dyDescent="0.35">
@@ -8317,7 +8468,7 @@
       </c>
       <c r="F193" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G193" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -8365,7 +8516,7 @@
       </c>
       <c r="F195" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G195" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -8389,7 +8540,7 @@
       </c>
       <c r="F196" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G196" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -8413,7 +8564,7 @@
       </c>
       <c r="F197" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G197" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -8437,11 +8588,11 @@
       </c>
       <c r="F198" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G198" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="2:7" x14ac:dyDescent="0.35">
@@ -8485,7 +8636,7 @@
       </c>
       <c r="F200" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G200" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -8533,11 +8684,11 @@
       </c>
       <c r="F202" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G202" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="203" spans="2:7" x14ac:dyDescent="0.35">
@@ -8581,11 +8732,11 @@
       </c>
       <c r="F204" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G204" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="2:7" x14ac:dyDescent="0.35">
@@ -8629,7 +8780,7 @@
       </c>
       <c r="F206" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G206" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -8869,7 +9020,7 @@
       </c>
       <c r="F216" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G216" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -8893,11 +9044,11 @@
       </c>
       <c r="F217" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G217" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="218" spans="2:7" x14ac:dyDescent="0.35">
@@ -9061,7 +9212,7 @@
       </c>
       <c r="F224" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G224" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -9109,11 +9260,11 @@
       </c>
       <c r="F226" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G226" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227" spans="2:7" x14ac:dyDescent="0.35">
@@ -9133,11 +9284,11 @@
       </c>
       <c r="F227" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G227" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228" spans="2:7" x14ac:dyDescent="0.35">
@@ -9229,11 +9380,11 @@
       </c>
       <c r="F231" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G231" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="232" spans="2:7" x14ac:dyDescent="0.35">
@@ -9277,11 +9428,11 @@
       </c>
       <c r="F233" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G233" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="234" spans="2:7" x14ac:dyDescent="0.35">
@@ -9325,7 +9476,7 @@
       </c>
       <c r="F235" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G235" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -9589,11 +9740,11 @@
       </c>
       <c r="F246" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G246" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="2:7" x14ac:dyDescent="0.35">
@@ -9805,11 +9956,11 @@
       </c>
       <c r="F255" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G255" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256" spans="2:7" x14ac:dyDescent="0.35">
@@ -9829,11 +9980,11 @@
       </c>
       <c r="F256" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G256" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="2:7" x14ac:dyDescent="0.35">
@@ -9877,11 +10028,11 @@
       </c>
       <c r="F258" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G258" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="2:7" x14ac:dyDescent="0.35">
@@ -9925,11 +10076,11 @@
       </c>
       <c r="F260" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G260" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="261" spans="2:7" x14ac:dyDescent="0.35">
@@ -9973,11 +10124,11 @@
       </c>
       <c r="F262" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G262" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="263" spans="2:7" x14ac:dyDescent="0.35">
@@ -9997,7 +10148,7 @@
       </c>
       <c r="F263" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G263" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -10021,7 +10172,7 @@
       </c>
       <c r="F264" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G264" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -10141,7 +10292,7 @@
       </c>
       <c r="F269" s="1">
         <f>SUMIFS(تفاصيل_الفرق[عدد الفرق],تفاصيل_الفرق[الفئة العمرية],ملخص_المجموعات[[#This Row],[الفئة]],تفاصيل_الفرق[المجموعة],ملخص_المجموعات[[#This Row],[المجموعة]])</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G269" s="1">
         <f>MAX(0,الحد_الأدنى-ملخص_المجموعات[[#This Row],[مجموع الفرق]])</f>
@@ -10243,7 +10394,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E314F1D-8FB9-4A6C-9518-3732E171E21C}">
-  <dimension ref="B2:E580"/>
+  <dimension ref="B2:E583"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="6"/>
@@ -10489,7 +10640,7 @@
       </c>
       <c r="E16" s="2" cm="1">
         <f t="array" ref="E16">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.35">
@@ -10777,7 +10928,7 @@
       </c>
       <c r="E34" s="2" cm="1">
         <f t="array" ref="E34">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.35">
@@ -10809,7 +10960,7 @@
       </c>
       <c r="E36" s="2" cm="1">
         <f t="array" ref="E36">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.35">
@@ -10985,7 +11136,7 @@
       </c>
       <c r="E47" s="2" cm="1">
         <f t="array" ref="E47">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.35">
@@ -11033,7 +11184,7 @@
       </c>
       <c r="E50" s="2" cm="1">
         <f t="array" ref="E50">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.35">
@@ -11049,7 +11200,7 @@
       </c>
       <c r="E51" s="2" cm="1">
         <f t="array" ref="E51">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.35">
@@ -12649,7 +12800,7 @@
       </c>
       <c r="E151" s="2" cm="1">
         <f t="array" ref="E151">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.35">
@@ -12857,7 +13008,7 @@
       </c>
       <c r="E164" s="2" cm="1">
         <f t="array" ref="E164">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.35">
@@ -12873,7 +13024,7 @@
       </c>
       <c r="E165" s="2" cm="1">
         <f t="array" ref="E165">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.35">
@@ -12889,7 +13040,7 @@
       </c>
       <c r="E166" s="2" cm="1">
         <f t="array" ref="E166">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.35">
@@ -13022,7 +13173,7 @@
     </row>
     <row r="175" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B175" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>104</v>
@@ -13038,7 +13189,7 @@
     </row>
     <row r="176" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B176" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>104</v>
@@ -13054,7 +13205,7 @@
     </row>
     <row r="177" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B177" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>104</v>
@@ -13065,12 +13216,12 @@
       </c>
       <c r="E177" s="2" cm="1">
         <f t="array" ref="E177">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B178" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>104</v>
@@ -13086,46 +13237,46 @@
     </row>
     <row r="179" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B179" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="D179" s="6" t="str" cm="1">
         <f t="array" ref="D179">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة صبيا</v>
+        <v>مجموعة الباحة</v>
       </c>
       <c r="E179" s="2" cm="1">
         <f t="array" ref="E179">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B180" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="D180" s="6" t="str" cm="1">
         <f t="array" ref="D180">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة صبيا</v>
+        <v>مجموعة الباحة</v>
       </c>
       <c r="E180" s="2" cm="1">
         <f t="array" ref="E180">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B181" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="D181" s="6" t="str" cm="1">
         <f t="array" ref="D181">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة صبيا</v>
+        <v>مجموعة الباحة</v>
       </c>
       <c r="E181" s="2" cm="1">
         <f t="array" ref="E181">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13134,14 +13285,14 @@
     </row>
     <row r="182" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B182" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>137</v>
       </c>
       <c r="D182" s="6" t="str" cm="1">
         <f t="array" ref="D182">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جازان</v>
+        <v>مجموعة صبيا</v>
       </c>
       <c r="E182" s="2" cm="1">
         <f t="array" ref="E182">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13150,14 +13301,14 @@
     </row>
     <row r="183" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B183" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>137</v>
       </c>
       <c r="D183" s="6" t="str" cm="1">
         <f t="array" ref="D183">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جازان</v>
+        <v>مجموعة صبيا</v>
       </c>
       <c r="E183" s="2" cm="1">
         <f t="array" ref="E183">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13166,14 +13317,14 @@
     </row>
     <row r="184" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B184" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>137</v>
       </c>
       <c r="D184" s="6" t="str" cm="1">
         <f t="array" ref="D184">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جازان</v>
+        <v>مجموعة صبيا</v>
       </c>
       <c r="E184" s="2" cm="1">
         <f t="array" ref="E184">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13182,7 +13333,7 @@
     </row>
     <row r="185" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B185" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>137</v>
@@ -13198,14 +13349,14 @@
     </row>
     <row r="186" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B186" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D186" s="6" t="str" cm="1">
         <f t="array" ref="D186">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المجمعة</v>
+        <v>مجموعة جازان</v>
       </c>
       <c r="E186" s="2" cm="1">
         <f t="array" ref="E186">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13214,14 +13365,14 @@
     </row>
     <row r="187" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B187" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D187" s="6" t="str" cm="1">
         <f t="array" ref="D187">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المجمعة</v>
+        <v>مجموعة جازان</v>
       </c>
       <c r="E187" s="2" cm="1">
         <f t="array" ref="E187">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13230,14 +13381,14 @@
     </row>
     <row r="188" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B188" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D188" s="6" t="str" cm="1">
         <f t="array" ref="D188">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المجمعة</v>
+        <v>مجموعة جازان</v>
       </c>
       <c r="E188" s="2" cm="1">
         <f t="array" ref="E188">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13246,7 +13397,7 @@
     </row>
     <row r="189" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B189" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>131</v>
@@ -13262,7 +13413,7 @@
     </row>
     <row r="190" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B190" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>131</v>
@@ -13273,12 +13424,12 @@
       </c>
       <c r="E190" s="2" cm="1">
         <f t="array" ref="E190">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B191" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>131</v>
@@ -13294,7 +13445,7 @@
     </row>
     <row r="192" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B192" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>131</v>
@@ -13310,55 +13461,55 @@
     </row>
     <row r="193" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B193" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="D193" s="6" t="str" cm="1">
         <f t="array" ref="D193">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القطيف</v>
+        <v>مجموعة المجمعة</v>
       </c>
       <c r="E193" s="2" cm="1">
         <f t="array" ref="E193">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B194" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="D194" s="6" t="str" cm="1">
         <f t="array" ref="D194">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القطيف</v>
+        <v>مجموعة المجمعة</v>
       </c>
       <c r="E194" s="2" cm="1">
         <f t="array" ref="E194">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B195" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="D195" s="6" t="str" cm="1">
         <f t="array" ref="D195">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القطيف</v>
+        <v>مجموعة المجمعة</v>
       </c>
       <c r="E195" s="2" cm="1">
         <f t="array" ref="E195">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B196" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>98</v>
@@ -13369,12 +13520,12 @@
       </c>
       <c r="E196" s="2" cm="1">
         <f t="array" ref="E196">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B197" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>98</v>
@@ -13385,12 +13536,12 @@
       </c>
       <c r="E197" s="2" cm="1">
         <f t="array" ref="E197">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B198" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>98</v>
@@ -13401,12 +13552,12 @@
       </c>
       <c r="E198" s="2" cm="1">
         <f t="array" ref="E198">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="199" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B199" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>98</v>
@@ -13417,60 +13568,60 @@
       </c>
       <c r="E199" s="2" cm="1">
         <f t="array" ref="E199">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B200" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D200" s="6" t="str" cm="1">
         <f t="array" ref="D200">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القنفذة</v>
+        <v>مجموعة القطيف</v>
       </c>
       <c r="E200" s="2" cm="1">
         <f t="array" ref="E200">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B201" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D201" s="6" t="str" cm="1">
         <f t="array" ref="D201">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القنفذة</v>
+        <v>مجموعة القطيف</v>
       </c>
       <c r="E201" s="2" cm="1">
         <f t="array" ref="E201">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="202" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B202" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D202" s="6" t="str" cm="1">
         <f t="array" ref="D202">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القنفذة</v>
+        <v>مجموعة القطيف</v>
       </c>
       <c r="E202" s="2" cm="1">
         <f t="array" ref="E202">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B203" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>53</v>
@@ -13481,12 +13632,12 @@
       </c>
       <c r="E203" s="2" cm="1">
         <f t="array" ref="E203">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B204" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>53</v>
@@ -13497,12 +13648,12 @@
       </c>
       <c r="E204" s="2" cm="1">
         <f t="array" ref="E204">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B205" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>53</v>
@@ -13513,12 +13664,12 @@
       </c>
       <c r="E205" s="2" cm="1">
         <f t="array" ref="E205">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="206" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B206" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>53</v>
@@ -13529,60 +13680,60 @@
       </c>
       <c r="E206" s="2" cm="1">
         <f t="array" ref="E206">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B207" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="D207" s="6" t="str" cm="1">
         <f t="array" ref="D207">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الدوادمي</v>
+        <v>مجموعة القنفذة</v>
       </c>
       <c r="E207" s="2" cm="1">
         <f t="array" ref="E207">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="208" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B208" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="D208" s="6" t="str" cm="1">
         <f t="array" ref="D208">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الدوادمي</v>
+        <v>مجموعة القنفذة</v>
       </c>
       <c r="E208" s="2" cm="1">
         <f t="array" ref="E208">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B209" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="D209" s="6" t="str" cm="1">
         <f t="array" ref="D209">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الدوادمي</v>
+        <v>مجموعة القنفذة</v>
       </c>
       <c r="E209" s="2" cm="1">
         <f t="array" ref="E209">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="210" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B210" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>113</v>
@@ -13598,14 +13749,14 @@
     </row>
     <row r="211" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B211" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="D211" s="6" t="str" cm="1">
         <f t="array" ref="D211">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة حفر الباطن</v>
+        <v>مجموعة الدوادمي</v>
       </c>
       <c r="E211" s="2" cm="1">
         <f t="array" ref="E211">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13614,14 +13765,14 @@
     </row>
     <row r="212" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B212" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="D212" s="6" t="str" cm="1">
         <f t="array" ref="D212">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة حفر الباطن</v>
+        <v>مجموعة الدوادمي</v>
       </c>
       <c r="E212" s="2" cm="1">
         <f t="array" ref="E212">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13630,14 +13781,14 @@
     </row>
     <row r="213" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B213" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="D213" s="6" t="str" cm="1">
         <f t="array" ref="D213">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة حفر الباطن</v>
+        <v>مجموعة الدوادمي</v>
       </c>
       <c r="E213" s="2" cm="1">
         <f t="array" ref="E213">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13646,7 +13797,7 @@
     </row>
     <row r="214" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B214" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>139</v>
@@ -13662,7 +13813,7 @@
     </row>
     <row r="215" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B215" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>139</v>
@@ -13678,7 +13829,7 @@
     </row>
     <row r="216" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B216" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>139</v>
@@ -13694,7 +13845,7 @@
     </row>
     <row r="217" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B217" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>139</v>
@@ -13710,14 +13861,14 @@
     </row>
     <row r="218" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B218" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>56</v>
+        <v>139</v>
       </c>
       <c r="D218" s="6" t="str" cm="1">
         <f t="array" ref="D218">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الليث</v>
+        <v>مجموعة حفر الباطن</v>
       </c>
       <c r="E218" s="2" cm="1">
         <f t="array" ref="E218">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13726,14 +13877,14 @@
     </row>
     <row r="219" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B219" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>56</v>
+        <v>139</v>
       </c>
       <c r="D219" s="6" t="str" cm="1">
         <f t="array" ref="D219">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الليث</v>
+        <v>مجموعة حفر الباطن</v>
       </c>
       <c r="E219" s="2" cm="1">
         <f t="array" ref="E219">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13742,62 +13893,62 @@
     </row>
     <row r="220" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B220" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>56</v>
+        <v>139</v>
       </c>
       <c r="D220" s="6" t="str" cm="1">
         <f t="array" ref="D220">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الليث</v>
+        <v>مجموعة حفر الباطن</v>
       </c>
       <c r="E220" s="2" cm="1">
         <f t="array" ref="E220">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B221" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>56</v>
       </c>
       <c r="D221" s="6" t="str" cm="1">
         <f t="array" ref="D221">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القنفذة</v>
+        <v>مجموعة الليث</v>
       </c>
       <c r="E221" s="2" cm="1">
         <f t="array" ref="E221">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B222" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>56</v>
       </c>
       <c r="D222" s="6" t="str" cm="1">
         <f t="array" ref="D222">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القنفذة</v>
+        <v>مجموعة الليث</v>
       </c>
       <c r="E222" s="2" cm="1">
         <f t="array" ref="E222">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B223" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>56</v>
       </c>
       <c r="D223" s="6" t="str" cm="1">
         <f t="array" ref="D223">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القنفذة</v>
+        <v>مجموعة الليث</v>
       </c>
       <c r="E223" s="2" cm="1">
         <f t="array" ref="E223">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13806,7 +13957,7 @@
     </row>
     <row r="224" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B224" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>56</v>
@@ -13822,55 +13973,55 @@
     </row>
     <row r="225" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B225" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="D225" s="6" t="str" cm="1">
         <f t="array" ref="D225">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الأحساء</v>
+        <v>مجموعة القنفذة</v>
       </c>
       <c r="E225" s="2" cm="1">
         <f t="array" ref="E225">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B226" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="D226" s="6" t="str" cm="1">
         <f t="array" ref="D226">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الأحساء</v>
+        <v>مجموعة القنفذة</v>
       </c>
       <c r="E226" s="2" cm="1">
         <f t="array" ref="E226">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B227" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="D227" s="6" t="str" cm="1">
         <f t="array" ref="D227">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الأحساء</v>
+        <v>مجموعة القنفذة</v>
       </c>
       <c r="E227" s="2" cm="1">
         <f t="array" ref="E227">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B228" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C228" s="6" t="s">
         <v>103</v>
@@ -13886,7 +14037,7 @@
     </row>
     <row r="229" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B229" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C229" s="6" t="s">
         <v>103</v>
@@ -13902,7 +14053,7 @@
     </row>
     <row r="230" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B230" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C230" s="6" t="s">
         <v>103</v>
@@ -13918,7 +14069,7 @@
     </row>
     <row r="231" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B231" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C231" s="6" t="s">
         <v>103</v>
@@ -13934,14 +14085,14 @@
     </row>
     <row r="232" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B232" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="D232" s="6" t="str" cm="1">
         <f t="array" ref="D232">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المجاردة</v>
+        <v>مجموعة الأحساء</v>
       </c>
       <c r="E232" s="2" cm="1">
         <f t="array" ref="E232">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13950,14 +14101,14 @@
     </row>
     <row r="233" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B233" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="D233" s="6" t="str" cm="1">
         <f t="array" ref="D233">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المجاردة</v>
+        <v>مجموعة الأحساء</v>
       </c>
       <c r="E233" s="2" cm="1">
         <f t="array" ref="E233">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13966,14 +14117,14 @@
     </row>
     <row r="234" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B234" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="D234" s="6" t="str" cm="1">
         <f t="array" ref="D234">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المجاردة</v>
+        <v>مجموعة الأحساء</v>
       </c>
       <c r="E234" s="2" cm="1">
         <f t="array" ref="E234">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13982,14 +14133,14 @@
     </row>
     <row r="235" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B235" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C235" s="6" t="s">
         <v>140</v>
       </c>
       <c r="D235" s="6" t="str" cm="1">
         <f t="array" ref="D235">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة محايل عسير</v>
+        <v>مجموعة المجاردة</v>
       </c>
       <c r="E235" s="2" cm="1">
         <f t="array" ref="E235">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -13998,14 +14149,14 @@
     </row>
     <row r="236" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B236" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C236" s="6" t="s">
         <v>140</v>
       </c>
       <c r="D236" s="6" t="str" cm="1">
         <f t="array" ref="D236">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة محايل عسير</v>
+        <v>مجموعة المجاردة</v>
       </c>
       <c r="E236" s="2" cm="1">
         <f t="array" ref="E236">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14014,14 +14165,14 @@
     </row>
     <row r="237" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B237" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C237" s="6" t="s">
         <v>140</v>
       </c>
       <c r="D237" s="6" t="str" cm="1">
         <f t="array" ref="D237">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة محايل عسير</v>
+        <v>مجموعة المجاردة</v>
       </c>
       <c r="E237" s="2" cm="1">
         <f t="array" ref="E237">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14030,7 +14181,7 @@
     </row>
     <row r="238" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B238" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C238" s="6" t="s">
         <v>140</v>
@@ -14046,14 +14197,14 @@
     </row>
     <row r="239" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B239" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="D239" s="6" t="str" cm="1">
         <f t="array" ref="D239">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المجمعة</v>
+        <v>مجموعة محايل عسير</v>
       </c>
       <c r="E239" s="2" cm="1">
         <f t="array" ref="E239">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14062,14 +14213,14 @@
     </row>
     <row r="240" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B240" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="D240" s="6" t="str" cm="1">
         <f t="array" ref="D240">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المجمعة</v>
+        <v>مجموعة محايل عسير</v>
       </c>
       <c r="E240" s="2" cm="1">
         <f t="array" ref="E240">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14078,14 +14229,14 @@
     </row>
     <row r="241" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B241" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="D241" s="6" t="str" cm="1">
         <f t="array" ref="D241">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المجمعة</v>
+        <v>مجموعة محايل عسير</v>
       </c>
       <c r="E241" s="2" cm="1">
         <f t="array" ref="E241">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14094,7 +14245,7 @@
     </row>
     <row r="242" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B242" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C242" s="6" t="s">
         <v>99</v>
@@ -14110,7 +14261,7 @@
     </row>
     <row r="243" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B243" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C243" s="6" t="s">
         <v>99</v>
@@ -14126,7 +14277,7 @@
     </row>
     <row r="244" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B244" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C244" s="6" t="s">
         <v>99</v>
@@ -14142,7 +14293,7 @@
     </row>
     <row r="245" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B245" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C245" s="6" t="s">
         <v>99</v>
@@ -14158,14 +14309,14 @@
     </row>
     <row r="246" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B246" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D246" s="6" t="str" cm="1">
         <f t="array" ref="D246">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الباحة</v>
+        <v>مجموعة المجمعة</v>
       </c>
       <c r="E246" s="2" cm="1">
         <f t="array" ref="E246">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14174,14 +14325,14 @@
     </row>
     <row r="247" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B247" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D247" s="6" t="str" cm="1">
         <f t="array" ref="D247">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الباحة</v>
+        <v>مجموعة المجمعة</v>
       </c>
       <c r="E247" s="2" cm="1">
         <f t="array" ref="E247">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14190,14 +14341,14 @@
     </row>
     <row r="248" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B248" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D248" s="6" t="str" cm="1">
         <f t="array" ref="D248">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الباحة</v>
+        <v>مجموعة المجمعة</v>
       </c>
       <c r="E248" s="2" cm="1">
         <f t="array" ref="E248">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14206,7 +14357,7 @@
     </row>
     <row r="249" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B249" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C249" s="6" t="s">
         <v>106</v>
@@ -14222,55 +14373,55 @@
     </row>
     <row r="250" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B250" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="D250" s="6" t="str" cm="1">
         <f t="array" ref="D250">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المدينة المنورة</v>
+        <v>مجموعة الباحة</v>
       </c>
       <c r="E250" s="2" cm="1">
         <f t="array" ref="E250">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B251" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="D251" s="6" t="str" cm="1">
         <f t="array" ref="D251">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المدينة المنورة</v>
+        <v>مجموعة الباحة</v>
       </c>
       <c r="E251" s="2" cm="1">
         <f t="array" ref="E251">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B252" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="D252" s="6" t="str" cm="1">
         <f t="array" ref="D252">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المدينة المنورة</v>
+        <v>مجموعة الباحة</v>
       </c>
       <c r="E252" s="2" cm="1">
         <f t="array" ref="E252">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B253" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C253" s="6" t="s">
         <v>24</v>
@@ -14281,12 +14432,12 @@
       </c>
       <c r="E253" s="2" cm="1">
         <f t="array" ref="E253">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B254" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C254" s="6" t="s">
         <v>24</v>
@@ -14297,12 +14448,12 @@
       </c>
       <c r="E254" s="2" cm="1">
         <f t="array" ref="E254">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B255" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C255" s="6" t="s">
         <v>24</v>
@@ -14313,12 +14464,12 @@
       </c>
       <c r="E255" s="2" cm="1">
         <f t="array" ref="E255">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="256" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B256" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C256" s="6" t="s">
         <v>24</v>
@@ -14329,67 +14480,67 @@
       </c>
       <c r="E256" s="2" cm="1">
         <f t="array" ref="E256">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="257" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B257" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="D257" s="6" t="str" cm="1">
         <f t="array" ref="D257">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة عنيزة</v>
+        <v>مجموعة المدينة المنورة</v>
       </c>
       <c r="E257" s="2" cm="1">
         <f t="array" ref="E257">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="258" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B258" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="D258" s="6" t="str" cm="1">
         <f t="array" ref="D258">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة عنيزة</v>
+        <v>مجموعة المدينة المنورة</v>
       </c>
       <c r="E258" s="2" cm="1">
         <f t="array" ref="E258">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="259" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B259" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="D259" s="6" t="str" cm="1">
         <f t="array" ref="D259">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة عنيزة</v>
+        <v>مجموعة المدينة المنورة</v>
       </c>
       <c r="E259" s="2" cm="1">
         <f t="array" ref="E259">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="260" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B260" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C260" s="6" t="s">
         <v>124</v>
       </c>
       <c r="D260" s="6" t="str" cm="1">
         <f t="array" ref="D260">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القصيم</v>
+        <v>مجموعة عنيزة</v>
       </c>
       <c r="E260" s="2" cm="1">
         <f t="array" ref="E260">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14398,14 +14549,14 @@
     </row>
     <row r="261" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B261" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C261" s="6" t="s">
         <v>124</v>
       </c>
       <c r="D261" s="6" t="str" cm="1">
         <f t="array" ref="D261">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القصيم</v>
+        <v>مجموعة عنيزة</v>
       </c>
       <c r="E261" s="2" cm="1">
         <f t="array" ref="E261">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14414,14 +14565,14 @@
     </row>
     <row r="262" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B262" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C262" s="6" t="s">
         <v>124</v>
       </c>
       <c r="D262" s="6" t="str" cm="1">
         <f t="array" ref="D262">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القصيم</v>
+        <v>مجموعة عنيزة</v>
       </c>
       <c r="E262" s="2" cm="1">
         <f t="array" ref="E262">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14430,7 +14581,7 @@
     </row>
     <row r="263" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B263" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C263" s="6" t="s">
         <v>124</v>
@@ -14446,14 +14597,14 @@
     </row>
     <row r="264" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B264" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D264" s="6" t="str" cm="1">
         <f t="array" ref="D264">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المزاحمية</v>
+        <v>مجموعة القصيم</v>
       </c>
       <c r="E264" s="2" cm="1">
         <f t="array" ref="E264">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14462,14 +14613,14 @@
     </row>
     <row r="265" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B265" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D265" s="6" t="str" cm="1">
         <f t="array" ref="D265">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المزاحمية</v>
+        <v>مجموعة القصيم</v>
       </c>
       <c r="E265" s="2" cm="1">
         <f t="array" ref="E265">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14478,14 +14629,14 @@
     </row>
     <row r="266" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B266" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D266" s="6" t="str" cm="1">
         <f t="array" ref="D266">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المزاحمية</v>
+        <v>مجموعة القصيم</v>
       </c>
       <c r="E266" s="2" cm="1">
         <f t="array" ref="E266">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14494,14 +14645,14 @@
     </row>
     <row r="267" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B267" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C267" s="6" t="s">
         <v>114</v>
       </c>
       <c r="D267" s="6" t="str" cm="1">
         <f t="array" ref="D267">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الرياض</v>
+        <v>مجموعة المزاحمية</v>
       </c>
       <c r="E267" s="2" cm="1">
         <f t="array" ref="E267">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14510,14 +14661,14 @@
     </row>
     <row r="268" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B268" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C268" s="6" t="s">
         <v>114</v>
       </c>
       <c r="D268" s="6" t="str" cm="1">
         <f t="array" ref="D268">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الرياض</v>
+        <v>مجموعة المزاحمية</v>
       </c>
       <c r="E268" s="2" cm="1">
         <f t="array" ref="E268">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14526,14 +14677,14 @@
     </row>
     <row r="269" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B269" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C269" s="6" t="s">
         <v>114</v>
       </c>
       <c r="D269" s="6" t="str" cm="1">
         <f t="array" ref="D269">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الرياض</v>
+        <v>مجموعة المزاحمية</v>
       </c>
       <c r="E269" s="2" cm="1">
         <f t="array" ref="E269">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14542,7 +14693,7 @@
     </row>
     <row r="270" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B270" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C270" s="6" t="s">
         <v>114</v>
@@ -14558,14 +14709,14 @@
     </row>
     <row r="271" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B271" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D271" s="6" t="str" cm="1">
         <f t="array" ref="D271">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الباحة</v>
+        <v>مجموعة الرياض</v>
       </c>
       <c r="E271" s="2" cm="1">
         <f t="array" ref="E271">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14574,14 +14725,14 @@
     </row>
     <row r="272" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B272" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D272" s="6" t="str" cm="1">
         <f t="array" ref="D272">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الباحة</v>
+        <v>مجموعة الرياض</v>
       </c>
       <c r="E272" s="2" cm="1">
         <f t="array" ref="E272">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14590,14 +14741,14 @@
     </row>
     <row r="273" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B273" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D273" s="6" t="str" cm="1">
         <f t="array" ref="D273">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الباحة</v>
+        <v>مجموعة الرياض</v>
       </c>
       <c r="E273" s="2" cm="1">
         <f t="array" ref="E273">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14606,7 +14757,7 @@
     </row>
     <row r="274" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B274" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C274" s="6" t="s">
         <v>105</v>
@@ -14622,14 +14773,14 @@
     </row>
     <row r="275" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B275" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="D275" s="6" t="str" cm="1">
         <f t="array" ref="D275">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة النماص</v>
+        <v>مجموعة الباحة</v>
       </c>
       <c r="E275" s="2" cm="1">
         <f t="array" ref="E275">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14638,14 +14789,14 @@
     </row>
     <row r="276" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B276" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="D276" s="6" t="str" cm="1">
         <f t="array" ref="D276">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة النماص</v>
+        <v>مجموعة الباحة</v>
       </c>
       <c r="E276" s="2" cm="1">
         <f t="array" ref="E276">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14654,14 +14805,14 @@
     </row>
     <row r="277" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B277" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="D277" s="6" t="str" cm="1">
         <f t="array" ref="D277">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة النماص</v>
+        <v>مجموعة الباحة</v>
       </c>
       <c r="E277" s="2" cm="1">
         <f t="array" ref="E277">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14670,14 +14821,14 @@
     </row>
     <row r="278" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B278" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C278" s="6" t="s">
         <v>141</v>
       </c>
       <c r="D278" s="6" t="str" cm="1">
         <f t="array" ref="D278">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة محايل عسير</v>
+        <v>مجموعة النماص</v>
       </c>
       <c r="E278" s="2" cm="1">
         <f t="array" ref="E278">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14686,14 +14837,14 @@
     </row>
     <row r="279" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B279" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C279" s="6" t="s">
         <v>141</v>
       </c>
       <c r="D279" s="6" t="str" cm="1">
         <f t="array" ref="D279">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة محايل عسير</v>
+        <v>مجموعة النماص</v>
       </c>
       <c r="E279" s="2" cm="1">
         <f t="array" ref="E279">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14702,14 +14853,14 @@
     </row>
     <row r="280" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B280" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C280" s="6" t="s">
         <v>141</v>
       </c>
       <c r="D280" s="6" t="str" cm="1">
         <f t="array" ref="D280">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة محايل عسير</v>
+        <v>مجموعة النماص</v>
       </c>
       <c r="E280" s="2" cm="1">
         <f t="array" ref="E280">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14718,7 +14869,7 @@
     </row>
     <row r="281" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B281" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C281" s="6" t="s">
         <v>141</v>
@@ -14734,14 +14885,14 @@
     </row>
     <row r="282" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B282" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D282" s="6" t="str" cm="1">
         <f t="array" ref="D282">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المجاردة</v>
+        <v>مجموعة محايل عسير</v>
       </c>
       <c r="E282" s="2" cm="1">
         <f t="array" ref="E282">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14750,14 +14901,14 @@
     </row>
     <row r="283" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B283" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D283" s="6" t="str" cm="1">
         <f t="array" ref="D283">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المجاردة</v>
+        <v>مجموعة محايل عسير</v>
       </c>
       <c r="E283" s="2" cm="1">
         <f t="array" ref="E283">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14766,14 +14917,14 @@
     </row>
     <row r="284" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B284" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D284" s="6" t="str" cm="1">
         <f t="array" ref="D284">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المجاردة</v>
+        <v>مجموعة محايل عسير</v>
       </c>
       <c r="E284" s="2" cm="1">
         <f t="array" ref="E284">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14782,14 +14933,14 @@
     </row>
     <row r="285" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B285" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C285" s="6" t="s">
         <v>143</v>
       </c>
       <c r="D285" s="6" t="str" cm="1">
         <f t="array" ref="D285">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة محايل عسير</v>
+        <v>مجموعة المجاردة</v>
       </c>
       <c r="E285" s="2" cm="1">
         <f t="array" ref="E285">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14798,14 +14949,14 @@
     </row>
     <row r="286" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B286" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C286" s="6" t="s">
         <v>143</v>
       </c>
       <c r="D286" s="6" t="str" cm="1">
         <f t="array" ref="D286">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة محايل عسير</v>
+        <v>مجموعة المجاردة</v>
       </c>
       <c r="E286" s="2" cm="1">
         <f t="array" ref="E286">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14814,14 +14965,14 @@
     </row>
     <row r="287" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B287" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C287" s="6" t="s">
         <v>143</v>
       </c>
       <c r="D287" s="6" t="str" cm="1">
         <f t="array" ref="D287">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة محايل عسير</v>
+        <v>مجموعة المجاردة</v>
       </c>
       <c r="E287" s="2" cm="1">
         <f t="array" ref="E287">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14830,7 +14981,7 @@
     </row>
     <row r="288" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B288" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C288" s="6" t="s">
         <v>143</v>
@@ -14846,14 +14997,14 @@
     </row>
     <row r="289" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B289" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D289" s="6" t="str" cm="1">
         <f t="array" ref="D289">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة مكة المكرمة</v>
+        <v>مجموعة محايل عسير</v>
       </c>
       <c r="E289" s="2" cm="1">
         <f t="array" ref="E289">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14862,14 +15013,14 @@
     </row>
     <row r="290" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B290" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D290" s="6" t="str" cm="1">
         <f t="array" ref="D290">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة مكة المكرمة</v>
+        <v>مجموعة محايل عسير</v>
       </c>
       <c r="E290" s="2" cm="1">
         <f t="array" ref="E290">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14878,14 +15029,14 @@
     </row>
     <row r="291" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B291" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D291" s="6" t="str" cm="1">
         <f t="array" ref="D291">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة مكة المكرمة</v>
+        <v>مجموعة محايل عسير</v>
       </c>
       <c r="E291" s="2" cm="1">
         <f t="array" ref="E291">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14894,7 +15045,7 @@
     </row>
     <row r="292" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B292" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C292" s="6" t="s">
         <v>146</v>
@@ -14910,7 +15061,7 @@
     </row>
     <row r="293" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B293" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C293" s="6" t="s">
         <v>146</v>
@@ -14926,7 +15077,7 @@
     </row>
     <row r="294" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B294" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C294" s="6" t="s">
         <v>146</v>
@@ -14942,7 +15093,7 @@
     </row>
     <row r="295" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B295" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C295" s="6" t="s">
         <v>146</v>
@@ -14958,14 +15109,14 @@
     </row>
     <row r="296" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B296" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="D296" s="6" t="str" cm="1">
         <f t="array" ref="D296">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القصيم</v>
+        <v>مجموعة مكة المكرمة</v>
       </c>
       <c r="E296" s="2" cm="1">
         <f t="array" ref="E296">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -14974,39 +15125,39 @@
     </row>
     <row r="297" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B297" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="D297" s="6" t="str" cm="1">
         <f t="array" ref="D297">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القصيم</v>
+        <v>مجموعة مكة المكرمة</v>
       </c>
       <c r="E297" s="2" cm="1">
         <f t="array" ref="E297">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B298" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="D298" s="6" t="str" cm="1">
         <f t="array" ref="D298">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القصيم</v>
+        <v>مجموعة مكة المكرمة</v>
       </c>
       <c r="E298" s="2" cm="1">
         <f t="array" ref="E298">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B299" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C299" s="6" t="s">
         <v>120</v>
@@ -15017,12 +15168,12 @@
       </c>
       <c r="E299" s="2" cm="1">
         <f t="array" ref="E299">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B300" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C300" s="6" t="s">
         <v>120</v>
@@ -15033,12 +15184,12 @@
       </c>
       <c r="E300" s="2" cm="1">
         <f t="array" ref="E300">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B301" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C301" s="6" t="s">
         <v>120</v>
@@ -15049,12 +15200,12 @@
       </c>
       <c r="E301" s="2" cm="1">
         <f t="array" ref="E301">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="302" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B302" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C302" s="6" t="s">
         <v>120</v>
@@ -15065,67 +15216,67 @@
       </c>
       <c r="E302" s="2" cm="1">
         <f t="array" ref="E302">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="303" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B303" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="D303" s="6" t="str" cm="1">
         <f t="array" ref="D303">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة بقيق</v>
+        <v>مجموعة القصيم</v>
       </c>
       <c r="E303" s="2" cm="1">
         <f t="array" ref="E303">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="304" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B304" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="D304" s="6" t="str" cm="1">
         <f t="array" ref="D304">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة بقيق</v>
+        <v>مجموعة القصيم</v>
       </c>
       <c r="E304" s="2" cm="1">
         <f t="array" ref="E304">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B305" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="D305" s="6" t="str" cm="1">
         <f t="array" ref="D305">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة بقيق</v>
+        <v>مجموعة القصيم</v>
       </c>
       <c r="E305" s="2" cm="1">
         <f t="array" ref="E305">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B306" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C306" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D306" s="6" t="str" cm="1">
         <f t="array" ref="D306">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الأحساء</v>
+        <v>مجموعة بقيق</v>
       </c>
       <c r="E306" s="2" cm="1">
         <f t="array" ref="E306">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -15134,14 +15285,14 @@
     </row>
     <row r="307" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B307" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C307" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D307" s="6" t="str" cm="1">
         <f t="array" ref="D307">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الأحساء</v>
+        <v>مجموعة بقيق</v>
       </c>
       <c r="E307" s="2" cm="1">
         <f t="array" ref="E307">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -15150,14 +15301,14 @@
     </row>
     <row r="308" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B308" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C308" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D308" s="6" t="str" cm="1">
         <f t="array" ref="D308">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الأحساء</v>
+        <v>مجموعة بقيق</v>
       </c>
       <c r="E308" s="2" cm="1">
         <f t="array" ref="E308">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -15166,7 +15317,7 @@
     </row>
     <row r="309" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B309" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C309" s="6" t="s">
         <v>62</v>
@@ -15182,14 +15333,14 @@
     </row>
     <row r="310" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B310" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="D310" s="6" t="str" cm="1">
         <f t="array" ref="D310">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الباحة</v>
+        <v>مجموعة الأحساء</v>
       </c>
       <c r="E310" s="2" cm="1">
         <f t="array" ref="E310">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -15198,14 +15349,14 @@
     </row>
     <row r="311" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B311" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="D311" s="6" t="str" cm="1">
         <f t="array" ref="D311">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الباحة</v>
+        <v>مجموعة الأحساء</v>
       </c>
       <c r="E311" s="2" cm="1">
         <f t="array" ref="E311">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -15214,14 +15365,14 @@
     </row>
     <row r="312" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B312" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="D312" s="6" t="str" cm="1">
         <f t="array" ref="D312">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الباحة</v>
+        <v>مجموعة الأحساء</v>
       </c>
       <c r="E312" s="2" cm="1">
         <f t="array" ref="E312">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -15230,7 +15381,7 @@
     </row>
     <row r="313" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B313" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C313" s="6" t="s">
         <v>107</v>
@@ -15246,7 +15397,7 @@
     </row>
     <row r="314" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B314" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C314" s="6" t="s">
         <v>107</v>
@@ -15262,7 +15413,7 @@
     </row>
     <row r="315" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B315" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C315" s="6" t="s">
         <v>107</v>
@@ -15278,7 +15429,7 @@
     </row>
     <row r="316" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B316" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C316" s="6" t="s">
         <v>107</v>
@@ -15294,55 +15445,55 @@
     </row>
     <row r="317" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B317" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="D317" s="6" t="str" cm="1">
         <f t="array" ref="D317">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة بيش</v>
+        <v>مجموعة الباحة</v>
       </c>
       <c r="E317" s="2" cm="1">
         <f t="array" ref="E317">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B318" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="D318" s="6" t="str" cm="1">
         <f t="array" ref="D318">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة بيش</v>
+        <v>مجموعة الباحة</v>
       </c>
       <c r="E318" s="2" cm="1">
         <f t="array" ref="E318">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B319" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="D319" s="6" t="str" cm="1">
         <f t="array" ref="D319">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة بيش</v>
+        <v>مجموعة الباحة</v>
       </c>
       <c r="E319" s="2" cm="1">
         <f t="array" ref="E319">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B320" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C320" s="6" t="s">
         <v>39</v>
@@ -15358,7 +15509,7 @@
     </row>
     <row r="321" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B321" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C321" s="6" t="s">
         <v>39</v>
@@ -15374,7 +15525,7 @@
     </row>
     <row r="322" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B322" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C322" s="6" t="s">
         <v>39</v>
@@ -15390,7 +15541,7 @@
     </row>
     <row r="323" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B323" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C323" s="6" t="s">
         <v>39</v>
@@ -15401,60 +15552,60 @@
       </c>
       <c r="E323" s="2" cm="1">
         <f t="array" ref="E323">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="324" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B324" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="D324" s="6" t="str" cm="1">
         <f t="array" ref="D324">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة بيشة</v>
+        <v>مجموعة بيش</v>
       </c>
       <c r="E324" s="2" cm="1">
         <f t="array" ref="E324">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="325" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B325" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="D325" s="6" t="str" cm="1">
         <f t="array" ref="D325">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة بيشة</v>
+        <v>مجموعة بيش</v>
       </c>
       <c r="E325" s="2" cm="1">
         <f t="array" ref="E325">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="326" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B326" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C326" s="6" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="D326" s="6" t="str" cm="1">
         <f t="array" ref="D326">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة بيشة</v>
+        <v>مجموعة بيش</v>
       </c>
       <c r="E326" s="2" cm="1">
         <f t="array" ref="E326">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B327" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C327" s="6" t="s">
         <v>65</v>
@@ -15470,7 +15621,7 @@
     </row>
     <row r="328" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B328" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C328" s="6" t="s">
         <v>65</v>
@@ -15486,7 +15637,7 @@
     </row>
     <row r="329" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B329" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C329" s="6" t="s">
         <v>65</v>
@@ -15502,7 +15653,7 @@
     </row>
     <row r="330" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B330" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C330" s="6" t="s">
         <v>65</v>
@@ -15513,19 +15664,19 @@
       </c>
       <c r="E330" s="2" cm="1">
         <f t="array" ref="E330">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B331" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C331" s="6" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D331" s="6" t="str" cm="1">
         <f t="array" ref="D331">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة تبوك</v>
+        <v>مجموعة بيشة</v>
       </c>
       <c r="E331" s="2" cm="1">
         <f t="array" ref="E331">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -15534,14 +15685,14 @@
     </row>
     <row r="332" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B332" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C332" s="6" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D332" s="6" t="str" cm="1">
         <f t="array" ref="D332">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة تبوك</v>
+        <v>مجموعة بيشة</v>
       </c>
       <c r="E332" s="2" cm="1">
         <f t="array" ref="E332">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -15550,23 +15701,23 @@
     </row>
     <row r="333" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B333" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C333" s="6" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D333" s="6" t="str" cm="1">
         <f t="array" ref="D333">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة تبوك</v>
+        <v>مجموعة بيشة</v>
       </c>
       <c r="E333" s="2" cm="1">
         <f t="array" ref="E333">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B334" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C334" s="6" t="s">
         <v>27</v>
@@ -15582,7 +15733,7 @@
     </row>
     <row r="335" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B335" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C335" s="6" t="s">
         <v>27</v>
@@ -15593,12 +15744,12 @@
       </c>
       <c r="E335" s="2" cm="1">
         <f t="array" ref="E335">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B336" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C336" s="6" t="s">
         <v>27</v>
@@ -15614,7 +15765,7 @@
     </row>
     <row r="337" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B337" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C337" s="6" t="s">
         <v>27</v>
@@ -15630,62 +15781,62 @@
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B338" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C338" s="6" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="D338" s="6" t="str" cm="1">
         <f t="array" ref="D338">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة النماص</v>
+        <v>مجموعة تبوك</v>
       </c>
       <c r="E338" s="2" cm="1">
         <f t="array" ref="E338">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B339" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="D339" s="6" t="str" cm="1">
         <f t="array" ref="D339">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة النماص</v>
+        <v>مجموعة تبوك</v>
       </c>
       <c r="E339" s="2" cm="1">
         <f t="array" ref="E339">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="340" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B340" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="D340" s="6" t="str" cm="1">
         <f t="array" ref="D340">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة النماص</v>
+        <v>مجموعة تبوك</v>
       </c>
       <c r="E340" s="2" cm="1">
         <f t="array" ref="E340">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B341" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C341" s="6" t="s">
         <v>142</v>
       </c>
       <c r="D341" s="6" t="str" cm="1">
         <f t="array" ref="D341">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة محايل عسير</v>
+        <v>مجموعة النماص</v>
       </c>
       <c r="E341" s="2" cm="1">
         <f t="array" ref="E341">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -15694,14 +15845,14 @@
     </row>
     <row r="342" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B342" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C342" s="6" t="s">
         <v>142</v>
       </c>
       <c r="D342" s="6" t="str" cm="1">
         <f t="array" ref="D342">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة محايل عسير</v>
+        <v>مجموعة النماص</v>
       </c>
       <c r="E342" s="2" cm="1">
         <f t="array" ref="E342">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -15710,14 +15861,14 @@
     </row>
     <row r="343" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B343" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C343" s="6" t="s">
         <v>142</v>
       </c>
       <c r="D343" s="6" t="str" cm="1">
         <f t="array" ref="D343">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة محايل عسير</v>
+        <v>مجموعة النماص</v>
       </c>
       <c r="E343" s="2" cm="1">
         <f t="array" ref="E343">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -15726,7 +15877,7 @@
     </row>
     <row r="344" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B344" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C344" s="6" t="s">
         <v>142</v>
@@ -15742,55 +15893,55 @@
     </row>
     <row r="345" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B345" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>501</v>
+        <v>142</v>
       </c>
       <c r="D345" s="6" t="str" cm="1">
         <f t="array" ref="D345">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جازان</v>
+        <v>مجموعة محايل عسير</v>
       </c>
       <c r="E345" s="2" cm="1">
         <f t="array" ref="E345">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B346" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>501</v>
+        <v>142</v>
       </c>
       <c r="D346" s="6" t="str" cm="1">
         <f t="array" ref="D346">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جازان</v>
+        <v>مجموعة محايل عسير</v>
       </c>
       <c r="E346" s="2" cm="1">
         <f t="array" ref="E346">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B347" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>501</v>
+        <v>142</v>
       </c>
       <c r="D347" s="6" t="str" cm="1">
         <f t="array" ref="D347">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جازان</v>
+        <v>مجموعة محايل عسير</v>
       </c>
       <c r="E347" s="2" cm="1">
         <f t="array" ref="E347">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B348" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C348" s="6" t="s">
         <v>501</v>
@@ -15801,12 +15952,12 @@
       </c>
       <c r="E348" s="2" cm="1">
         <f t="array" ref="E348">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="349" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B349" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C349" s="6" t="s">
         <v>501</v>
@@ -15817,12 +15968,12 @@
       </c>
       <c r="E349" s="2" cm="1">
         <f t="array" ref="E349">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="350" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B350" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C350" s="6" t="s">
         <v>501</v>
@@ -15833,12 +15984,12 @@
       </c>
       <c r="E350" s="2" cm="1">
         <f t="array" ref="E350">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="351" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B351" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C351" s="6" t="s">
         <v>501</v>
@@ -15849,60 +16000,60 @@
       </c>
       <c r="E351" s="2" cm="1">
         <f t="array" ref="E351">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="352" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B352" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C352" s="6" t="s">
-        <v>30</v>
+        <v>501</v>
       </c>
       <c r="D352" s="6" t="str" cm="1">
         <f t="array" ref="D352">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جدة</v>
+        <v>مجموعة جازان</v>
       </c>
       <c r="E352" s="2" cm="1">
         <f t="array" ref="E352">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="353" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B353" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>30</v>
+        <v>501</v>
       </c>
       <c r="D353" s="6" t="str" cm="1">
         <f t="array" ref="D353">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جدة</v>
+        <v>مجموعة جازان</v>
       </c>
       <c r="E353" s="2" cm="1">
         <f t="array" ref="E353">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="354" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B354" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>30</v>
+        <v>501</v>
       </c>
       <c r="D354" s="6" t="str" cm="1">
         <f t="array" ref="D354">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جدة</v>
+        <v>مجموعة جازان</v>
       </c>
       <c r="E354" s="2" cm="1">
         <f t="array" ref="E354">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="355" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B355" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C355" s="6" t="s">
         <v>30</v>
@@ -15913,12 +16064,12 @@
       </c>
       <c r="E355" s="2" cm="1">
         <f t="array" ref="E355">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="356" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B356" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C356" s="6" t="s">
         <v>30</v>
@@ -15929,12 +16080,12 @@
       </c>
       <c r="E356" s="2" cm="1">
         <f t="array" ref="E356">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="357" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B357" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C357" s="6" t="s">
         <v>30</v>
@@ -15945,12 +16096,12 @@
       </c>
       <c r="E357" s="2" cm="1">
         <f t="array" ref="E357">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="358" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B358" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C358" s="6" t="s">
         <v>30</v>
@@ -15961,60 +16112,60 @@
       </c>
       <c r="E358" s="2" cm="1">
         <f t="array" ref="E358">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="359" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B359" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C359" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D359" s="6" t="str" cm="1">
         <f t="array" ref="D359">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة حائل</v>
+        <v>مجموعة جدة</v>
       </c>
       <c r="E359" s="2" cm="1">
         <f t="array" ref="E359">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="360" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B360" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C360" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D360" s="6" t="str" cm="1">
         <f t="array" ref="D360">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة حائل</v>
+        <v>مجموعة جدة</v>
       </c>
       <c r="E360" s="2" cm="1">
         <f t="array" ref="E360">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="361" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B361" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C361" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D361" s="6" t="str" cm="1">
         <f t="array" ref="D361">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة حائل</v>
+        <v>مجموعة جدة</v>
       </c>
       <c r="E361" s="2" cm="1">
         <f t="array" ref="E361">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="362" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B362" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C362" s="6" t="s">
         <v>32</v>
@@ -16025,12 +16176,12 @@
       </c>
       <c r="E362" s="2" cm="1">
         <f t="array" ref="E362">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B363" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C363" s="6" t="s">
         <v>32</v>
@@ -16046,7 +16197,7 @@
     </row>
     <row r="364" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B364" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C364" s="6" t="s">
         <v>32</v>
@@ -16062,7 +16213,7 @@
     </row>
     <row r="365" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B365" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C365" s="6" t="s">
         <v>32</v>
@@ -16078,55 +16229,55 @@
     </row>
     <row r="366" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B366" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>147</v>
+        <v>32</v>
       </c>
       <c r="D366" s="6" t="str" cm="1">
         <f t="array" ref="D366">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة نجران</v>
+        <v>مجموعة حائل</v>
       </c>
       <c r="E366" s="2" cm="1">
         <f t="array" ref="E366">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B367" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C367" s="6" t="s">
-        <v>147</v>
+        <v>32</v>
       </c>
       <c r="D367" s="6" t="str" cm="1">
         <f t="array" ref="D367">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة نجران</v>
+        <v>مجموعة حائل</v>
       </c>
       <c r="E367" s="2" cm="1">
         <f t="array" ref="E367">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="368" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B368" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C368" s="6" t="s">
-        <v>147</v>
+        <v>32</v>
       </c>
       <c r="D368" s="6" t="str" cm="1">
         <f t="array" ref="D368">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة نجران</v>
+        <v>مجموعة حائل</v>
       </c>
       <c r="E368" s="2" cm="1">
         <f t="array" ref="E368">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B369" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C369" s="6" t="s">
         <v>147</v>
@@ -16142,55 +16293,55 @@
     </row>
     <row r="370" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B370" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C370" s="6" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D370" s="6" t="str" cm="1">
         <f t="array" ref="D370">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة حفر الباطن</v>
+        <v>مجموعة نجران</v>
       </c>
       <c r="E370" s="2" cm="1">
         <f t="array" ref="E370">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B371" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C371" s="6" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D371" s="6" t="str" cm="1">
         <f t="array" ref="D371">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة حفر الباطن</v>
+        <v>مجموعة نجران</v>
       </c>
       <c r="E371" s="2" cm="1">
         <f t="array" ref="E371">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B372" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C372" s="6" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D372" s="6" t="str" cm="1">
         <f t="array" ref="D372">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة حفر الباطن</v>
+        <v>مجموعة نجران</v>
       </c>
       <c r="E372" s="2" cm="1">
         <f t="array" ref="E372">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B373" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C373" s="6" t="s">
         <v>138</v>
@@ -16201,12 +16352,12 @@
       </c>
       <c r="E373" s="2" cm="1">
         <f t="array" ref="E373">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="374" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B374" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C374" s="6" t="s">
         <v>138</v>
@@ -16217,12 +16368,12 @@
       </c>
       <c r="E374" s="2" cm="1">
         <f t="array" ref="E374">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="375" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B375" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C375" s="6" t="s">
         <v>138</v>
@@ -16238,7 +16389,7 @@
     </row>
     <row r="376" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B376" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C376" s="6" t="s">
         <v>138</v>
@@ -16254,55 +16405,55 @@
     </row>
     <row r="377" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B377" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C377" s="6" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="D377" s="6" t="str" cm="1">
         <f t="array" ref="D377">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الخرج</v>
+        <v>مجموعة حفر الباطن</v>
       </c>
       <c r="E377" s="2" cm="1">
         <f t="array" ref="E377">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="378" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B378" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C378" s="6" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="D378" s="6" t="str" cm="1">
         <f t="array" ref="D378">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الخرج</v>
+        <v>مجموعة حفر الباطن</v>
       </c>
       <c r="E378" s="2" cm="1">
         <f t="array" ref="E378">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="379" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B379" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C379" s="6" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="D379" s="6" t="str" cm="1">
         <f t="array" ref="D379">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الخرج</v>
+        <v>مجموعة حفر الباطن</v>
       </c>
       <c r="E379" s="2" cm="1">
         <f t="array" ref="E379">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="380" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B380" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C380" s="6" t="s">
         <v>112</v>
@@ -16318,14 +16469,14 @@
     </row>
     <row r="381" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B381" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C381" s="6" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="D381" s="6" t="str" cm="1">
         <f t="array" ref="D381">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة نجران</v>
+        <v>مجموعة الخرج</v>
       </c>
       <c r="E381" s="2" cm="1">
         <f t="array" ref="E381">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16334,14 +16485,14 @@
     </row>
     <row r="382" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B382" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C382" s="6" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="D382" s="6" t="str" cm="1">
         <f t="array" ref="D382">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة نجران</v>
+        <v>مجموعة الخرج</v>
       </c>
       <c r="E382" s="2" cm="1">
         <f t="array" ref="E382">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16350,14 +16501,14 @@
     </row>
     <row r="383" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B383" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="D383" s="6" t="str" cm="1">
         <f t="array" ref="D383">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة نجران</v>
+        <v>مجموعة الخرج</v>
       </c>
       <c r="E383" s="2" cm="1">
         <f t="array" ref="E383">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16366,7 +16517,7 @@
     </row>
     <row r="384" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B384" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C384" s="6" t="s">
         <v>148</v>
@@ -16382,14 +16533,14 @@
     </row>
     <row r="385" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B385" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C385" s="6" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="D385" s="6" t="str" cm="1">
         <f t="array" ref="D385">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة أبها</v>
+        <v>مجموعة نجران</v>
       </c>
       <c r="E385" s="2" cm="1">
         <f t="array" ref="E385">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16398,39 +16549,39 @@
     </row>
     <row r="386" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B386" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C386" s="6" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="D386" s="6" t="str" cm="1">
         <f t="array" ref="D386">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة أبها</v>
+        <v>مجموعة نجران</v>
       </c>
       <c r="E386" s="2" cm="1">
         <f t="array" ref="E386">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B387" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C387" s="6" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="D387" s="6" t="str" cm="1">
         <f t="array" ref="D387">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة أبها</v>
+        <v>مجموعة نجران</v>
       </c>
       <c r="E387" s="2" cm="1">
         <f t="array" ref="E387">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B388" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C388" s="6" t="s">
         <v>101</v>
@@ -16441,12 +16592,12 @@
       </c>
       <c r="E388" s="2" cm="1">
         <f t="array" ref="E388">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B389" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C389" s="6" t="s">
         <v>101</v>
@@ -16457,12 +16608,12 @@
       </c>
       <c r="E389" s="2" cm="1">
         <f t="array" ref="E389">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="390" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B390" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C390" s="6" t="s">
         <v>101</v>
@@ -16473,12 +16624,12 @@
       </c>
       <c r="E390" s="2" cm="1">
         <f t="array" ref="E390">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="391" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B391" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C391" s="6" t="s">
         <v>101</v>
@@ -16489,60 +16640,60 @@
       </c>
       <c r="E391" s="2" cm="1">
         <f t="array" ref="E391">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="392" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B392" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C392" s="6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D392" s="6" t="str" cm="1">
         <f t="array" ref="D392">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الجوف</v>
+        <v>مجموعة أبها</v>
       </c>
       <c r="E392" s="2" cm="1">
         <f t="array" ref="E392">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="393" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B393" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C393" s="6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D393" s="6" t="str" cm="1">
         <f t="array" ref="D393">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الجوف</v>
+        <v>مجموعة أبها</v>
       </c>
       <c r="E393" s="2" cm="1">
         <f t="array" ref="E393">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="394" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B394" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C394" s="6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D394" s="6" t="str" cm="1">
         <f t="array" ref="D394">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الجوف</v>
+        <v>مجموعة أبها</v>
       </c>
       <c r="E394" s="2" cm="1">
         <f t="array" ref="E394">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B395" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C395" s="6" t="s">
         <v>109</v>
@@ -16558,7 +16709,7 @@
     </row>
     <row r="396" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B396" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C396" s="6" t="s">
         <v>109</v>
@@ -16574,7 +16725,7 @@
     </row>
     <row r="397" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B397" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C397" s="6" t="s">
         <v>109</v>
@@ -16590,7 +16741,7 @@
     </row>
     <row r="398" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B398" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C398" s="6" t="s">
         <v>109</v>
@@ -16606,55 +16757,55 @@
     </row>
     <row r="399" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B399" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C399" s="6" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="D399" s="6" t="str" cm="1">
         <f t="array" ref="D399">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القطيف</v>
+        <v>مجموعة الجوف</v>
       </c>
       <c r="E399" s="2" cm="1">
         <f t="array" ref="E399">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="400" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B400" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C400" s="6" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="D400" s="6" t="str" cm="1">
         <f t="array" ref="D400">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القطيف</v>
+        <v>مجموعة الجوف</v>
       </c>
       <c r="E400" s="2" cm="1">
         <f t="array" ref="E400">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B401" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C401" s="6" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="D401" s="6" t="str" cm="1">
         <f t="array" ref="D401">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القطيف</v>
+        <v>مجموعة الجوف</v>
       </c>
       <c r="E401" s="2" cm="1">
         <f t="array" ref="E401">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="402" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B402" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C402" s="6" t="s">
         <v>130</v>
@@ -16670,7 +16821,7 @@
     </row>
     <row r="403" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B403" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C403" s="6" t="s">
         <v>130</v>
@@ -16686,7 +16837,7 @@
     </row>
     <row r="404" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B404" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C404" s="6" t="s">
         <v>130</v>
@@ -16702,7 +16853,7 @@
     </row>
     <row r="405" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B405" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C405" s="6" t="s">
         <v>130</v>
@@ -16718,14 +16869,14 @@
     </row>
     <row r="406" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B406" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C406" s="6" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="D406" s="6" t="str" cm="1">
         <f t="array" ref="D406">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة رابغ</v>
+        <v>مجموعة القطيف</v>
       </c>
       <c r="E406" s="2" cm="1">
         <f t="array" ref="E406">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16734,14 +16885,14 @@
     </row>
     <row r="407" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B407" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C407" s="6" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="D407" s="6" t="str" cm="1">
         <f t="array" ref="D407">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة رابغ</v>
+        <v>مجموعة القطيف</v>
       </c>
       <c r="E407" s="2" cm="1">
         <f t="array" ref="E407">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16750,14 +16901,14 @@
     </row>
     <row r="408" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B408" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C408" s="6" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="D408" s="6" t="str" cm="1">
         <f t="array" ref="D408">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة رابغ</v>
+        <v>مجموعة القطيف</v>
       </c>
       <c r="E408" s="2" cm="1">
         <f t="array" ref="E408">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16769,11 +16920,11 @@
         <v>4</v>
       </c>
       <c r="C409" s="6" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D409" s="6" t="str" cm="1">
         <f t="array" ref="D409">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة رجال ألمع</v>
+        <v>مجموعة رابغ</v>
       </c>
       <c r="E409" s="2" cm="1">
         <f t="array" ref="E409">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16785,11 +16936,11 @@
         <v>150</v>
       </c>
       <c r="C410" s="6" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D410" s="6" t="str" cm="1">
         <f t="array" ref="D410">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة رجال ألمع</v>
+        <v>مجموعة رابغ</v>
       </c>
       <c r="E410" s="2" cm="1">
         <f t="array" ref="E410">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16801,11 +16952,11 @@
         <v>151</v>
       </c>
       <c r="C411" s="6" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D411" s="6" t="str" cm="1">
         <f t="array" ref="D411">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة رجال ألمع</v>
+        <v>مجموعة رابغ</v>
       </c>
       <c r="E411" s="2" cm="1">
         <f t="array" ref="E411">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16814,46 +16965,46 @@
     </row>
     <row r="412" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B412" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C412" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D412" s="6" t="str" cm="1">
         <f t="array" ref="D412">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة أبها</v>
+        <v>مجموعة رجال ألمع</v>
       </c>
       <c r="E412" s="2" cm="1">
         <f t="array" ref="E412">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="413" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B413" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C413" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D413" s="6" t="str" cm="1">
         <f t="array" ref="D413">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة أبها</v>
+        <v>مجموعة رجال ألمع</v>
       </c>
       <c r="E413" s="2" cm="1">
         <f t="array" ref="E413">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B414" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C414" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D414" s="6" t="str" cm="1">
         <f t="array" ref="D414">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة أبها</v>
+        <v>مجموعة رجال ألمع</v>
       </c>
       <c r="E414" s="2" cm="1">
         <f t="array" ref="E414">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16862,7 +17013,7 @@
     </row>
     <row r="415" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B415" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C415" s="6" t="s">
         <v>70</v>
@@ -16873,35 +17024,35 @@
       </c>
       <c r="E415" s="2" cm="1">
         <f t="array" ref="E415">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B416" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C416" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D416" s="6" t="str" cm="1">
         <f t="array" ref="D416">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة رفحاء</v>
+        <v>مجموعة أبها</v>
       </c>
       <c r="E416" s="2" cm="1">
         <f t="array" ref="E416">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B417" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C417" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D417" s="6" t="str" cm="1">
         <f t="array" ref="D417">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة رفحاء</v>
+        <v>مجموعة أبها</v>
       </c>
       <c r="E417" s="2" cm="1">
         <f t="array" ref="E417">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16910,14 +17061,14 @@
     </row>
     <row r="418" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B418" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C418" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D418" s="6" t="str" cm="1">
         <f t="array" ref="D418">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة رفحاء</v>
+        <v>مجموعة أبها</v>
       </c>
       <c r="E418" s="2" cm="1">
         <f t="array" ref="E418">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16926,14 +17077,14 @@
     </row>
     <row r="419" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B419" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C419" s="6" t="s">
         <v>72</v>
       </c>
       <c r="D419" s="6" t="str" cm="1">
         <f t="array" ref="D419">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الحدود الشمالية</v>
+        <v>مجموعة رفحاء</v>
       </c>
       <c r="E419" s="2" cm="1">
         <f t="array" ref="E419">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16942,14 +17093,14 @@
     </row>
     <row r="420" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B420" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C420" s="6" t="s">
         <v>72</v>
       </c>
       <c r="D420" s="6" t="str" cm="1">
         <f t="array" ref="D420">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الحدود الشمالية</v>
+        <v>مجموعة رفحاء</v>
       </c>
       <c r="E420" s="2" cm="1">
         <f t="array" ref="E420">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16958,14 +17109,14 @@
     </row>
     <row r="421" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B421" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C421" s="6" t="s">
         <v>72</v>
       </c>
       <c r="D421" s="6" t="str" cm="1">
         <f t="array" ref="D421">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الحدود الشمالية</v>
+        <v>مجموعة رفحاء</v>
       </c>
       <c r="E421" s="2" cm="1">
         <f t="array" ref="E421">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -16974,7 +17125,7 @@
     </row>
     <row r="422" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B422" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C422" s="6" t="s">
         <v>72</v>
@@ -16985,51 +17136,51 @@
       </c>
       <c r="E422" s="2" cm="1">
         <f t="array" ref="E422">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="423" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B423" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C423" s="6" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D423" s="6" t="str" cm="1">
         <f t="array" ref="D423">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الجوف</v>
+        <v>مجموعة الحدود الشمالية</v>
       </c>
       <c r="E423" s="2" cm="1">
         <f t="array" ref="E423">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="424" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B424" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C424" s="6" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D424" s="6" t="str" cm="1">
         <f t="array" ref="D424">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الجوف</v>
+        <v>مجموعة الحدود الشمالية</v>
       </c>
       <c r="E424" s="2" cm="1">
         <f t="array" ref="E424">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="425" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B425" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C425" s="6" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D425" s="6" t="str" cm="1">
         <f t="array" ref="D425">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الجوف</v>
+        <v>مجموعة الحدود الشمالية</v>
       </c>
       <c r="E425" s="2" cm="1">
         <f t="array" ref="E425">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17038,7 +17189,7 @@
     </row>
     <row r="426" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B426" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C426" s="6" t="s">
         <v>108</v>
@@ -17049,12 +17200,12 @@
       </c>
       <c r="E426" s="2" cm="1">
         <f t="array" ref="E426">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B427" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C427" s="6" t="s">
         <v>108</v>
@@ -17065,12 +17216,12 @@
       </c>
       <c r="E427" s="2" cm="1">
         <f t="array" ref="E427">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B428" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C428" s="6" t="s">
         <v>108</v>
@@ -17081,12 +17232,12 @@
       </c>
       <c r="E428" s="2" cm="1">
         <f t="array" ref="E428">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B429" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C429" s="6" t="s">
         <v>108</v>
@@ -17102,55 +17253,55 @@
     </row>
     <row r="430" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B430" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C430" s="6" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D430" s="6" t="str" cm="1">
         <f t="array" ref="D430">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الشرقية</v>
+        <v>مجموعة الجوف</v>
       </c>
       <c r="E430" s="2" cm="1">
         <f t="array" ref="E430">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B431" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C431" s="6" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D431" s="6" t="str" cm="1">
         <f t="array" ref="D431">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الشرقية</v>
+        <v>مجموعة الجوف</v>
       </c>
       <c r="E431" s="2" cm="1">
         <f t="array" ref="E431">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="432" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B432" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C432" s="6" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D432" s="6" t="str" cm="1">
         <f t="array" ref="D432">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الشرقية</v>
+        <v>مجموعة الجوف</v>
       </c>
       <c r="E432" s="2" cm="1">
         <f t="array" ref="E432">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B433" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C433" s="6" t="s">
         <v>119</v>
@@ -17166,7 +17317,7 @@
     </row>
     <row r="434" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B434" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C434" s="6" t="s">
         <v>119</v>
@@ -17182,7 +17333,7 @@
     </row>
     <row r="435" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B435" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C435" s="6" t="s">
         <v>119</v>
@@ -17198,7 +17349,7 @@
     </row>
     <row r="436" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B436" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C436" s="6" t="s">
         <v>119</v>
@@ -17214,14 +17365,14 @@
     </row>
     <row r="437" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B437" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C437" s="6" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="D437" s="6" t="str" cm="1">
         <f t="array" ref="D437">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة شرورة</v>
+        <v>مجموعة الشرقية</v>
       </c>
       <c r="E437" s="2" cm="1">
         <f t="array" ref="E437">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17230,14 +17381,14 @@
     </row>
     <row r="438" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B438" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C438" s="6" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="D438" s="6" t="str" cm="1">
         <f t="array" ref="D438">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة شرورة</v>
+        <v>مجموعة الشرقية</v>
       </c>
       <c r="E438" s="2" cm="1">
         <f t="array" ref="E438">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17246,14 +17397,14 @@
     </row>
     <row r="439" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B439" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C439" s="6" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="D439" s="6" t="str" cm="1">
         <f t="array" ref="D439">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة شرورة</v>
+        <v>مجموعة الشرقية</v>
       </c>
       <c r="E439" s="2" cm="1">
         <f t="array" ref="E439">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17262,14 +17413,14 @@
     </row>
     <row r="440" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B440" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C440" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D440" s="6" t="str" cm="1">
         <f t="array" ref="D440">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة نجران</v>
+        <v>مجموعة شرورة</v>
       </c>
       <c r="E440" s="2" cm="1">
         <f t="array" ref="E440">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17278,14 +17429,14 @@
     </row>
     <row r="441" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B441" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C441" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D441" s="6" t="str" cm="1">
         <f t="array" ref="D441">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة نجران</v>
+        <v>مجموعة شرورة</v>
       </c>
       <c r="E441" s="2" cm="1">
         <f t="array" ref="E441">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17294,14 +17445,14 @@
     </row>
     <row r="442" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B442" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C442" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D442" s="6" t="str" cm="1">
         <f t="array" ref="D442">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة نجران</v>
+        <v>مجموعة شرورة</v>
       </c>
       <c r="E442" s="2" cm="1">
         <f t="array" ref="E442">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17310,7 +17461,7 @@
     </row>
     <row r="443" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B443" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C443" s="6" t="s">
         <v>74</v>
@@ -17326,14 +17477,14 @@
     </row>
     <row r="444" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B444" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C444" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D444" s="6" t="str" cm="1">
         <f t="array" ref="D444">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة شقراء</v>
+        <v>مجموعة نجران</v>
       </c>
       <c r="E444" s="2" cm="1">
         <f t="array" ref="E444">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17342,14 +17493,14 @@
     </row>
     <row r="445" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B445" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C445" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D445" s="6" t="str" cm="1">
         <f t="array" ref="D445">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة شقراء</v>
+        <v>مجموعة نجران</v>
       </c>
       <c r="E445" s="2" cm="1">
         <f t="array" ref="E445">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17358,14 +17509,14 @@
     </row>
     <row r="446" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B446" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C446" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D446" s="6" t="str" cm="1">
         <f t="array" ref="D446">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة شقراء</v>
+        <v>مجموعة نجران</v>
       </c>
       <c r="E446" s="2" cm="1">
         <f t="array" ref="E446">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17374,14 +17525,14 @@
     </row>
     <row r="447" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B447" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C447" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D447" s="6" t="str" cm="1">
         <f t="array" ref="D447">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المجمعة</v>
+        <v>مجموعة شقراء</v>
       </c>
       <c r="E447" s="2" cm="1">
         <f t="array" ref="E447">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17390,14 +17541,14 @@
     </row>
     <row r="448" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B448" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C448" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D448" s="6" t="str" cm="1">
         <f t="array" ref="D448">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المجمعة</v>
+        <v>مجموعة شقراء</v>
       </c>
       <c r="E448" s="2" cm="1">
         <f t="array" ref="E448">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17406,14 +17557,14 @@
     </row>
     <row r="449" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B449" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C449" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D449" s="6" t="str" cm="1">
         <f t="array" ref="D449">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المجمعة</v>
+        <v>مجموعة شقراء</v>
       </c>
       <c r="E449" s="2" cm="1">
         <f t="array" ref="E449">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17422,7 +17573,7 @@
     </row>
     <row r="450" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B450" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C450" s="6" t="s">
         <v>76</v>
@@ -17438,78 +17589,78 @@
     </row>
     <row r="451" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B451" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C451" s="6" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="D451" s="6" t="str" cm="1">
         <f t="array" ref="D451">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة صامطة</v>
+        <v>مجموعة المجمعة</v>
       </c>
       <c r="E451" s="2" cm="1">
         <f t="array" ref="E451">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B452" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C452" s="6" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="D452" s="6" t="str" cm="1">
         <f t="array" ref="D452">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة صامطة</v>
+        <v>مجموعة المجمعة</v>
       </c>
       <c r="E452" s="2" cm="1">
         <f t="array" ref="E452">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B453" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C453" s="6" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="D453" s="6" t="str" cm="1">
         <f t="array" ref="D453">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة صامطة</v>
+        <v>مجموعة المجمعة</v>
       </c>
       <c r="E453" s="2" cm="1">
         <f t="array" ref="E453">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="454" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B454" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C454" s="6" t="s">
         <v>134</v>
       </c>
       <c r="D454" s="6" t="str" cm="1">
         <f t="array" ref="D454">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جازان</v>
+        <v>مجموعة صامطة</v>
       </c>
       <c r="E454" s="2" cm="1">
         <f t="array" ref="E454">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="455" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B455" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C455" s="6" t="s">
         <v>134</v>
       </c>
       <c r="D455" s="6" t="str" cm="1">
         <f t="array" ref="D455">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جازان</v>
+        <v>مجموعة صامطة</v>
       </c>
       <c r="E455" s="2" cm="1">
         <f t="array" ref="E455">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17518,23 +17669,23 @@
     </row>
     <row r="456" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B456" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C456" s="6" t="s">
         <v>134</v>
       </c>
       <c r="D456" s="6" t="str" cm="1">
         <f t="array" ref="D456">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جازان</v>
+        <v>مجموعة صامطة</v>
       </c>
       <c r="E456" s="2" cm="1">
         <f t="array" ref="E456">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="457" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B457" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C457" s="6" t="s">
         <v>134</v>
@@ -17545,35 +17696,35 @@
       </c>
       <c r="E457" s="2" cm="1">
         <f t="array" ref="E457">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="458" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B458" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C458" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D458" s="6" t="str" cm="1">
         <f t="array" ref="D458">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة صبيا</v>
+        <v>مجموعة جازان</v>
       </c>
       <c r="E458" s="2" cm="1">
         <f t="array" ref="E458">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="459" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B459" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C459" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D459" s="6" t="str" cm="1">
         <f t="array" ref="D459">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة صبيا</v>
+        <v>مجموعة جازان</v>
       </c>
       <c r="E459" s="2" cm="1">
         <f t="array" ref="E459">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17582,14 +17733,14 @@
     </row>
     <row r="460" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B460" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C460" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D460" s="6" t="str" cm="1">
         <f t="array" ref="D460">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة صبيا</v>
+        <v>مجموعة جازان</v>
       </c>
       <c r="E460" s="2" cm="1">
         <f t="array" ref="E460">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17598,14 +17749,14 @@
     </row>
     <row r="461" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B461" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C461" s="6" t="s">
         <v>133</v>
       </c>
       <c r="D461" s="6" t="str" cm="1">
         <f t="array" ref="D461">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جازان</v>
+        <v>مجموعة صبيا</v>
       </c>
       <c r="E461" s="2" cm="1">
         <f t="array" ref="E461">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17614,14 +17765,14 @@
     </row>
     <row r="462" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B462" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C462" s="6" t="s">
         <v>133</v>
       </c>
       <c r="D462" s="6" t="str" cm="1">
         <f t="array" ref="D462">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جازان</v>
+        <v>مجموعة صبيا</v>
       </c>
       <c r="E462" s="2" cm="1">
         <f t="array" ref="E462">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17630,23 +17781,23 @@
     </row>
     <row r="463" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B463" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C463" s="6" t="s">
         <v>133</v>
       </c>
       <c r="D463" s="6" t="str" cm="1">
         <f t="array" ref="D463">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جازان</v>
+        <v>مجموعة صبيا</v>
       </c>
       <c r="E463" s="2" cm="1">
         <f t="array" ref="E463">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="464" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B464" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C464" s="6" t="s">
         <v>133</v>
@@ -17657,60 +17808,60 @@
       </c>
       <c r="E464" s="2" cm="1">
         <f t="array" ref="E464">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="465" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B465" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C465" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D465" s="6" t="str" cm="1">
         <f t="array" ref="D465">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القطيف</v>
+        <v>مجموعة جازان</v>
       </c>
       <c r="E465" s="2" cm="1">
         <f t="array" ref="E465">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="466" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B466" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C466" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D466" s="6" t="str" cm="1">
         <f t="array" ref="D466">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القطيف</v>
+        <v>مجموعة جازان</v>
       </c>
       <c r="E466" s="2" cm="1">
         <f t="array" ref="E466">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="467" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B467" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C467" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D467" s="6" t="str" cm="1">
         <f t="array" ref="D467">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القطيف</v>
+        <v>مجموعة جازان</v>
       </c>
       <c r="E467" s="2" cm="1">
         <f t="array" ref="E467">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="468" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B468" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C468" s="6" t="s">
         <v>127</v>
@@ -17726,7 +17877,7 @@
     </row>
     <row r="469" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B469" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C469" s="6" t="s">
         <v>127</v>
@@ -17742,7 +17893,7 @@
     </row>
     <row r="470" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B470" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C470" s="6" t="s">
         <v>127</v>
@@ -17758,7 +17909,7 @@
     </row>
     <row r="471" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B471" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C471" s="6" t="s">
         <v>127</v>
@@ -17774,14 +17925,14 @@
     </row>
     <row r="472" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B472" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C472" s="6" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D472" s="6" t="str" cm="1">
         <f t="array" ref="D472">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المزاحمية</v>
+        <v>مجموعة القطيف</v>
       </c>
       <c r="E472" s="2" cm="1">
         <f t="array" ref="E472">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17790,14 +17941,14 @@
     </row>
     <row r="473" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B473" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C473" s="6" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D473" s="6" t="str" cm="1">
         <f t="array" ref="D473">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المزاحمية</v>
+        <v>مجموعة القطيف</v>
       </c>
       <c r="E473" s="2" cm="1">
         <f t="array" ref="E473">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17806,14 +17957,14 @@
     </row>
     <row r="474" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B474" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C474" s="6" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D474" s="6" t="str" cm="1">
         <f t="array" ref="D474">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة المزاحمية</v>
+        <v>مجموعة القطيف</v>
       </c>
       <c r="E474" s="2" cm="1">
         <f t="array" ref="E474">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17822,14 +17973,14 @@
     </row>
     <row r="475" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B475" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C475" s="6" t="s">
         <v>115</v>
       </c>
       <c r="D475" s="6" t="str" cm="1">
         <f t="array" ref="D475">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الرياض</v>
+        <v>مجموعة المزاحمية</v>
       </c>
       <c r="E475" s="2" cm="1">
         <f t="array" ref="E475">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17838,14 +17989,14 @@
     </row>
     <row r="476" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B476" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C476" s="6" t="s">
         <v>115</v>
       </c>
       <c r="D476" s="6" t="str" cm="1">
         <f t="array" ref="D476">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الرياض</v>
+        <v>مجموعة المزاحمية</v>
       </c>
       <c r="E476" s="2" cm="1">
         <f t="array" ref="E476">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17854,14 +18005,14 @@
     </row>
     <row r="477" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B477" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C477" s="6" t="s">
         <v>115</v>
       </c>
       <c r="D477" s="6" t="str" cm="1">
         <f t="array" ref="D477">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الرياض</v>
+        <v>مجموعة المزاحمية</v>
       </c>
       <c r="E477" s="2" cm="1">
         <f t="array" ref="E477">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17870,7 +18021,7 @@
     </row>
     <row r="478" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B478" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C478" s="6" t="s">
         <v>115</v>
@@ -17886,14 +18037,14 @@
     </row>
     <row r="479" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B479" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C479" s="6" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="D479" s="6" t="str" cm="1">
         <f t="array" ref="D479">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة صبيا</v>
+        <v>مجموعة الرياض</v>
       </c>
       <c r="E479" s="2" cm="1">
         <f t="array" ref="E479">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17902,62 +18053,62 @@
     </row>
     <row r="480" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B480" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C480" s="6" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="D480" s="6" t="str" cm="1">
         <f t="array" ref="D480">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة صبيا</v>
+        <v>مجموعة الرياض</v>
       </c>
       <c r="E480" s="2" cm="1">
         <f t="array" ref="E480">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="481" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B481" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C481" s="6" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="D481" s="6" t="str" cm="1">
         <f t="array" ref="D481">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة صبيا</v>
+        <v>مجموعة الرياض</v>
       </c>
       <c r="E481" s="2" cm="1">
         <f t="array" ref="E481">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="482" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B482" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C482" s="6" t="s">
         <v>136</v>
       </c>
       <c r="D482" s="6" t="str" cm="1">
         <f t="array" ref="D482">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جازان</v>
+        <v>مجموعة صبيا</v>
       </c>
       <c r="E482" s="2" cm="1">
         <f t="array" ref="E482">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B483" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C483" s="6" t="s">
         <v>136</v>
       </c>
       <c r="D483" s="6" t="str" cm="1">
         <f t="array" ref="D483">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جازان</v>
+        <v>مجموعة صبيا</v>
       </c>
       <c r="E483" s="2" cm="1">
         <f t="array" ref="E483">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17966,14 +18117,14 @@
     </row>
     <row r="484" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B484" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C484" s="6" t="s">
         <v>136</v>
       </c>
       <c r="D484" s="6" t="str" cm="1">
         <f t="array" ref="D484">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة جازان</v>
+        <v>مجموعة صبيا</v>
       </c>
       <c r="E484" s="2" cm="1">
         <f t="array" ref="E484">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -17982,7 +18133,7 @@
     </row>
     <row r="485" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B485" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C485" s="6" t="s">
         <v>136</v>
@@ -17998,55 +18149,55 @@
     </row>
     <row r="486" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B486" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="D486" s="6" t="str" cm="1">
         <f t="array" ref="D486">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الجوف</v>
+        <v>مجموعة جازان</v>
       </c>
       <c r="E486" s="2" cm="1">
         <f t="array" ref="E486">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="487" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B487" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C487" s="6" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="D487" s="6" t="str" cm="1">
         <f t="array" ref="D487">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الجوف</v>
+        <v>مجموعة جازان</v>
       </c>
       <c r="E487" s="2" cm="1">
         <f t="array" ref="E487">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="488" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B488" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C488" s="6" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="D488" s="6" t="str" cm="1">
         <f t="array" ref="D488">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الجوف</v>
+        <v>مجموعة جازان</v>
       </c>
       <c r="E488" s="2" cm="1">
         <f t="array" ref="E488">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="489" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B489" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C489" s="6" t="s">
         <v>110</v>
@@ -18062,14 +18213,14 @@
     </row>
     <row r="490" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B490" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D490" s="6" t="str" cm="1">
         <f t="array" ref="D490">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة طريف</v>
+        <v>مجموعة الجوف</v>
       </c>
       <c r="E490" s="2" cm="1">
         <f t="array" ref="E490">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18078,14 +18229,14 @@
     </row>
     <row r="491" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B491" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C491" s="6" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D491" s="6" t="str" cm="1">
         <f t="array" ref="D491">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة طريف</v>
+        <v>مجموعة الجوف</v>
       </c>
       <c r="E491" s="2" cm="1">
         <f t="array" ref="E491">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18094,14 +18245,14 @@
     </row>
     <row r="492" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B492" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C492" s="6" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D492" s="6" t="str" cm="1">
         <f t="array" ref="D492">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة طريف</v>
+        <v>مجموعة الجوف</v>
       </c>
       <c r="E492" s="2" cm="1">
         <f t="array" ref="E492">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18110,14 +18261,14 @@
     </row>
     <row r="493" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B493" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C493" s="6" t="s">
         <v>79</v>
       </c>
       <c r="D493" s="6" t="str" cm="1">
         <f t="array" ref="D493">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الحدود الشمالية</v>
+        <v>مجموعة طريف</v>
       </c>
       <c r="E493" s="2" cm="1">
         <f t="array" ref="E493">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18126,14 +18277,14 @@
     </row>
     <row r="494" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B494" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C494" s="6" t="s">
         <v>79</v>
       </c>
       <c r="D494" s="6" t="str" cm="1">
         <f t="array" ref="D494">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الحدود الشمالية</v>
+        <v>مجموعة طريف</v>
       </c>
       <c r="E494" s="2" cm="1">
         <f t="array" ref="E494">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18142,14 +18293,14 @@
     </row>
     <row r="495" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B495" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C495" s="6" t="s">
         <v>79</v>
       </c>
       <c r="D495" s="6" t="str" cm="1">
         <f t="array" ref="D495">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الحدود الشمالية</v>
+        <v>مجموعة طريف</v>
       </c>
       <c r="E495" s="2" cm="1">
         <f t="array" ref="E495">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18158,7 +18309,7 @@
     </row>
     <row r="496" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B496" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C496" s="6" t="s">
         <v>79</v>
@@ -18174,10 +18325,10 @@
     </row>
     <row r="497" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B497" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C497" s="6" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="D497" s="6" t="str" cm="1">
         <f t="array" ref="D497">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
@@ -18190,10 +18341,10 @@
     </row>
     <row r="498" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B498" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C498" s="6" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="D498" s="6" t="str" cm="1">
         <f t="array" ref="D498">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
@@ -18206,10 +18357,10 @@
     </row>
     <row r="499" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B499" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C499" s="6" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="D499" s="6" t="str" cm="1">
         <f t="array" ref="D499">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
@@ -18222,7 +18373,7 @@
     </row>
     <row r="500" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B500" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C500" s="6" t="s">
         <v>45</v>
@@ -18233,12 +18384,12 @@
       </c>
       <c r="E500" s="2" cm="1">
         <f t="array" ref="E500">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="501" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B501" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C501" s="6" t="s">
         <v>45</v>
@@ -18249,12 +18400,12 @@
       </c>
       <c r="E501" s="2" cm="1">
         <f t="array" ref="E501">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="502" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B502" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C502" s="6" t="s">
         <v>45</v>
@@ -18265,12 +18416,12 @@
       </c>
       <c r="E502" s="2" cm="1">
         <f t="array" ref="E502">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B503" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C503" s="6" t="s">
         <v>45</v>
@@ -18286,62 +18437,62 @@
     </row>
     <row r="504" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B504" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C504" s="6" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="D504" s="6" t="str" cm="1">
         <f t="array" ref="D504">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة عفيف</v>
+        <v>مجموعة الحدود الشمالية</v>
       </c>
       <c r="E504" s="2" cm="1">
         <f t="array" ref="E504">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="505" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B505" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C505" s="6" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="D505" s="6" t="str" cm="1">
         <f t="array" ref="D505">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة عفيف</v>
+        <v>مجموعة الحدود الشمالية</v>
       </c>
       <c r="E505" s="2" cm="1">
         <f t="array" ref="E505">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B506" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C506" s="6" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="D506" s="6" t="str" cm="1">
         <f t="array" ref="D506">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة عفيف</v>
+        <v>مجموعة الحدود الشمالية</v>
       </c>
       <c r="E506" s="2" cm="1">
         <f t="array" ref="E506">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="507" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B507" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C507" s="6" t="s">
         <v>81</v>
       </c>
       <c r="D507" s="6" t="str" cm="1">
         <f t="array" ref="D507">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الدوادمي</v>
+        <v>مجموعة عفيف</v>
       </c>
       <c r="E507" s="2" cm="1">
         <f t="array" ref="E507">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18350,14 +18501,14 @@
     </row>
     <row r="508" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B508" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C508" s="6" t="s">
         <v>81</v>
       </c>
       <c r="D508" s="6" t="str" cm="1">
         <f t="array" ref="D508">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الدوادمي</v>
+        <v>مجموعة عفيف</v>
       </c>
       <c r="E508" s="2" cm="1">
         <f t="array" ref="E508">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18366,14 +18517,14 @@
     </row>
     <row r="509" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B509" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C509" s="6" t="s">
         <v>81</v>
       </c>
       <c r="D509" s="6" t="str" cm="1">
         <f t="array" ref="D509">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الدوادمي</v>
+        <v>مجموعة عفيف</v>
       </c>
       <c r="E509" s="2" cm="1">
         <f t="array" ref="E509">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18382,7 +18533,7 @@
     </row>
     <row r="510" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B510" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C510" s="6" t="s">
         <v>81</v>
@@ -18398,14 +18549,14 @@
     </row>
     <row r="511" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B511" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C511" s="6" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="D511" s="6" t="str" cm="1">
         <f t="array" ref="D511">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة عنيزة</v>
+        <v>مجموعة الدوادمي</v>
       </c>
       <c r="E511" s="2" cm="1">
         <f t="array" ref="E511">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18414,14 +18565,14 @@
     </row>
     <row r="512" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B512" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C512" s="6" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="D512" s="6" t="str" cm="1">
         <f t="array" ref="D512">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة عنيزة</v>
+        <v>مجموعة الدوادمي</v>
       </c>
       <c r="E512" s="2" cm="1">
         <f t="array" ref="E512">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18430,14 +18581,14 @@
     </row>
     <row r="513" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B513" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C513" s="6" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="D513" s="6" t="str" cm="1">
         <f t="array" ref="D513">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة عنيزة</v>
+        <v>مجموعة الدوادمي</v>
       </c>
       <c r="E513" s="2" cm="1">
         <f t="array" ref="E513">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18446,14 +18597,14 @@
     </row>
     <row r="514" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B514" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C514" s="6" t="s">
         <v>121</v>
       </c>
       <c r="D514" s="6" t="str" cm="1">
         <f t="array" ref="D514">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القصيم</v>
+        <v>مجموعة عنيزة</v>
       </c>
       <c r="E514" s="2" cm="1">
         <f t="array" ref="E514">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18462,14 +18613,14 @@
     </row>
     <row r="515" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B515" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C515" s="6" t="s">
         <v>121</v>
       </c>
       <c r="D515" s="6" t="str" cm="1">
         <f t="array" ref="D515">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القصيم</v>
+        <v>مجموعة عنيزة</v>
       </c>
       <c r="E515" s="2" cm="1">
         <f t="array" ref="E515">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18478,23 +18629,23 @@
     </row>
     <row r="516" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B516" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C516" s="6" t="s">
         <v>121</v>
       </c>
       <c r="D516" s="6" t="str" cm="1">
         <f t="array" ref="D516">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة القصيم</v>
+        <v>مجموعة عنيزة</v>
       </c>
       <c r="E516" s="2" cm="1">
         <f t="array" ref="E516">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="517" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B517" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C517" s="6" t="s">
         <v>121</v>
@@ -18505,15 +18656,15 @@
       </c>
       <c r="E517" s="2" cm="1">
         <f t="array" ref="E517">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="518" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B518" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C518" s="6" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="D518" s="6" t="str" cm="1">
         <f t="array" ref="D518">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
@@ -18521,15 +18672,15 @@
       </c>
       <c r="E518" s="2" cm="1">
         <f t="array" ref="E518">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="519" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B519" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C519" s="6" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="D519" s="6" t="str" cm="1">
         <f t="array" ref="D519">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
@@ -18542,10 +18693,10 @@
     </row>
     <row r="520" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B520" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C520" s="6" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="D520" s="6" t="str" cm="1">
         <f t="array" ref="D520">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
@@ -18561,15 +18712,15 @@
         <v>4</v>
       </c>
       <c r="C521" s="6" t="s">
-        <v>84</v>
+        <v>149</v>
       </c>
       <c r="D521" s="6" t="str" cm="1">
         <f t="array" ref="D521">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة فرسان</v>
+        <v>مجموعة القصيم</v>
       </c>
       <c r="E521" s="2" cm="1">
         <f t="array" ref="E521">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522" spans="2:5" x14ac:dyDescent="0.35">
@@ -18577,15 +18728,15 @@
         <v>150</v>
       </c>
       <c r="C522" s="6" t="s">
-        <v>84</v>
+        <v>149</v>
       </c>
       <c r="D522" s="6" t="str" cm="1">
         <f t="array" ref="D522">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة فرسان</v>
+        <v>مجموعة القصيم</v>
       </c>
       <c r="E522" s="2" cm="1">
         <f t="array" ref="E522">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="523" spans="2:5" x14ac:dyDescent="0.35">
@@ -18593,15 +18744,15 @@
         <v>151</v>
       </c>
       <c r="C523" s="6" t="s">
-        <v>84</v>
+        <v>149</v>
       </c>
       <c r="D523" s="6" t="str" cm="1">
         <f t="array" ref="D523">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة فرسان</v>
+        <v>مجموعة القصيم</v>
       </c>
       <c r="E523" s="2" cm="1">
         <f t="array" ref="E523">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="524" spans="2:5" x14ac:dyDescent="0.35">
@@ -18609,11 +18760,11 @@
         <v>4</v>
       </c>
       <c r="C524" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D524" s="6" t="str" cm="1">
         <f t="array" ref="D524">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة قلوة</v>
+        <v>مجموعة فرسان</v>
       </c>
       <c r="E524" s="2" cm="1">
         <f t="array" ref="E524">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18625,11 +18776,11 @@
         <v>150</v>
       </c>
       <c r="C525" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D525" s="6" t="str" cm="1">
         <f t="array" ref="D525">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة قلوة</v>
+        <v>مجموعة فرسان</v>
       </c>
       <c r="E525" s="2" cm="1">
         <f t="array" ref="E525">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18641,11 +18792,11 @@
         <v>151</v>
       </c>
       <c r="C526" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D526" s="6" t="str" cm="1">
         <f t="array" ref="D526">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة قلوة</v>
+        <v>مجموعة فرسان</v>
       </c>
       <c r="E526" s="2" cm="1">
         <f t="array" ref="E526">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18654,14 +18805,14 @@
     </row>
     <row r="527" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B527" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C527" s="6" t="s">
         <v>86</v>
       </c>
       <c r="D527" s="6" t="str" cm="1">
         <f t="array" ref="D527">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الباحة</v>
+        <v>مجموعة قلوة</v>
       </c>
       <c r="E527" s="2" cm="1">
         <f t="array" ref="E527">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18670,14 +18821,14 @@
     </row>
     <row r="528" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B528" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C528" s="6" t="s">
         <v>86</v>
       </c>
       <c r="D528" s="6" t="str" cm="1">
         <f t="array" ref="D528">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الباحة</v>
+        <v>مجموعة قلوة</v>
       </c>
       <c r="E528" s="2" cm="1">
         <f t="array" ref="E528">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18686,14 +18837,14 @@
     </row>
     <row r="529" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B529" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C529" s="6" t="s">
         <v>86</v>
       </c>
       <c r="D529" s="6" t="str" cm="1">
         <f t="array" ref="D529">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الباحة</v>
+        <v>مجموعة قلوة</v>
       </c>
       <c r="E529" s="2" cm="1">
         <f t="array" ref="E529">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18702,7 +18853,7 @@
     </row>
     <row r="530" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B530" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C530" s="6" t="s">
         <v>86</v>
@@ -18718,14 +18869,14 @@
     </row>
     <row r="531" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B531" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C531" s="6" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="D531" s="6" t="str" cm="1">
         <f t="array" ref="D531">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة محايل عسير</v>
+        <v>مجموعة الباحة</v>
       </c>
       <c r="E531" s="2" cm="1">
         <f t="array" ref="E531">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18734,14 +18885,14 @@
     </row>
     <row r="532" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B532" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C532" s="6" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="D532" s="6" t="str" cm="1">
         <f t="array" ref="D532">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة محايل عسير</v>
+        <v>مجموعة الباحة</v>
       </c>
       <c r="E532" s="2" cm="1">
         <f t="array" ref="E532">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -18750,23 +18901,23 @@
     </row>
     <row r="533" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B533" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C533" s="6" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="D533" s="6" t="str" cm="1">
         <f t="array" ref="D533">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة محايل عسير</v>
+        <v>مجموعة الباحة</v>
       </c>
       <c r="E533" s="2" cm="1">
         <f t="array" ref="E533">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="534" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B534" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C534" s="6" t="s">
         <v>41</v>
@@ -18777,12 +18928,12 @@
       </c>
       <c r="E534" s="2" cm="1">
         <f t="array" ref="E534">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="535" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B535" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C535" s="6" t="s">
         <v>41</v>
@@ -18793,12 +18944,12 @@
       </c>
       <c r="E535" s="2" cm="1">
         <f t="array" ref="E535">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="536" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B536" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C536" s="6" t="s">
         <v>41</v>
@@ -18809,12 +18960,12 @@
       </c>
       <c r="E536" s="2" cm="1">
         <f t="array" ref="E536">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="537" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B537" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C537" s="6" t="s">
         <v>41</v>
@@ -18830,55 +18981,55 @@
     </row>
     <row r="538" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B538" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C538" s="6" t="s">
-        <v>144</v>
+        <v>41</v>
       </c>
       <c r="D538" s="6" t="str" cm="1">
         <f t="array" ref="D538">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة مكة المكرمة</v>
+        <v>مجموعة محايل عسير</v>
       </c>
       <c r="E538" s="2" cm="1">
         <f t="array" ref="E538">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="539" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B539" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C539" s="6" t="s">
-        <v>144</v>
+        <v>41</v>
       </c>
       <c r="D539" s="6" t="str" cm="1">
         <f t="array" ref="D539">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة مكة المكرمة</v>
+        <v>مجموعة محايل عسير</v>
       </c>
       <c r="E539" s="2" cm="1">
         <f t="array" ref="E539">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B540" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C540" s="6" t="s">
-        <v>144</v>
+        <v>41</v>
       </c>
       <c r="D540" s="6" t="str" cm="1">
         <f t="array" ref="D540">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة مكة المكرمة</v>
+        <v>مجموعة محايل عسير</v>
       </c>
       <c r="E540" s="2" cm="1">
         <f t="array" ref="E540">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="541" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B541" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C541" s="6" t="s">
         <v>144</v>
@@ -18889,12 +19040,12 @@
       </c>
       <c r="E541" s="2" cm="1">
         <f t="array" ref="E541">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="542" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B542" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C542" s="6" t="s">
         <v>144</v>
@@ -18910,7 +19061,7 @@
     </row>
     <row r="543" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B543" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C543" s="6" t="s">
         <v>144</v>
@@ -18921,12 +19072,12 @@
       </c>
       <c r="E543" s="2" cm="1">
         <f t="array" ref="E543">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="544" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B544" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C544" s="6" t="s">
         <v>144</v>
@@ -18942,55 +19093,55 @@
     </row>
     <row r="545" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B545" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C545" s="6" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="D545" s="6" t="str" cm="1">
         <f t="array" ref="D545">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة نجران</v>
+        <v>مجموعة مكة المكرمة</v>
       </c>
       <c r="E545" s="2" cm="1">
         <f t="array" ref="E545">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="546" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B546" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C546" s="6" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="D546" s="6" t="str" cm="1">
         <f t="array" ref="D546">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة نجران</v>
+        <v>مجموعة مكة المكرمة</v>
       </c>
       <c r="E546" s="2" cm="1">
         <f t="array" ref="E546">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="547" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B547" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C547" s="6" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="D547" s="6" t="str" cm="1">
         <f t="array" ref="D547">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة نجران</v>
+        <v>مجموعة مكة المكرمة</v>
       </c>
       <c r="E547" s="2" cm="1">
         <f t="array" ref="E547">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="548" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B548" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C548" s="6" t="s">
         <v>87</v>
@@ -19006,7 +19157,7 @@
     </row>
     <row r="549" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B549" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C549" s="6" t="s">
         <v>87</v>
@@ -19017,12 +19168,12 @@
       </c>
       <c r="E549" s="2" cm="1">
         <f t="array" ref="E549">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="550" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B550" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C550" s="6" t="s">
         <v>87</v>
@@ -19033,12 +19184,12 @@
       </c>
       <c r="E550" s="2" cm="1">
         <f t="array" ref="E550">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="551" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B551" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C551" s="6" t="s">
         <v>87</v>
@@ -19049,19 +19200,19 @@
       </c>
       <c r="E551" s="2" cm="1">
         <f t="array" ref="E551">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="552" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B552" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C552" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D552" s="6" t="str" cm="1">
         <f t="array" ref="D552">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة وادي الدواسر</v>
+        <v>مجموعة نجران</v>
       </c>
       <c r="E552" s="2" cm="1">
         <f t="array" ref="E552">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -19070,78 +19221,78 @@
     </row>
     <row r="553" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B553" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C553" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D553" s="6" t="str" cm="1">
         <f t="array" ref="D553">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة وادي الدواسر</v>
+        <v>مجموعة نجران</v>
       </c>
       <c r="E553" s="2" cm="1">
         <f t="array" ref="E553">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B554" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C554" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D554" s="6" t="str" cm="1">
         <f t="array" ref="D554">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة وادي الدواسر</v>
+        <v>مجموعة نجران</v>
       </c>
       <c r="E554" s="2" cm="1">
         <f t="array" ref="E554">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="555" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B555" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C555" s="6" t="s">
         <v>89</v>
       </c>
       <c r="D555" s="6" t="str" cm="1">
         <f t="array" ref="D555">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الدوادمي</v>
+        <v>مجموعة وادي الدواسر</v>
       </c>
       <c r="E555" s="2" cm="1">
         <f t="array" ref="E555">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="556" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B556" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C556" s="6" t="s">
         <v>89</v>
       </c>
       <c r="D556" s="6" t="str" cm="1">
         <f t="array" ref="D556">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الدوادمي</v>
+        <v>مجموعة وادي الدواسر</v>
       </c>
       <c r="E556" s="2" cm="1">
         <f t="array" ref="E556">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="557" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B557" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C557" s="6" t="s">
         <v>89</v>
       </c>
       <c r="D557" s="6" t="str" cm="1">
         <f t="array" ref="D557">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الدوادمي</v>
+        <v>مجموعة وادي الدواسر</v>
       </c>
       <c r="E557" s="2" cm="1">
         <f t="array" ref="E557">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -19150,7 +19301,7 @@
     </row>
     <row r="558" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B558" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C558" s="6" t="s">
         <v>89</v>
@@ -19161,19 +19312,19 @@
       </c>
       <c r="E558" s="2" cm="1">
         <f t="array" ref="E558">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="559" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B559" s="6" t="s">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="C559" s="6" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="D559" s="6" t="str" cm="1">
         <f t="array" ref="D559">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة ينبع</v>
+        <v>مجموعة الدوادمي</v>
       </c>
       <c r="E559" s="2" cm="1">
         <f t="array" ref="E559">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -19182,14 +19333,14 @@
     </row>
     <row r="560" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B560" s="6" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C560" s="6" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="D560" s="6" t="str" cm="1">
         <f t="array" ref="D560">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة ينبع</v>
+        <v>مجموعة الدوادمي</v>
       </c>
       <c r="E560" s="2" cm="1">
         <f t="array" ref="E560">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -19198,18 +19349,18 @@
     </row>
     <row r="561" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B561" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C561" s="6" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="D561" s="6" t="str" cm="1">
         <f t="array" ref="D561">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة ينبع</v>
+        <v>مجموعة الدوادمي</v>
       </c>
       <c r="E561" s="2" cm="1">
         <f t="array" ref="E561">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="562" spans="2:5" x14ac:dyDescent="0.35">
@@ -19217,15 +19368,15 @@
         <v>4</v>
       </c>
       <c r="C562" s="6" t="s">
-        <v>606</v>
+        <v>68</v>
       </c>
       <c r="D562" s="6" t="str" cm="1">
         <f t="array" ref="D562">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة أملج</v>
+        <v>مجموعة ينبع</v>
       </c>
       <c r="E562" s="2" cm="1">
         <f t="array" ref="E562">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="563" spans="2:5" x14ac:dyDescent="0.35">
@@ -19233,15 +19384,15 @@
         <v>150</v>
       </c>
       <c r="C563" s="6" t="s">
-        <v>606</v>
+        <v>68</v>
       </c>
       <c r="D563" s="6" t="str" cm="1">
         <f t="array" ref="D563">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة أملج</v>
+        <v>مجموعة ينبع</v>
       </c>
       <c r="E563" s="2" cm="1">
         <f t="array" ref="E563">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="564" spans="2:5" x14ac:dyDescent="0.35">
@@ -19249,20 +19400,20 @@
         <v>151</v>
       </c>
       <c r="C564" s="6" t="s">
-        <v>606</v>
+        <v>68</v>
       </c>
       <c r="D564" s="6" t="str" cm="1">
         <f t="array" ref="D564">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة أملج</v>
+        <v>مجموعة ينبع</v>
       </c>
       <c r="E564" s="2" cm="1">
         <f t="array" ref="E564">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="565" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B565" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="C565" s="6" t="s">
         <v>606</v>
@@ -19273,12 +19424,12 @@
       </c>
       <c r="E565" s="2" cm="1">
         <f t="array" ref="E565">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="566" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B566" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C566" s="6" t="s">
         <v>606</v>
@@ -19289,12 +19440,12 @@
       </c>
       <c r="E566" s="2" cm="1">
         <f t="array" ref="E566">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="567" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B567" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C567" s="6" t="s">
         <v>606</v>
@@ -19305,12 +19456,12 @@
       </c>
       <c r="E567" s="2" cm="1">
         <f t="array" ref="E567">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="568" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B568" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C568" s="6" t="s">
         <v>606</v>
@@ -19326,14 +19477,14 @@
     </row>
     <row r="569" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B569" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C569" s="6" t="s">
-        <v>701</v>
+        <v>606</v>
       </c>
       <c r="D569" s="6" t="str" cm="1">
         <f t="array" ref="D569">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الوجه</v>
+        <v>مجموعة أملج</v>
       </c>
       <c r="E569" s="2" cm="1">
         <f t="array" ref="E569">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -19342,39 +19493,39 @@
     </row>
     <row r="570" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B570" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C570" s="6" t="s">
-        <v>701</v>
+        <v>606</v>
       </c>
       <c r="D570" s="6" t="str" cm="1">
         <f t="array" ref="D570">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الوجه</v>
+        <v>مجموعة أملج</v>
       </c>
       <c r="E570" s="2" cm="1">
         <f t="array" ref="E570">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="571" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B571" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C571" s="6" t="s">
-        <v>701</v>
+        <v>606</v>
       </c>
       <c r="D571" s="6" t="str" cm="1">
         <f t="array" ref="D571">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة الوجه</v>
+        <v>مجموعة أملج</v>
       </c>
       <c r="E571" s="2" cm="1">
         <f t="array" ref="E571">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="572" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B572" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C572" s="6" t="s">
         <v>701</v>
@@ -19390,46 +19541,46 @@
     </row>
     <row r="573" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B573" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C573" s="6" t="s">
-        <v>362</v>
+        <v>701</v>
       </c>
       <c r="D573" s="6" t="str" cm="1">
         <f t="array" ref="D573">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة ضباء</v>
+        <v>مجموعة الوجه</v>
       </c>
       <c r="E573" s="2" cm="1">
         <f t="array" ref="E573">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="574" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B574" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C574" s="6" t="s">
-        <v>362</v>
+        <v>701</v>
       </c>
       <c r="D574" s="6" t="str" cm="1">
         <f t="array" ref="D574">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة ضباء</v>
+        <v>مجموعة الوجه</v>
       </c>
       <c r="E574" s="2" cm="1">
         <f t="array" ref="E574">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="575" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B575" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C575" s="6" t="s">
-        <v>362</v>
+        <v>701</v>
       </c>
       <c r="D575" s="6" t="str" cm="1">
         <f t="array" ref="D575">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة ضباء</v>
+        <v>مجموعة الوجه</v>
       </c>
       <c r="E575" s="2" cm="1">
         <f t="array" ref="E575">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -19438,7 +19589,7 @@
     </row>
     <row r="576" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B576" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C576" s="6" t="s">
         <v>362</v>
@@ -19449,19 +19600,19 @@
       </c>
       <c r="E576" s="2" cm="1">
         <f t="array" ref="E576">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="577" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B577" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C577" s="6" t="s">
-        <v>264</v>
+        <v>362</v>
       </c>
       <c r="D577" s="6" t="str" cm="1">
         <f t="array" ref="D577">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة مهد الذهب</v>
+        <v>مجموعة ضباء</v>
       </c>
       <c r="E577" s="2" cm="1">
         <f t="array" ref="E577">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
@@ -19470,39 +19621,39 @@
     </row>
     <row r="578" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B578" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C578" s="6" t="s">
-        <v>264</v>
+        <v>362</v>
       </c>
       <c r="D578" s="6" t="str" cm="1">
         <f t="array" ref="D578">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة مهد الذهب</v>
+        <v>مجموعة ضباء</v>
       </c>
       <c r="E578" s="2" cm="1">
         <f t="array" ref="E578">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="579" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B579" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C579" s="6" t="s">
-        <v>264</v>
+        <v>362</v>
       </c>
       <c r="D579" s="6" t="str" cm="1">
         <f t="array" ref="D579">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
-        <v>مجموعة مهد الذهب</v>
+        <v>مجموعة ضباء</v>
       </c>
       <c r="E579" s="2" cm="1">
         <f t="array" ref="E579">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="580" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B580" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C580" s="6" t="s">
         <v>264</v>
@@ -19513,6 +19664,54 @@
       </c>
       <c r="E580" s="2" cm="1">
         <f t="array" ref="E580">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B581" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C581" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D581" s="6" t="str" cm="1">
+        <f t="array" ref="D581">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
+        <v>مجموعة مهد الذهب</v>
+      </c>
+      <c r="E581" s="2" cm="1">
+        <f t="array" ref="E581">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B582" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C582" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D582" s="6" t="str" cm="1">
+        <f t="array" ref="D582">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
+        <v>مجموعة مهد الذهب</v>
+      </c>
+      <c r="E582" s="2" cm="1">
+        <f t="array" ref="E582">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B583" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C583" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D583" s="6" t="str" cm="1">
+        <f t="array" ref="D583">INDEX(المدن_المصدر[المجموعة],MATCH(1,(المدن_المصدر[الفئة العمرية]=VLOOKUP(تفاصيل_الفرق[[#This Row],[الفئة العمرية]],ربط_الفئات[],2,FALSE))*(المدن_المصدر[المدينة/المحافظة]=تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]),0))</f>
+        <v>مجموعة مهد الذهب</v>
+      </c>
+      <c r="E583" s="2" cm="1">
+        <f t="array" ref="E583">SUMPRODUCT((TRIM(التسجيل[المدينة])=TRIM(تفاصيل_الفرق[[#This Row],[المدينة/المحافظة]]))*INDEX(التسجيل[],0,MATCH("*"&amp;تفاصيل_الفرق[[#This Row],[الفئة العمرية]]&amp;"*",التسجيل[#Headers],0)))</f>
         <v>1</v>
       </c>
     </row>
@@ -19531,7 +19730,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9454EB1B-CAB5-4DFF-97FB-825E9861B431}">
-  <dimension ref="B2:HM227"/>
+  <dimension ref="B2:HM246"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="16.453125" style="3" customWidth="1"/>
@@ -20743,7 +20942,7 @@
         <v>2</v>
       </c>
       <c r="O21" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P21" s="12">
         <v>0</v>
@@ -31032,13 +31231,963 @@
         <v>0</v>
       </c>
     </row>
+    <row r="228" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B228" s="15">
+        <v>226</v>
+      </c>
+      <c r="C228" s="15" t="s">
+        <v>707</v>
+      </c>
+      <c r="D228" s="15" t="s">
+        <v>708</v>
+      </c>
+      <c r="E228" s="15">
+        <v>530282832</v>
+      </c>
+      <c r="F228" s="15" t="s">
+        <v>709</v>
+      </c>
+      <c r="G228" s="15" t="s">
+        <v>700</v>
+      </c>
+      <c r="H228" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="I228" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="J228" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="K228" s="12">
+        <v>0</v>
+      </c>
+      <c r="L228" s="12">
+        <v>1</v>
+      </c>
+      <c r="M228" s="12">
+        <v>1</v>
+      </c>
+      <c r="N228" s="12">
+        <v>0</v>
+      </c>
+      <c r="O228" s="12">
+        <v>1</v>
+      </c>
+      <c r="P228" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q228" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B229" s="15">
+        <v>227</v>
+      </c>
+      <c r="C229" s="15" t="s">
+        <v>710</v>
+      </c>
+      <c r="D229" s="15" t="s">
+        <v>711</v>
+      </c>
+      <c r="E229" s="15">
+        <v>561040409</v>
+      </c>
+      <c r="F229" s="15" t="s">
+        <v>710</v>
+      </c>
+      <c r="G229" s="15" t="s">
+        <v>700</v>
+      </c>
+      <c r="H229" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="I229" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="J229" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="K229" s="14">
+        <v>1</v>
+      </c>
+      <c r="L229" s="14">
+        <v>1</v>
+      </c>
+      <c r="M229" s="14">
+        <v>0</v>
+      </c>
+      <c r="N229" s="14">
+        <v>0</v>
+      </c>
+      <c r="O229" s="14">
+        <v>1</v>
+      </c>
+      <c r="P229" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q229" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B230" s="15">
+        <v>228</v>
+      </c>
+      <c r="C230" s="15" t="s">
+        <v>712</v>
+      </c>
+      <c r="D230" s="15" t="s">
+        <v>713</v>
+      </c>
+      <c r="E230" s="15">
+        <v>531210933</v>
+      </c>
+      <c r="F230" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G230" s="15" t="s">
+        <v>700</v>
+      </c>
+      <c r="H230" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I230" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="J230" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="K230" s="12">
+        <v>0</v>
+      </c>
+      <c r="L230" s="12">
+        <v>0</v>
+      </c>
+      <c r="M230" s="12">
+        <v>1</v>
+      </c>
+      <c r="N230" s="12">
+        <v>1</v>
+      </c>
+      <c r="O230" s="12">
+        <v>0</v>
+      </c>
+      <c r="P230" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q230" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B231" s="15">
+        <v>229</v>
+      </c>
+      <c r="C231" s="15" t="s">
+        <v>714</v>
+      </c>
+      <c r="D231" s="15" t="s">
+        <v>715</v>
+      </c>
+      <c r="E231" s="15">
+        <v>556046415</v>
+      </c>
+      <c r="F231" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="G231" s="15" t="s">
+        <v>700</v>
+      </c>
+      <c r="H231" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="I231" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="J231" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="K231" s="14">
+        <v>1</v>
+      </c>
+      <c r="L231" s="14">
+        <v>1</v>
+      </c>
+      <c r="M231" s="14">
+        <v>1</v>
+      </c>
+      <c r="N231" s="14">
+        <v>1</v>
+      </c>
+      <c r="O231" s="14">
+        <v>2</v>
+      </c>
+      <c r="P231" s="14">
+        <v>2</v>
+      </c>
+      <c r="Q231" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B232" s="15">
+        <v>230</v>
+      </c>
+      <c r="C232" s="15" t="s">
+        <v>716</v>
+      </c>
+      <c r="D232" s="15" t="s">
+        <v>717</v>
+      </c>
+      <c r="E232" s="15">
+        <v>565885126</v>
+      </c>
+      <c r="F232" s="15" t="s">
+        <v>716</v>
+      </c>
+      <c r="G232" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="H232" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="I232" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J232" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="K232" s="12">
+        <v>1</v>
+      </c>
+      <c r="L232" s="12">
+        <v>1</v>
+      </c>
+      <c r="M232" s="12">
+        <v>1</v>
+      </c>
+      <c r="N232" s="12">
+        <v>0</v>
+      </c>
+      <c r="O232" s="12">
+        <v>0</v>
+      </c>
+      <c r="P232" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q232" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B233" s="15">
+        <v>231</v>
+      </c>
+      <c r="C233" s="15" t="s">
+        <v>718</v>
+      </c>
+      <c r="D233" s="15" t="s">
+        <v>719</v>
+      </c>
+      <c r="E233" s="15">
+        <v>560404898</v>
+      </c>
+      <c r="F233" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G233" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="H233" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="I233" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="J233" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="K233" s="14">
+        <v>0</v>
+      </c>
+      <c r="L233" s="14">
+        <v>1</v>
+      </c>
+      <c r="M233" s="14">
+        <v>0</v>
+      </c>
+      <c r="N233" s="14">
+        <v>1</v>
+      </c>
+      <c r="O233" s="14">
+        <v>0</v>
+      </c>
+      <c r="P233" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q233" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B234" s="15">
+        <v>232</v>
+      </c>
+      <c r="C234" s="15" t="s">
+        <v>720</v>
+      </c>
+      <c r="D234" s="15" t="s">
+        <v>721</v>
+      </c>
+      <c r="E234" s="15">
+        <v>508665628</v>
+      </c>
+      <c r="F234" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G234" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="H234" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="I234" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J234" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="K234" s="12">
+        <v>0</v>
+      </c>
+      <c r="L234" s="12">
+        <v>1</v>
+      </c>
+      <c r="M234" s="12">
+        <v>1</v>
+      </c>
+      <c r="N234" s="12">
+        <v>1</v>
+      </c>
+      <c r="O234" s="12">
+        <v>1</v>
+      </c>
+      <c r="P234" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q234" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B235" s="15">
+        <v>233</v>
+      </c>
+      <c r="C235" s="15" t="s">
+        <v>722</v>
+      </c>
+      <c r="D235" s="15" t="s">
+        <v>723</v>
+      </c>
+      <c r="E235" s="15">
+        <v>556435560</v>
+      </c>
+      <c r="F235" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G235" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="H235" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="I235" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J235" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="K235" s="14">
+        <v>1</v>
+      </c>
+      <c r="L235" s="14">
+        <v>0</v>
+      </c>
+      <c r="M235" s="14">
+        <v>0</v>
+      </c>
+      <c r="N235" s="14">
+        <v>0</v>
+      </c>
+      <c r="O235" s="14">
+        <v>0</v>
+      </c>
+      <c r="P235" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q235" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B236" s="15">
+        <v>234</v>
+      </c>
+      <c r="C236" s="15" t="s">
+        <v>724</v>
+      </c>
+      <c r="D236" s="15" t="s">
+        <v>725</v>
+      </c>
+      <c r="E236" s="15">
+        <v>556613563</v>
+      </c>
+      <c r="F236" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G236" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="H236" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="I236" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J236" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="K236" s="12">
+        <v>1</v>
+      </c>
+      <c r="L236" s="12">
+        <v>1</v>
+      </c>
+      <c r="M236" s="12">
+        <v>1</v>
+      </c>
+      <c r="N236" s="12">
+        <v>0</v>
+      </c>
+      <c r="O236" s="12">
+        <v>0</v>
+      </c>
+      <c r="P236" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q236" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B237" s="15">
+        <v>235</v>
+      </c>
+      <c r="C237" s="15" t="s">
+        <v>726</v>
+      </c>
+      <c r="D237" s="15" t="s">
+        <v>727</v>
+      </c>
+      <c r="E237" s="15">
+        <v>535352410</v>
+      </c>
+      <c r="F237" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G237" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="H237" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I237" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J237" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="K237" s="14">
+        <v>1</v>
+      </c>
+      <c r="L237" s="14">
+        <v>0</v>
+      </c>
+      <c r="M237" s="14">
+        <v>1</v>
+      </c>
+      <c r="N237" s="14">
+        <v>0</v>
+      </c>
+      <c r="O237" s="14">
+        <v>0</v>
+      </c>
+      <c r="P237" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q237" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B238" s="15">
+        <v>236</v>
+      </c>
+      <c r="C238" s="15" t="s">
+        <v>728</v>
+      </c>
+      <c r="D238" s="15" t="s">
+        <v>729</v>
+      </c>
+      <c r="E238" s="15">
+        <v>559946660</v>
+      </c>
+      <c r="F238" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G238" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="H238" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="I238" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J238" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="K238" s="12">
+        <v>1</v>
+      </c>
+      <c r="L238" s="12">
+        <v>1</v>
+      </c>
+      <c r="M238" s="12">
+        <v>1</v>
+      </c>
+      <c r="N238" s="12">
+        <v>1</v>
+      </c>
+      <c r="O238" s="12">
+        <v>0</v>
+      </c>
+      <c r="P238" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q238" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B239" s="15">
+        <v>237</v>
+      </c>
+      <c r="C239" s="15" t="s">
+        <v>730</v>
+      </c>
+      <c r="D239" s="15" t="s">
+        <v>731</v>
+      </c>
+      <c r="E239" s="15">
+        <v>550424299</v>
+      </c>
+      <c r="F239" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G239" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="H239" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="I239" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J239" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K239" s="14">
+        <v>0</v>
+      </c>
+      <c r="L239" s="14">
+        <v>1</v>
+      </c>
+      <c r="M239" s="14">
+        <v>1</v>
+      </c>
+      <c r="N239" s="14">
+        <v>1</v>
+      </c>
+      <c r="O239" s="14">
+        <v>0</v>
+      </c>
+      <c r="P239" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q239" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B240" s="15">
+        <v>238</v>
+      </c>
+      <c r="C240" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="D240" s="15" t="s">
+        <v>733</v>
+      </c>
+      <c r="E240" s="15">
+        <v>551191791</v>
+      </c>
+      <c r="F240" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G240" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="H240" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I240" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="J240" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="K240" s="12">
+        <v>1</v>
+      </c>
+      <c r="L240" s="12">
+        <v>1</v>
+      </c>
+      <c r="M240" s="12">
+        <v>1</v>
+      </c>
+      <c r="N240" s="12">
+        <v>1</v>
+      </c>
+      <c r="O240" s="12">
+        <v>0</v>
+      </c>
+      <c r="P240" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q240" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B241" s="15">
+        <v>239</v>
+      </c>
+      <c r="C241" s="15" t="s">
+        <v>734</v>
+      </c>
+      <c r="D241" s="15" t="s">
+        <v>735</v>
+      </c>
+      <c r="E241" s="15">
+        <v>554268528</v>
+      </c>
+      <c r="F241" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G241" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="H241" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="I241" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J241" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="K241" s="14">
+        <v>1</v>
+      </c>
+      <c r="L241" s="14">
+        <v>1</v>
+      </c>
+      <c r="M241" s="14">
+        <v>1</v>
+      </c>
+      <c r="N241" s="14">
+        <v>1</v>
+      </c>
+      <c r="O241" s="14">
+        <v>1</v>
+      </c>
+      <c r="P241" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q241" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B242" s="15">
+        <v>240</v>
+      </c>
+      <c r="C242" s="15" t="s">
+        <v>736</v>
+      </c>
+      <c r="D242" s="15" t="s">
+        <v>737</v>
+      </c>
+      <c r="E242" s="15">
+        <v>500265545</v>
+      </c>
+      <c r="F242" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G242" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="H242" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I242" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J242" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="K242" s="12">
+        <v>1</v>
+      </c>
+      <c r="L242" s="12">
+        <v>1</v>
+      </c>
+      <c r="M242" s="12">
+        <v>1</v>
+      </c>
+      <c r="N242" s="12">
+        <v>1</v>
+      </c>
+      <c r="O242" s="12">
+        <v>1</v>
+      </c>
+      <c r="P242" s="12">
+        <v>1</v>
+      </c>
+      <c r="Q242" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B243" s="15">
+        <v>241</v>
+      </c>
+      <c r="C243" s="15" t="s">
+        <v>738</v>
+      </c>
+      <c r="D243" s="15" t="s">
+        <v>739</v>
+      </c>
+      <c r="E243" s="15">
+        <v>509245807</v>
+      </c>
+      <c r="F243" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G243" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="H243" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="I243" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="J243" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="K243" s="14">
+        <v>1</v>
+      </c>
+      <c r="L243" s="14">
+        <v>0</v>
+      </c>
+      <c r="M243" s="14">
+        <v>0</v>
+      </c>
+      <c r="N243" s="14">
+        <v>0</v>
+      </c>
+      <c r="O243" s="14">
+        <v>0</v>
+      </c>
+      <c r="P243" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q243" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B244" s="15">
+        <v>242</v>
+      </c>
+      <c r="C244" s="15" t="s">
+        <v>740</v>
+      </c>
+      <c r="D244" s="15" t="s">
+        <v>741</v>
+      </c>
+      <c r="E244" s="15">
+        <v>534641409</v>
+      </c>
+      <c r="F244" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G244" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="H244" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I244" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="J244" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="K244" s="12">
+        <v>1</v>
+      </c>
+      <c r="L244" s="12">
+        <v>0</v>
+      </c>
+      <c r="M244" s="12">
+        <v>0</v>
+      </c>
+      <c r="N244" s="12">
+        <v>0</v>
+      </c>
+      <c r="O244" s="12">
+        <v>0</v>
+      </c>
+      <c r="P244" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q244" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B245" s="15">
+        <v>243</v>
+      </c>
+      <c r="C245" s="15" t="s">
+        <v>742</v>
+      </c>
+      <c r="D245" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="E245" s="15">
+        <v>571133686</v>
+      </c>
+      <c r="F245" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G245" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="H245" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="I245" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="J245" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="K245" s="14">
+        <v>1</v>
+      </c>
+      <c r="L245" s="14">
+        <v>0</v>
+      </c>
+      <c r="M245" s="14">
+        <v>0</v>
+      </c>
+      <c r="N245" s="14">
+        <v>0</v>
+      </c>
+      <c r="O245" s="14">
+        <v>0</v>
+      </c>
+      <c r="P245" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q245" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="2:17" ht="17" x14ac:dyDescent="0.35">
+      <c r="B246" s="17">
+        <v>244</v>
+      </c>
+      <c r="C246" s="17" t="s">
+        <v>744</v>
+      </c>
+      <c r="D246" s="17" t="s">
+        <v>745</v>
+      </c>
+      <c r="E246" s="17">
+        <v>555299927</v>
+      </c>
+      <c r="F246" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="G246" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="H246" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I246" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="J246" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K246" s="12">
+        <v>0</v>
+      </c>
+      <c r="L246" s="12">
+        <v>0</v>
+      </c>
+      <c r="M246" s="12">
+        <v>1</v>
+      </c>
+      <c r="N246" s="12">
+        <v>0</v>
+      </c>
+      <c r="O246" s="12">
+        <v>0</v>
+      </c>
+      <c r="P246" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q246" s="12">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H227" xr:uid="{D6B9FDF5-5DF8-4124-BBB2-1189797DB0D6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H246" xr:uid="{D6B9FDF5-5DF8-4124-BBB2-1189797DB0D6}">
       <formula1>"الشرقية,الحدود الشمالية,حائل,تبوك,الجوف,الرياض,القصيم,المدينة المنورة,مكة المكرمة,الباحة,عسير,جازان,نجران"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G227" xr:uid="{0D086DC4-C253-4F2C-BC46-4D98516339D1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G246" xr:uid="{0D086DC4-C253-4F2C-BC46-4D98516339D1}">
       <formula1>"نادي,أكاديمية,هواة"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J1048576" xr:uid="{C70771D5-DC31-46B8-9D72-41134C1DE4DD}">
@@ -31056,7 +32205,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E85B3A8-D39B-4E9A-9642-B8B8450C6AC3}">
-  <dimension ref="B2:I166"/>
+  <dimension ref="B2:I167"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="6"/>
@@ -32941,6 +34090,17 @@
         <v>65</v>
       </c>
     </row>
+    <row r="167" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B167" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
@@ -32951,26 +34111,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="16be648b-369d-4545-b3ec-980ea45f5768" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="892e9dcf-b510-48d2-a32f-1ed59fe9f3eb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AFBC82852503AF4EAB2EF5018DE9DEC7" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="eab508c9951ee695015998ff06a21af9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="892e9dcf-b510-48d2-a32f-1ed59fe9f3eb" xmlns:ns3="16be648b-369d-4545-b3ec-980ea45f5768" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="73c3eb72b85b8edb3d3b90476ca60681" ns2:_="" ns3:_="">
     <xsd:import namespace="892e9dcf-b510-48d2-a32f-1ed59fe9f3eb"/>
@@ -33171,26 +34311,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A115B9C8-233C-43CA-A247-273FF172EBFC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FAA5E74-1211-482A-8855-78EF88D8B1E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="16be648b-369d-4545-b3ec-980ea45f5768"/>
-    <ds:schemaRef ds:uri="892e9dcf-b510-48d2-a32f-1ed59fe9f3eb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="16be648b-369d-4545-b3ec-980ea45f5768" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="892e9dcf-b510-48d2-a32f-1ed59fe9f3eb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D063081C-01A5-4A80-B507-73DEE5C9C0AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -33207,4 +34348,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A115B9C8-233C-43CA-A247-273FF172EBFC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FAA5E74-1211-482A-8855-78EF88D8B1E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="16be648b-369d-4545-b3ec-980ea45f5768"/>
+    <ds:schemaRef ds:uri="892e9dcf-b510-48d2-a32f-1ed59fe9f3eb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>